--- a/reports/Load_Test_Analysis_Report.xlsx
+++ b/reports/Load_Test_Analysis_Report.xlsx
@@ -1325,7 +1325,7 @@
         <v>Test Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:01:33</v>
+        <v>26/10/2026, 17:02:59</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Status:</v>
@@ -1635,13 +1635,13 @@
         <v>Sustained phase duration (s)</v>
       </c>
       <c r="B23" s="5">
-        <v>20.27</v>
+        <v>20.21</v>
       </c>
       <c r="D23" s="13" t="str">
         <v>Throughput (req/s)</v>
       </c>
       <c r="E23" s="13" t="str">
-        <v>119.36 (≥ 5)</v>
+        <v>150.04 (≥ 5)</v>
       </c>
       <c r="F23" s="25" t="str">
         <v>PASS</v>
@@ -1652,13 +1652,13 @@
         <v>Total HTTP requests</v>
       </c>
       <c r="B24" s="5">
-        <v>2420</v>
+        <v>3033</v>
       </c>
       <c r="D24" s="17" t="str">
         <v>p95 latency (ms)</v>
       </c>
       <c r="E24" s="17" t="str">
-        <v>732.2 (≤ 3000)</v>
+        <v>606.2 (≤ 3000)</v>
       </c>
       <c r="F24" s="25" t="str">
         <v>PASS</v>
@@ -1669,7 +1669,7 @@
         <v>Throughput (req/s)</v>
       </c>
       <c r="B25" s="5">
-        <v>119.36</v>
+        <v>150.04</v>
       </c>
       <c r="D25" s="13" t="str">
         <v>Error rate (%)</v>
@@ -1686,7 +1686,7 @@
         <v>Average latency (ms)</v>
       </c>
       <c r="B26" s="5">
-        <v>166.3</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="27">
@@ -1694,7 +1694,7 @@
         <v>p95 latency (ms)</v>
       </c>
       <c r="B27" s="5">
-        <v>732.2</v>
+        <v>606.2</v>
       </c>
     </row>
     <row r="28">
@@ -1702,7 +1702,7 @@
         <v>p99 latency (ms)</v>
       </c>
       <c r="B28" s="5">
-        <v>815.7</v>
+        <v>643.9</v>
       </c>
     </row>
     <row r="29">
@@ -1718,7 +1718,7 @@
         <v>Data transferred (MB)</v>
       </c>
       <c r="B30" s="5">
-        <v>1988</v>
+        <v>2497.7</v>
       </c>
     </row>
   </sheetData>
@@ -1825,10 +1825,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="13">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="H3" s="13">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I3" s="13">
         <v>1500</v>
@@ -1860,10 +1860,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="17">
-        <v>584</v>
+        <v>465</v>
       </c>
       <c r="H4" s="17">
-        <v>584</v>
+        <v>465</v>
       </c>
       <c r="I4" s="17">
         <v>2500</v>
@@ -1895,10 +1895,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="13">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H5" s="13">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I5" s="13">
         <v>2000</v>
@@ -1930,10 +1930,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="17">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H6" s="17">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I6" s="17">
         <v>1200</v>
@@ -1965,10 +1965,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="13">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="H7" s="13">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="I7" s="13">
         <v>1500</v>
@@ -2000,10 +2000,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="17">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H8" s="17">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I8" s="17">
         <v>1500</v>
@@ -2035,10 +2035,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="13">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="H9" s="13">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="I9" s="13">
         <v>2000</v>
@@ -2070,10 +2070,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="17">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="H10" s="17">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="I10" s="17">
         <v>1500</v>
@@ -2105,10 +2105,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="13">
-        <v>593</v>
+        <v>454</v>
       </c>
       <c r="H11" s="13">
-        <v>593</v>
+        <v>454</v>
       </c>
       <c r="I11" s="13">
         <v>2500</v>
@@ -2140,10 +2140,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="17">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H12" s="17">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I12" s="17">
         <v>1500</v>
@@ -2175,10 +2175,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="13">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H13" s="13">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I13" s="13">
         <v>2000</v>
@@ -2210,10 +2210,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="17">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H14" s="17">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I14" s="17">
         <v>1200</v>
@@ -2245,10 +2245,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="13">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H15" s="13">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I15" s="13">
         <v>1500</v>
@@ -2280,10 +2280,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="17">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H16" s="17">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I16" s="17">
         <v>1500</v>
@@ -2315,10 +2315,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="13">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H17" s="13">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I17" s="13">
         <v>2000</v>
@@ -2350,10 +2350,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="17">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H18" s="17">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I18" s="17">
         <v>1500</v>
@@ -2385,10 +2385,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="13">
-        <v>567</v>
+        <v>412</v>
       </c>
       <c r="H19" s="13">
-        <v>567</v>
+        <v>412</v>
       </c>
       <c r="I19" s="13">
         <v>2500</v>
@@ -2420,10 +2420,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="17">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H20" s="17">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I20" s="17">
         <v>2000</v>
@@ -2455,10 +2455,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="13">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H21" s="13">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I21" s="13">
         <v>1200</v>
@@ -2490,10 +2490,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="17">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H22" s="17">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I22" s="17">
         <v>1500</v>
@@ -2525,10 +2525,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="13">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H23" s="13">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I23" s="13">
         <v>1500</v>
@@ -2560,10 +2560,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="17">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H24" s="17">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I24" s="17">
         <v>2000</v>
@@ -2595,10 +2595,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="13">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H25" s="13">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I25" s="13">
         <v>1500</v>
@@ -2630,10 +2630,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="17">
-        <v>552</v>
+        <v>429</v>
       </c>
       <c r="H26" s="17">
-        <v>552</v>
+        <v>429</v>
       </c>
       <c r="I26" s="17">
         <v>2500</v>
@@ -2665,10 +2665,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="13">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H27" s="13">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I27" s="13">
         <v>2000</v>
@@ -2700,10 +2700,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="17">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H28" s="17">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I28" s="17">
         <v>1200</v>
@@ -2735,10 +2735,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="13">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H29" s="13">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I29" s="13">
         <v>1500</v>
@@ -2770,10 +2770,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="17">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H30" s="17">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I30" s="17">
         <v>1500</v>
@@ -2805,10 +2805,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="13">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H31" s="13">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I31" s="13">
         <v>2000</v>
@@ -2840,10 +2840,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="17">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H32" s="17">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I32" s="17">
         <v>1500</v>
@@ -2875,10 +2875,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="13">
-        <v>541</v>
+        <v>435</v>
       </c>
       <c r="H33" s="13">
-        <v>541</v>
+        <v>435</v>
       </c>
       <c r="I33" s="13">
         <v>2500</v>
@@ -2910,10 +2910,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="17">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H34" s="17">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="I34" s="17">
         <v>1500</v>
@@ -2945,10 +2945,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="13">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H35" s="13">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I35" s="13">
         <v>2000</v>
@@ -2980,10 +2980,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="17">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H36" s="17">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I36" s="17">
         <v>1200</v>
@@ -3015,10 +3015,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="13">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H37" s="13">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I37" s="13">
         <v>1500</v>
@@ -3050,10 +3050,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="17">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="H38" s="17">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="I38" s="17">
         <v>1500</v>
@@ -3085,10 +3085,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H39" s="13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I39" s="13">
         <v>2000</v>
@@ -3120,10 +3120,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="17">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H40" s="17">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I40" s="17">
         <v>1500</v>
@@ -3155,10 +3155,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="13">
-        <v>511</v>
+        <v>415</v>
       </c>
       <c r="H41" s="13">
-        <v>511</v>
+        <v>415</v>
       </c>
       <c r="I41" s="13">
         <v>2500</v>
@@ -3190,10 +3190,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="17">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="H42" s="17">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="I42" s="17">
         <v>2000</v>
@@ -3225,10 +3225,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="13">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H43" s="13">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I43" s="13">
         <v>1200</v>
@@ -3260,10 +3260,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="17">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H44" s="17">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I44" s="17">
         <v>1500</v>
@@ -3295,10 +3295,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="13">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H45" s="13">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I45" s="13">
         <v>1500</v>
@@ -3365,10 +3365,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H47" s="13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I47" s="13">
         <v>1500</v>
@@ -3400,10 +3400,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="17">
-        <v>461</v>
+        <v>399</v>
       </c>
       <c r="H48" s="17">
-        <v>461</v>
+        <v>399</v>
       </c>
       <c r="I48" s="17">
         <v>2500</v>
@@ -3435,10 +3435,10 @@
         <v>1</v>
       </c>
       <c r="G49" s="13">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H49" s="13">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I49" s="13">
         <v>2000</v>
@@ -3470,10 +3470,10 @@
         <v>1</v>
       </c>
       <c r="G50" s="17">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H50" s="17">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I50" s="17">
         <v>1200</v>
@@ -3505,10 +3505,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="13">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H51" s="13">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I51" s="13">
         <v>1500</v>
@@ -3540,10 +3540,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H52" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I52" s="17">
         <v>1500</v>
@@ -3575,10 +3575,10 @@
         <v>1</v>
       </c>
       <c r="G53" s="13">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H53" s="13">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I53" s="13">
         <v>2000</v>
@@ -3610,10 +3610,10 @@
         <v>1</v>
       </c>
       <c r="G54" s="17">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H54" s="17">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I54" s="17">
         <v>1500</v>
@@ -3645,10 +3645,10 @@
         <v>1</v>
       </c>
       <c r="G55" s="13">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="H55" s="13">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="I55" s="13">
         <v>2500</v>
@@ -3680,10 +3680,10 @@
         <v>1</v>
       </c>
       <c r="G56" s="17">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H56" s="17">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I56" s="17">
         <v>1500</v>
@@ -3750,10 +3750,10 @@
         <v>1</v>
       </c>
       <c r="G58" s="17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H58" s="17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I58" s="17">
         <v>1200</v>
@@ -3785,10 +3785,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="13">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H59" s="13">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I59" s="13">
         <v>1500</v>
@@ -3820,10 +3820,10 @@
         <v>1</v>
       </c>
       <c r="G60" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I60" s="17">
         <v>1500</v>
@@ -3855,10 +3855,10 @@
         <v>1</v>
       </c>
       <c r="G61" s="13">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H61" s="13">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I61" s="13">
         <v>2000</v>
@@ -3925,10 +3925,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="13">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="H63" s="13">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="I63" s="13">
         <v>2500</v>
@@ -3960,10 +3960,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="17">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H64" s="17">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I64" s="17">
         <v>2000</v>
@@ -3995,10 +3995,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I65" s="13">
         <v>1200</v>
@@ -4030,10 +4030,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="17">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H66" s="17">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I66" s="17">
         <v>1500</v>
@@ -4065,10 +4065,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H67" s="13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I67" s="13">
         <v>1500</v>
@@ -4100,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H68" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I68" s="17">
         <v>2000</v>
@@ -4135,10 +4135,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I69" s="13">
         <v>1500</v>
@@ -4170,10 +4170,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="17">
-        <v>426</v>
+        <v>373</v>
       </c>
       <c r="H70" s="17">
-        <v>426</v>
+        <v>373</v>
       </c>
       <c r="I70" s="17">
         <v>2500</v>
@@ -4205,10 +4205,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="13">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H71" s="13">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I71" s="13">
         <v>2000</v>
@@ -4275,10 +4275,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="13">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H73" s="13">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I73" s="13">
         <v>1500</v>
@@ -4310,10 +4310,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H74" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I74" s="17">
         <v>1500</v>
@@ -4345,10 +4345,10 @@
         <v>1</v>
       </c>
       <c r="G75" s="13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H75" s="13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I75" s="13">
         <v>2000</v>
@@ -4380,10 +4380,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H76" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I76" s="17">
         <v>1500</v>
@@ -4415,10 +4415,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="13">
-        <v>440</v>
+        <v>384</v>
       </c>
       <c r="H77" s="13">
-        <v>440</v>
+        <v>384</v>
       </c>
       <c r="I77" s="13">
         <v>2500</v>
@@ -4450,10 +4450,10 @@
         <v>1</v>
       </c>
       <c r="G78" s="17">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H78" s="17">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I78" s="17">
         <v>1500</v>
@@ -4485,10 +4485,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="13">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H79" s="13">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="I79" s="13">
         <v>2000</v>
@@ -4520,10 +4520,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H80" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I80" s="17">
         <v>1200</v>
@@ -4555,10 +4555,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H81" s="13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I81" s="13">
         <v>1500</v>
@@ -4590,10 +4590,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="17">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H82" s="17">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I82" s="17">
         <v>1500</v>
@@ -4625,10 +4625,10 @@
         <v>1</v>
       </c>
       <c r="G83" s="13">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H83" s="13">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I83" s="13">
         <v>2000</v>
@@ -4660,10 +4660,10 @@
         <v>1</v>
       </c>
       <c r="G84" s="17">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H84" s="17">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I84" s="17">
         <v>1500</v>
@@ -4695,10 +4695,10 @@
         <v>1</v>
       </c>
       <c r="G85" s="13">
-        <v>441</v>
+        <v>383</v>
       </c>
       <c r="H85" s="13">
-        <v>441</v>
+        <v>383</v>
       </c>
       <c r="I85" s="13">
         <v>2500</v>
@@ -4730,10 +4730,10 @@
         <v>1</v>
       </c>
       <c r="G86" s="17">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H86" s="17">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I86" s="17">
         <v>2000</v>
@@ -4765,10 +4765,10 @@
         <v>1</v>
       </c>
       <c r="G87" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I87" s="13">
         <v>1200</v>
@@ -4800,10 +4800,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H88" s="17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I88" s="17">
         <v>1500</v>
@@ -4835,10 +4835,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H89" s="13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I89" s="13">
         <v>1500</v>
@@ -4870,10 +4870,10 @@
         <v>1</v>
       </c>
       <c r="G90" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H90" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I90" s="17">
         <v>2000</v>
@@ -4905,10 +4905,10 @@
         <v>1</v>
       </c>
       <c r="G91" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H91" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I91" s="13">
         <v>1500</v>
@@ -4940,10 +4940,10 @@
         <v>1</v>
       </c>
       <c r="G92" s="17">
-        <v>443</v>
+        <v>378</v>
       </c>
       <c r="H92" s="17">
-        <v>443</v>
+        <v>378</v>
       </c>
       <c r="I92" s="17">
         <v>2500</v>
@@ -4975,10 +4975,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H93" s="13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I93" s="13">
         <v>2000</v>
@@ -5010,10 +5010,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H94" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I94" s="17">
         <v>1200</v>
@@ -5045,10 +5045,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H95" s="13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I95" s="13">
         <v>1500</v>
@@ -5080,10 +5080,10 @@
         <v>1</v>
       </c>
       <c r="G96" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H96" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I96" s="17">
         <v>1500</v>
@@ -5115,10 +5115,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="13">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I97" s="13">
         <v>2000</v>
@@ -5150,10 +5150,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="17">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H98" s="17">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I98" s="17">
         <v>1500</v>
@@ -5185,10 +5185,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="13">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="H99" s="13">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="I99" s="13">
         <v>2500</v>
@@ -5255,10 +5255,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="13">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H101" s="13">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I101" s="13">
         <v>2000</v>
@@ -5290,10 +5290,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H102" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I102" s="17">
         <v>1200</v>
@@ -5325,10 +5325,10 @@
         <v>1</v>
       </c>
       <c r="G103" s="13">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H103" s="13">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I103" s="13">
         <v>1500</v>
@@ -5360,10 +5360,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H104" s="17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I104" s="17">
         <v>1500</v>
@@ -5395,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H105" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I105" s="13">
         <v>2000</v>
@@ -5430,10 +5430,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="17">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H106" s="17">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I106" s="17">
         <v>1500</v>
@@ -5465,10 +5465,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="13">
-        <v>464</v>
+        <v>384</v>
       </c>
       <c r="H107" s="13">
-        <v>464</v>
+        <v>384</v>
       </c>
       <c r="I107" s="13">
         <v>2500</v>
@@ -5500,10 +5500,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H108" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I108" s="17">
         <v>2000</v>
@@ -5535,10 +5535,10 @@
         <v>1</v>
       </c>
       <c r="G109" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I109" s="13">
         <v>1200</v>
@@ -5570,10 +5570,10 @@
         <v>1</v>
       </c>
       <c r="G110" s="17">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H110" s="17">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I110" s="17">
         <v>1500</v>
@@ -5605,10 +5605,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="13">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H111" s="13">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I111" s="13">
         <v>1500</v>
@@ -5640,10 +5640,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H112" s="17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I112" s="17">
         <v>2000</v>
@@ -5675,10 +5675,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="13">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H113" s="13">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I113" s="13">
         <v>1500</v>
@@ -5710,10 +5710,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="17">
-        <v>468</v>
+        <v>355</v>
       </c>
       <c r="H114" s="17">
-        <v>468</v>
+        <v>355</v>
       </c>
       <c r="I114" s="17">
         <v>2500</v>
@@ -5745,10 +5745,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="13">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H115" s="13">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I115" s="13">
         <v>2000</v>
@@ -5780,10 +5780,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="17">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H116" s="17">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I116" s="17">
         <v>1200</v>
@@ -5815,10 +5815,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H117" s="13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I117" s="13">
         <v>1500</v>
@@ -5850,10 +5850,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H118" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I118" s="17">
         <v>1500</v>
@@ -5885,10 +5885,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="13">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H119" s="13">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I119" s="13">
         <v>2000</v>
@@ -5920,10 +5920,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="17">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H120" s="17">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I120" s="17">
         <v>1500</v>
@@ -5955,10 +5955,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="13">
-        <v>439</v>
+        <v>396</v>
       </c>
       <c r="H121" s="13">
-        <v>439</v>
+        <v>396</v>
       </c>
       <c r="I121" s="13">
         <v>2500</v>
@@ -5990,10 +5990,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="17">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H122" s="17">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I122" s="17">
         <v>1500</v>
@@ -6025,10 +6025,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="13">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H123" s="13">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I123" s="13">
         <v>2000</v>
@@ -6060,10 +6060,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="17">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H124" s="17">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I124" s="17">
         <v>1200</v>
@@ -6095,10 +6095,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H125" s="13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I125" s="13">
         <v>1500</v>
@@ -6130,10 +6130,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="17">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H126" s="17">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I126" s="17">
         <v>1500</v>
@@ -6165,10 +6165,10 @@
         <v>1</v>
       </c>
       <c r="G127" s="13">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="I127" s="13">
         <v>2000</v>
@@ -6200,10 +6200,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="17">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H128" s="17">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I128" s="17">
         <v>1500</v>
@@ -6235,10 +6235,10 @@
         <v>1</v>
       </c>
       <c r="G129" s="13">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="H129" s="13">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="I129" s="13">
         <v>2500</v>
@@ -6270,10 +6270,10 @@
         <v>1</v>
       </c>
       <c r="G130" s="17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H130" s="17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I130" s="17">
         <v>2000</v>
@@ -6305,10 +6305,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H131" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I131" s="13">
         <v>1200</v>
@@ -6340,10 +6340,10 @@
         <v>1</v>
       </c>
       <c r="G132" s="17">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H132" s="17">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I132" s="17">
         <v>1500</v>
@@ -6375,10 +6375,10 @@
         <v>1</v>
       </c>
       <c r="G133" s="13">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H133" s="13">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I133" s="13">
         <v>1500</v>
@@ -6410,10 +6410,10 @@
         <v>1</v>
       </c>
       <c r="G134" s="17">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H134" s="17">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I134" s="17">
         <v>2000</v>
@@ -6445,10 +6445,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="13">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H135" s="13">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I135" s="13">
         <v>1500</v>
@@ -6480,10 +6480,10 @@
         <v>1</v>
       </c>
       <c r="G136" s="17">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="H136" s="17">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="I136" s="17">
         <v>2500</v>
@@ -6515,10 +6515,10 @@
         <v>1</v>
       </c>
       <c r="G137" s="13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H137" s="13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I137" s="13">
         <v>2000</v>
@@ -6550,10 +6550,10 @@
         <v>1</v>
       </c>
       <c r="G138" s="17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H138" s="17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I138" s="17">
         <v>1200</v>
@@ -6585,10 +6585,10 @@
         <v>1</v>
       </c>
       <c r="G139" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H139" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I139" s="13">
         <v>1500</v>
@@ -6620,10 +6620,10 @@
         <v>1</v>
       </c>
       <c r="G140" s="17">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H140" s="17">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I140" s="17">
         <v>1500</v>
@@ -6655,10 +6655,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="13">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H141" s="13">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I141" s="13">
         <v>2000</v>
@@ -6690,10 +6690,10 @@
         <v>1</v>
       </c>
       <c r="G142" s="17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H142" s="17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I142" s="17">
         <v>1500</v>
@@ -6725,10 +6725,10 @@
         <v>1</v>
       </c>
       <c r="G143" s="13">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="H143" s="13">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="I143" s="13">
         <v>2500</v>
@@ -6760,10 +6760,10 @@
         <v>1</v>
       </c>
       <c r="G144" s="17">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H144" s="17">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I144" s="17">
         <v>1500</v>
@@ -6795,10 +6795,10 @@
         <v>1</v>
       </c>
       <c r="G145" s="13">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H145" s="13">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I145" s="13">
         <v>2000</v>
@@ -6830,10 +6830,10 @@
         <v>1</v>
       </c>
       <c r="G146" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H146" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I146" s="17">
         <v>1200</v>
@@ -6865,10 +6865,10 @@
         <v>1</v>
       </c>
       <c r="G147" s="13">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H147" s="13">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I147" s="13">
         <v>1500</v>
@@ -6900,10 +6900,10 @@
         <v>1</v>
       </c>
       <c r="G148" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H148" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I148" s="17">
         <v>1500</v>
@@ -6935,10 +6935,10 @@
         <v>1</v>
       </c>
       <c r="G149" s="13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H149" s="13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I149" s="13">
         <v>2000</v>
@@ -6970,10 +6970,10 @@
         <v>1</v>
       </c>
       <c r="G150" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H150" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I150" s="17">
         <v>1500</v>
@@ -7005,10 +7005,10 @@
         <v>1</v>
       </c>
       <c r="G151" s="13">
-        <v>390</v>
+        <v>355</v>
       </c>
       <c r="H151" s="13">
-        <v>390</v>
+        <v>355</v>
       </c>
       <c r="I151" s="13">
         <v>2500</v>
@@ -7040,10 +7040,10 @@
         <v>1</v>
       </c>
       <c r="G152" s="17">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H152" s="17">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I152" s="17">
         <v>2000</v>
@@ -7075,10 +7075,10 @@
         <v>1</v>
       </c>
       <c r="G153" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H153" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I153" s="13">
         <v>1200</v>
@@ -7110,10 +7110,10 @@
         <v>1</v>
       </c>
       <c r="G154" s="17">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H154" s="17">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I154" s="17">
         <v>1500</v>
@@ -7145,10 +7145,10 @@
         <v>1</v>
       </c>
       <c r="G155" s="13">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H155" s="13">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I155" s="13">
         <v>1500</v>
@@ -7215,10 +7215,10 @@
         <v>1</v>
       </c>
       <c r="G157" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H157" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I157" s="13">
         <v>1500</v>
@@ -7250,10 +7250,10 @@
         <v>1</v>
       </c>
       <c r="G158" s="17">
-        <v>469</v>
+        <v>324</v>
       </c>
       <c r="H158" s="17">
-        <v>469</v>
+        <v>324</v>
       </c>
       <c r="I158" s="17">
         <v>2500</v>
@@ -7285,10 +7285,10 @@
         <v>1</v>
       </c>
       <c r="G159" s="13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H159" s="13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I159" s="13">
         <v>2000</v>
@@ -7320,10 +7320,10 @@
         <v>1</v>
       </c>
       <c r="G160" s="17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H160" s="17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I160" s="17">
         <v>1200</v>
@@ -7355,10 +7355,10 @@
         <v>1</v>
       </c>
       <c r="G161" s="13">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H161" s="13">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I161" s="13">
         <v>1500</v>
@@ -7390,10 +7390,10 @@
         <v>1</v>
       </c>
       <c r="G162" s="17">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H162" s="17">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I162" s="17">
         <v>1500</v>
@@ -7425,10 +7425,10 @@
         <v>1</v>
       </c>
       <c r="G163" s="13">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H163" s="13">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I163" s="13">
         <v>2000</v>
@@ -7460,10 +7460,10 @@
         <v>1</v>
       </c>
       <c r="G164" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H164" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I164" s="17">
         <v>1500</v>
@@ -7495,10 +7495,10 @@
         <v>1</v>
       </c>
       <c r="G165" s="13">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="H165" s="13">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="I165" s="13">
         <v>2500</v>
@@ -7530,10 +7530,10 @@
         <v>1</v>
       </c>
       <c r="G166" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H166" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I166" s="17">
         <v>1500</v>
@@ -7565,10 +7565,10 @@
         <v>1</v>
       </c>
       <c r="G167" s="13">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H167" s="13">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I167" s="13">
         <v>2000</v>
@@ -7600,10 +7600,10 @@
         <v>1</v>
       </c>
       <c r="G168" s="17">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H168" s="17">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I168" s="17">
         <v>1200</v>
@@ -7635,10 +7635,10 @@
         <v>1</v>
       </c>
       <c r="G169" s="13">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H169" s="13">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I169" s="13">
         <v>1500</v>
@@ -7670,10 +7670,10 @@
         <v>1</v>
       </c>
       <c r="G170" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H170" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I170" s="17">
         <v>1500</v>
@@ -7705,10 +7705,10 @@
         <v>1</v>
       </c>
       <c r="G171" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H171" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I171" s="13">
         <v>2000</v>
@@ -7775,10 +7775,10 @@
         <v>1</v>
       </c>
       <c r="G173" s="13">
-        <v>370</v>
+        <v>292</v>
       </c>
       <c r="H173" s="13">
-        <v>370</v>
+        <v>292</v>
       </c>
       <c r="I173" s="13">
         <v>2500</v>
@@ -7810,10 +7810,10 @@
         <v>1</v>
       </c>
       <c r="G174" s="17">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H174" s="17">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I174" s="17">
         <v>2000</v>
@@ -7845,10 +7845,10 @@
         <v>1</v>
       </c>
       <c r="G175" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H175" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I175" s="13">
         <v>1200</v>
@@ -7880,10 +7880,10 @@
         <v>1</v>
       </c>
       <c r="G176" s="17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H176" s="17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I176" s="17">
         <v>1500</v>
@@ -7915,10 +7915,10 @@
         <v>1</v>
       </c>
       <c r="G177" s="13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H177" s="13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I177" s="13">
         <v>1500</v>
@@ -7985,10 +7985,10 @@
         <v>1</v>
       </c>
       <c r="G179" s="13">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H179" s="13">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I179" s="13">
         <v>1500</v>
@@ -8020,10 +8020,10 @@
         <v>1</v>
       </c>
       <c r="G180" s="17">
-        <v>404</v>
+        <v>285</v>
       </c>
       <c r="H180" s="17">
-        <v>404</v>
+        <v>285</v>
       </c>
       <c r="I180" s="17">
         <v>2500</v>
@@ -8055,10 +8055,10 @@
         <v>1</v>
       </c>
       <c r="G181" s="13">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H181" s="13">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="I181" s="13">
         <v>2000</v>
@@ -8090,10 +8090,10 @@
         <v>1</v>
       </c>
       <c r="G182" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H182" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I182" s="17">
         <v>1200</v>
@@ -8125,10 +8125,10 @@
         <v>1</v>
       </c>
       <c r="G183" s="13">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H183" s="13">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I183" s="13">
         <v>1500</v>
@@ -8160,10 +8160,10 @@
         <v>1</v>
       </c>
       <c r="G184" s="17">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H184" s="17">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I184" s="17">
         <v>1500</v>
@@ -8195,10 +8195,10 @@
         <v>1</v>
       </c>
       <c r="G185" s="13">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H185" s="13">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I185" s="13">
         <v>2000</v>
@@ -8230,10 +8230,10 @@
         <v>1</v>
       </c>
       <c r="G186" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H186" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I186" s="17">
         <v>1500</v>
@@ -8265,10 +8265,10 @@
         <v>1</v>
       </c>
       <c r="G187" s="13">
-        <v>370</v>
+        <v>278</v>
       </c>
       <c r="H187" s="13">
-        <v>370</v>
+        <v>278</v>
       </c>
       <c r="I187" s="13">
         <v>2500</v>
@@ -8335,10 +8335,10 @@
         <v>1</v>
       </c>
       <c r="G189" s="13">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H189" s="13">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I189" s="13">
         <v>2000</v>
@@ -8370,10 +8370,10 @@
         <v>1</v>
       </c>
       <c r="G190" s="17">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H190" s="17">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I190" s="17">
         <v>1200</v>
@@ -8405,10 +8405,10 @@
         <v>1</v>
       </c>
       <c r="G191" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H191" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I191" s="13">
         <v>1500</v>
@@ -8440,10 +8440,10 @@
         <v>1</v>
       </c>
       <c r="G192" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H192" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I192" s="17">
         <v>1500</v>
@@ -8475,10 +8475,10 @@
         <v>1</v>
       </c>
       <c r="G193" s="13">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H193" s="13">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I193" s="13">
         <v>2000</v>
@@ -8510,10 +8510,10 @@
         <v>1</v>
       </c>
       <c r="G194" s="17">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H194" s="17">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I194" s="17">
         <v>1500</v>
@@ -8545,10 +8545,10 @@
         <v>1</v>
       </c>
       <c r="G195" s="13">
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="H195" s="13">
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="I195" s="13">
         <v>2500</v>
@@ -8580,10 +8580,10 @@
         <v>1</v>
       </c>
       <c r="G196" s="17">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H196" s="17">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I196" s="17">
         <v>2000</v>
@@ -8615,10 +8615,10 @@
         <v>1</v>
       </c>
       <c r="G197" s="13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I197" s="13">
         <v>1200</v>
@@ -8650,10 +8650,10 @@
         <v>1</v>
       </c>
       <c r="G198" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H198" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I198" s="17">
         <v>1500</v>
@@ -8685,10 +8685,10 @@
         <v>1</v>
       </c>
       <c r="G199" s="13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H199" s="13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I199" s="13">
         <v>1500</v>
@@ -8720,10 +8720,10 @@
         <v>1</v>
       </c>
       <c r="G200" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H200" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I200" s="17">
         <v>2000</v>
@@ -8755,10 +8755,10 @@
         <v>1</v>
       </c>
       <c r="G201" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H201" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I201" s="13">
         <v>1500</v>
@@ -8790,10 +8790,10 @@
         <v>1</v>
       </c>
       <c r="G202" s="17">
-        <v>395</v>
+        <v>288</v>
       </c>
       <c r="H202" s="17">
-        <v>395</v>
+        <v>288</v>
       </c>
       <c r="I202" s="17">
         <v>2500</v>
@@ -8825,10 +8825,10 @@
         <v>1</v>
       </c>
       <c r="G203" s="13">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H203" s="13">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I203" s="13">
         <v>2000</v>
@@ -8860,10 +8860,10 @@
         <v>1</v>
       </c>
       <c r="G204" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H204" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I204" s="17">
         <v>1200</v>
@@ -8895,10 +8895,10 @@
         <v>1</v>
       </c>
       <c r="G205" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H205" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I205" s="13">
         <v>1500</v>
@@ -8930,10 +8930,10 @@
         <v>1</v>
       </c>
       <c r="G206" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H206" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I206" s="17">
         <v>1500</v>
@@ -8965,10 +8965,10 @@
         <v>1</v>
       </c>
       <c r="G207" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H207" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I207" s="13">
         <v>2000</v>
@@ -9000,10 +9000,10 @@
         <v>1</v>
       </c>
       <c r="G208" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H208" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I208" s="17">
         <v>1500</v>
@@ -9035,10 +9035,10 @@
         <v>1</v>
       </c>
       <c r="G209" s="13">
-        <v>399</v>
+        <v>300</v>
       </c>
       <c r="H209" s="13">
-        <v>399</v>
+        <v>300</v>
       </c>
       <c r="I209" s="13">
         <v>2500</v>
@@ -9070,10 +9070,10 @@
         <v>1</v>
       </c>
       <c r="G210" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H210" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I210" s="17">
         <v>1500</v>
@@ -9105,10 +9105,10 @@
         <v>1</v>
       </c>
       <c r="G211" s="13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H211" s="13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I211" s="13">
         <v>2000</v>
@@ -9140,10 +9140,10 @@
         <v>1</v>
       </c>
       <c r="G212" s="17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H212" s="17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I212" s="17">
         <v>1200</v>
@@ -9175,10 +9175,10 @@
         <v>1</v>
       </c>
       <c r="G213" s="13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H213" s="13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I213" s="13">
         <v>1500</v>
@@ -9210,10 +9210,10 @@
         <v>1</v>
       </c>
       <c r="G214" s="17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H214" s="17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I214" s="17">
         <v>1500</v>
@@ -9245,10 +9245,10 @@
         <v>1</v>
       </c>
       <c r="G215" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H215" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I215" s="13">
         <v>2000</v>
@@ -9280,10 +9280,10 @@
         <v>1</v>
       </c>
       <c r="G216" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H216" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I216" s="17">
         <v>1500</v>
@@ -9315,10 +9315,10 @@
         <v>1</v>
       </c>
       <c r="G217" s="13">
-        <v>444</v>
+        <v>322</v>
       </c>
       <c r="H217" s="13">
-        <v>444</v>
+        <v>322</v>
       </c>
       <c r="I217" s="13">
         <v>2500</v>
@@ -9350,10 +9350,10 @@
         <v>1</v>
       </c>
       <c r="G218" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H218" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I218" s="17">
         <v>2000</v>
@@ -9420,10 +9420,10 @@
         <v>1</v>
       </c>
       <c r="G220" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H220" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I220" s="17">
         <v>1500</v>
@@ -9455,10 +9455,10 @@
         <v>1</v>
       </c>
       <c r="G221" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H221" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I221" s="13">
         <v>1500</v>
@@ -9490,10 +9490,10 @@
         <v>1</v>
       </c>
       <c r="G222" s="17">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H222" s="17">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I222" s="17">
         <v>2000</v>
@@ -9525,10 +9525,10 @@
         <v>1</v>
       </c>
       <c r="G223" s="13">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H223" s="13">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I223" s="13">
         <v>1500</v>
@@ -9560,10 +9560,10 @@
         <v>1</v>
       </c>
       <c r="G224" s="17">
-        <v>452</v>
+        <v>349</v>
       </c>
       <c r="H224" s="17">
-        <v>452</v>
+        <v>349</v>
       </c>
       <c r="I224" s="17">
         <v>2500</v>
@@ -9595,10 +9595,10 @@
         <v>1</v>
       </c>
       <c r="G225" s="13">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H225" s="13">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I225" s="13">
         <v>2000</v>
@@ -9630,10 +9630,10 @@
         <v>1</v>
       </c>
       <c r="G226" s="17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H226" s="17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I226" s="17">
         <v>1200</v>
@@ -9665,10 +9665,10 @@
         <v>1</v>
       </c>
       <c r="G227" s="13">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H227" s="13">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I227" s="13">
         <v>1500</v>
@@ -9700,10 +9700,10 @@
         <v>1</v>
       </c>
       <c r="G228" s="17">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H228" s="17">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I228" s="17">
         <v>1500</v>
@@ -9735,10 +9735,10 @@
         <v>1</v>
       </c>
       <c r="G229" s="13">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H229" s="13">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I229" s="13">
         <v>2000</v>
@@ -9770,10 +9770,10 @@
         <v>1</v>
       </c>
       <c r="G230" s="17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H230" s="17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I230" s="17">
         <v>1500</v>
@@ -9805,10 +9805,10 @@
         <v>1</v>
       </c>
       <c r="G231" s="13">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="H231" s="13">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="I231" s="13">
         <v>2500</v>
@@ -9840,10 +9840,10 @@
         <v>1</v>
       </c>
       <c r="G232" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H232" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I232" s="17">
         <v>1500</v>
@@ -9875,10 +9875,10 @@
         <v>1</v>
       </c>
       <c r="G233" s="13">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H233" s="13">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I233" s="13">
         <v>2000</v>
@@ -9910,10 +9910,10 @@
         <v>1</v>
       </c>
       <c r="G234" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H234" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I234" s="17">
         <v>1200</v>
@@ -9945,10 +9945,10 @@
         <v>1</v>
       </c>
       <c r="G235" s="13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H235" s="13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I235" s="13">
         <v>1500</v>
@@ -9980,10 +9980,10 @@
         <v>1</v>
       </c>
       <c r="G236" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H236" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I236" s="17">
         <v>1500</v>
@@ -10015,10 +10015,10 @@
         <v>1</v>
       </c>
       <c r="G237" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H237" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I237" s="13">
         <v>2000</v>
@@ -10050,10 +10050,10 @@
         <v>1</v>
       </c>
       <c r="G238" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H238" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I238" s="17">
         <v>1500</v>
@@ -10085,10 +10085,10 @@
         <v>1</v>
       </c>
       <c r="G239" s="13">
-        <v>407</v>
+        <v>330</v>
       </c>
       <c r="H239" s="13">
-        <v>407</v>
+        <v>330</v>
       </c>
       <c r="I239" s="13">
         <v>2500</v>
@@ -10120,10 +10120,10 @@
         <v>1</v>
       </c>
       <c r="G240" s="17">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H240" s="17">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I240" s="17">
         <v>2000</v>
@@ -10155,10 +10155,10 @@
         <v>1</v>
       </c>
       <c r="G241" s="13">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H241" s="13">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I241" s="13">
         <v>1200</v>
@@ -10190,10 +10190,10 @@
         <v>1</v>
       </c>
       <c r="G242" s="17">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H242" s="17">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I242" s="17">
         <v>1500</v>
@@ -10225,10 +10225,10 @@
         <v>1</v>
       </c>
       <c r="G243" s="13">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H243" s="13">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I243" s="13">
         <v>1500</v>
@@ -10260,10 +10260,10 @@
         <v>1</v>
       </c>
       <c r="G244" s="17">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H244" s="17">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I244" s="17">
         <v>2000</v>
@@ -10295,10 +10295,10 @@
         <v>1</v>
       </c>
       <c r="G245" s="13">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="H245" s="13">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I245" s="13">
         <v>1500</v>
@@ -10330,10 +10330,10 @@
         <v>1</v>
       </c>
       <c r="G246" s="17">
-        <v>383</v>
+        <v>312</v>
       </c>
       <c r="H246" s="17">
-        <v>383</v>
+        <v>312</v>
       </c>
       <c r="I246" s="17">
         <v>2500</v>
@@ -10365,10 +10365,10 @@
         <v>1</v>
       </c>
       <c r="G247" s="13">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H247" s="13">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I247" s="13">
         <v>2000</v>
@@ -10400,10 +10400,10 @@
         <v>1</v>
       </c>
       <c r="G248" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H248" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I248" s="17">
         <v>1200</v>
@@ -10435,10 +10435,10 @@
         <v>1</v>
       </c>
       <c r="G249" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I249" s="13">
         <v>1500</v>
@@ -10505,10 +10505,10 @@
         <v>1</v>
       </c>
       <c r="G251" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H251" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I251" s="13">
         <v>2000</v>
@@ -10540,10 +10540,10 @@
         <v>1</v>
       </c>
       <c r="G252" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H252" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I252" s="17">
         <v>1500</v>
@@ -10575,10 +10575,10 @@
         <v>1</v>
       </c>
       <c r="G253" s="13">
-        <v>390</v>
+        <v>296</v>
       </c>
       <c r="H253" s="13">
-        <v>390</v>
+        <v>296</v>
       </c>
       <c r="I253" s="13">
         <v>2500</v>
@@ -10610,10 +10610,10 @@
         <v>1</v>
       </c>
       <c r="G254" s="17">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H254" s="17">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I254" s="17">
         <v>1500</v>
@@ -10645,10 +10645,10 @@
         <v>1</v>
       </c>
       <c r="G255" s="13">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H255" s="13">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I255" s="13">
         <v>2000</v>
@@ -10680,10 +10680,10 @@
         <v>1</v>
       </c>
       <c r="G256" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H256" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I256" s="17">
         <v>1200</v>
@@ -10715,10 +10715,10 @@
         <v>1</v>
       </c>
       <c r="G257" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H257" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I257" s="13">
         <v>1500</v>
@@ -10750,10 +10750,10 @@
         <v>1</v>
       </c>
       <c r="G258" s="17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H258" s="17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I258" s="17">
         <v>1500</v>
@@ -10785,10 +10785,10 @@
         <v>1</v>
       </c>
       <c r="G259" s="13">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H259" s="13">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I259" s="13">
         <v>2000</v>
@@ -10820,10 +10820,10 @@
         <v>1</v>
       </c>
       <c r="G260" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H260" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I260" s="17">
         <v>1500</v>
@@ -10855,10 +10855,10 @@
         <v>1</v>
       </c>
       <c r="G261" s="13">
-        <v>356</v>
+        <v>274</v>
       </c>
       <c r="H261" s="13">
-        <v>356</v>
+        <v>274</v>
       </c>
       <c r="I261" s="13">
         <v>2500</v>
@@ -10890,10 +10890,10 @@
         <v>1</v>
       </c>
       <c r="G262" s="17">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H262" s="17">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="I262" s="17">
         <v>2000</v>
@@ -10925,10 +10925,10 @@
         <v>1</v>
       </c>
       <c r="G263" s="13">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H263" s="13">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I263" s="13">
         <v>1200</v>
@@ -10960,10 +10960,10 @@
         <v>1</v>
       </c>
       <c r="G264" s="17">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H264" s="17">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I264" s="17">
         <v>1500</v>
@@ -10995,10 +10995,10 @@
         <v>1</v>
       </c>
       <c r="G265" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H265" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I265" s="13">
         <v>1500</v>
@@ -11030,10 +11030,10 @@
         <v>1</v>
       </c>
       <c r="G266" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H266" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I266" s="17">
         <v>2000</v>
@@ -11065,10 +11065,10 @@
         <v>1</v>
       </c>
       <c r="G267" s="13">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H267" s="13">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I267" s="13">
         <v>1500</v>
@@ -11100,10 +11100,10 @@
         <v>1</v>
       </c>
       <c r="G268" s="17">
-        <v>328</v>
+        <v>253</v>
       </c>
       <c r="H268" s="17">
-        <v>328</v>
+        <v>253</v>
       </c>
       <c r="I268" s="17">
         <v>2500</v>
@@ -11135,10 +11135,10 @@
         <v>1</v>
       </c>
       <c r="G269" s="13">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H269" s="13">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I269" s="13">
         <v>2000</v>
@@ -11170,10 +11170,10 @@
         <v>1</v>
       </c>
       <c r="G270" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H270" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I270" s="17">
         <v>1200</v>
@@ -11205,10 +11205,10 @@
         <v>1</v>
       </c>
       <c r="G271" s="13">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I271" s="13">
         <v>1500</v>
@@ -11240,10 +11240,10 @@
         <v>1</v>
       </c>
       <c r="G272" s="17">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H272" s="17">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I272" s="17">
         <v>1500</v>
@@ -11275,10 +11275,10 @@
         <v>1</v>
       </c>
       <c r="G273" s="13">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H273" s="13">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I273" s="13">
         <v>2000</v>
@@ -11310,10 +11310,10 @@
         <v>1</v>
       </c>
       <c r="G274" s="17">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H274" s="17">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I274" s="17">
         <v>1500</v>
@@ -11345,10 +11345,10 @@
         <v>1</v>
       </c>
       <c r="G275" s="13">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="H275" s="13">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="I275" s="13">
         <v>2500</v>
@@ -11380,10 +11380,10 @@
         <v>1</v>
       </c>
       <c r="G276" s="17">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H276" s="17">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I276" s="17">
         <v>1500</v>
@@ -11415,10 +11415,10 @@
         <v>1</v>
       </c>
       <c r="G277" s="13">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H277" s="13">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I277" s="13">
         <v>2000</v>
@@ -11450,10 +11450,10 @@
         <v>1</v>
       </c>
       <c r="G278" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H278" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I278" s="17">
         <v>1200</v>
@@ -11485,10 +11485,10 @@
         <v>1</v>
       </c>
       <c r="G279" s="13">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H279" s="13">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I279" s="13">
         <v>1500</v>
@@ -11520,10 +11520,10 @@
         <v>1</v>
       </c>
       <c r="G280" s="17">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H280" s="17">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I280" s="17">
         <v>1500</v>
@@ -11555,10 +11555,10 @@
         <v>1</v>
       </c>
       <c r="G281" s="13">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H281" s="13">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I281" s="13">
         <v>2000</v>
@@ -11590,10 +11590,10 @@
         <v>1</v>
       </c>
       <c r="G282" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H282" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I282" s="17">
         <v>1500</v>
@@ -11625,10 +11625,10 @@
         <v>1</v>
       </c>
       <c r="G283" s="13">
-        <v>226</v>
+        <v>179</v>
       </c>
       <c r="H283" s="13">
-        <v>226</v>
+        <v>179</v>
       </c>
       <c r="I283" s="13">
         <v>2500</v>
@@ -11660,10 +11660,10 @@
         <v>1</v>
       </c>
       <c r="G284" s="17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H284" s="17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I284" s="17">
         <v>2000</v>
@@ -11730,10 +11730,10 @@
         <v>1</v>
       </c>
       <c r="G286" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H286" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I286" s="17">
         <v>1500</v>
@@ -11765,10 +11765,10 @@
         <v>1</v>
       </c>
       <c r="G287" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H287" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I287" s="13">
         <v>1500</v>
@@ -11800,10 +11800,10 @@
         <v>1</v>
       </c>
       <c r="G288" s="17">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="H288" s="17">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I288" s="17">
         <v>2000</v>
@@ -11835,10 +11835,10 @@
         <v>1</v>
       </c>
       <c r="G289" s="13">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I289" s="13">
         <v>1500</v>
@@ -11870,10 +11870,10 @@
         <v>1</v>
       </c>
       <c r="G290" s="17">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="H290" s="17">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="I290" s="17">
         <v>2500</v>
@@ -11905,10 +11905,10 @@
         <v>1</v>
       </c>
       <c r="G291" s="13">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H291" s="13">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I291" s="13">
         <v>2000</v>
@@ -11940,10 +11940,10 @@
         <v>1</v>
       </c>
       <c r="G292" s="17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H292" s="17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I292" s="17">
         <v>1200</v>
@@ -11975,10 +11975,10 @@
         <v>1</v>
       </c>
       <c r="G293" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H293" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I293" s="13">
         <v>1500</v>
@@ -12010,10 +12010,10 @@
         <v>1</v>
       </c>
       <c r="G294" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H294" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I294" s="17">
         <v>1500</v>
@@ -12045,10 +12045,10 @@
         <v>1</v>
       </c>
       <c r="G295" s="13">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H295" s="13">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I295" s="13">
         <v>2000</v>
@@ -12080,10 +12080,10 @@
         <v>1</v>
       </c>
       <c r="G296" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H296" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I296" s="17">
         <v>1500</v>
@@ -12115,10 +12115,10 @@
         <v>1</v>
       </c>
       <c r="G297" s="13">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="H297" s="13">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I297" s="13">
         <v>2500</v>
@@ -12150,10 +12150,10 @@
         <v>1</v>
       </c>
       <c r="G298" s="17">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H298" s="17">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I298" s="17">
         <v>1500</v>
@@ -12185,10 +12185,10 @@
         <v>1</v>
       </c>
       <c r="G299" s="13">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H299" s="13">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="I299" s="13">
         <v>2000</v>
@@ -12220,10 +12220,10 @@
         <v>1</v>
       </c>
       <c r="G300" s="17">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H300" s="17">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I300" s="17">
         <v>1200</v>
@@ -12255,10 +12255,10 @@
         <v>1</v>
       </c>
       <c r="G301" s="13">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I301" s="13">
         <v>1500</v>
@@ -12290,10 +12290,10 @@
         <v>1</v>
       </c>
       <c r="G302" s="17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H302" s="17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I302" s="17">
         <v>2000</v>
@@ -12322,13 +12322,13 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F303" s="13">
-        <v>2420</v>
+        <v>3033</v>
       </c>
       <c r="G303" s="13">
-        <v>166.3</v>
+        <v>132.6</v>
       </c>
       <c r="H303" s="13">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="I303" s="13">
         <v>3000</v>
@@ -12357,13 +12357,13 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F304" s="17">
-        <v>2420</v>
+        <v>3033</v>
       </c>
       <c r="G304" s="17">
-        <v>732.2</v>
+        <v>606.2</v>
       </c>
       <c r="H304" s="17">
-        <v>732</v>
+        <v>606</v>
       </c>
       <c r="I304" s="17">
         <v>3000</v>
@@ -12392,7 +12392,7 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F305" s="13">
-        <v>2420</v>
+        <v>3033</v>
       </c>
       <c r="G305" s="13">
         <v>0</v>
@@ -12473,7 +12473,7 @@
         <v>HTML shell response under cold load</v>
       </c>
       <c r="C5" s="33" t="str">
-        <v>33 / 100</v>
+        <v>27 / 100</v>
       </c>
       <c r="D5" s="34" t="str">
         <v>PARTIAL COMPLIANCE — Review</v>
@@ -12487,7 +12487,7 @@
         <v>p95 latency across the static asset surface</v>
       </c>
       <c r="C6" s="31" t="str">
-        <v>24 / 100</v>
+        <v>20 / 100</v>
       </c>
       <c r="D6" s="34" t="str">
         <v>PARTIAL COMPLIANCE — Review</v>
@@ -12529,7 +12529,7 @@
         <v>JavaScript bundle delivery latency</v>
       </c>
       <c r="C9" s="33" t="str">
-        <v>23 / 100</v>
+        <v>17 / 100</v>
       </c>
       <c r="D9" s="34" t="str">
         <v>PARTIAL COMPLIANCE — Review</v>
@@ -12605,7 +12605,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B4" s="5">
-        <v>20.27</v>
+        <v>20.21</v>
       </c>
       <c r="D4" s="13" t="str">
         <v>&lt; 50 ms</v>
@@ -12616,7 +12616,7 @@
         <v>Requests</v>
       </c>
       <c r="B5" s="5">
-        <v>2420</v>
+        <v>3033</v>
       </c>
       <c r="D5" s="17" t="str">
         <v>50–100 ms</v>
@@ -12627,7 +12627,7 @@
         <v>Throughput (req/s)</v>
       </c>
       <c r="B6" s="5">
-        <v>119.36</v>
+        <v>150.04</v>
       </c>
       <c r="D6" s="13" t="str">
         <v>100–200 ms</v>
@@ -12638,7 +12638,7 @@
         <v>Data transfer (Mbps)</v>
       </c>
       <c r="B7" s="5">
-        <v>784.44</v>
+        <v>988.51</v>
       </c>
       <c r="D7" s="17" t="str">
         <v>200–500 ms</v>
@@ -12649,7 +12649,7 @@
         <v>Average latency (ms)</v>
       </c>
       <c r="B8" s="5">
-        <v>166.3</v>
+        <v>132.6</v>
       </c>
       <c r="D8" s="13" t="str">
         <v>500–1000 ms</v>
@@ -12660,7 +12660,7 @@
         <v>p50 latency (ms)</v>
       </c>
       <c r="B9" s="5">
-        <v>41.8</v>
+        <v>31.2</v>
       </c>
       <c r="D9" s="17" t="str">
         <v>&gt; 1000 ms</v>
@@ -12671,7 +12671,7 @@
         <v>p95 latency (ms)</v>
       </c>
       <c r="B10" s="5">
-        <v>732.2</v>
+        <v>606.2</v>
       </c>
     </row>
     <row r="11">
@@ -12679,7 +12679,7 @@
         <v>p99 latency (ms)</v>
       </c>
       <c r="B11" s="5">
-        <v>815.7</v>
+        <v>643.9</v>
       </c>
     </row>
     <row r="12">
@@ -12687,7 +12687,7 @@
         <v>Max latency (ms)</v>
       </c>
       <c r="B12" s="5">
-        <v>983.2</v>
+        <v>680.3</v>
       </c>
     </row>
     <row r="13">
@@ -12775,7 +12775,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B8" s="13" t="str">
-        <v>40364632137</v>
+        <v>40364866245</v>
       </c>
     </row>
     <row r="9">
@@ -12799,7 +12799,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B11" s="17" t="str">
-        <v>581c970</v>
+        <v>0548411</v>
       </c>
     </row>
     <row r="12">
@@ -12807,7 +12807,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B12" s="13" t="str">
-        <v>2026-10-26T17:01:33.005Z</v>
+        <v>2026-10-26T17:02:59.584Z</v>
       </c>
     </row>
     <row r="13">
@@ -12815,7 +12815,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B13" s="17" t="str">
-        <v>2026-10-26T17:01:55.633Z</v>
+        <v>2026-10-26T17:03:21.753Z</v>
       </c>
     </row>
     <row r="14">
@@ -12847,7 +12847,7 @@
         <v>Sustained duration (s)</v>
       </c>
       <c r="B17" s="17">
-        <v>20.27</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="18">

--- a/reports/Load_Test_Analysis_Report.xlsx
+++ b/reports/Load_Test_Analysis_Report.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -220,14 +220,8 @@
       <name val="Calibri"/>
       <b/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <b/>
-      <color rgb="9C0006"/>
-    </font>
   </fonts>
-  <fills count="32">
+  <fills count="31">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -412,14 +406,8 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="31">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -854,26 +842,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="B4C6E7"/>
-      </left>
-      <right style="thin">
-        <color rgb="B4C6E7"/>
-      </right>
-      <top style="thin">
-        <color rgb="B4C6E7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="B4C6E7"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -969,9 +942,6 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -1325,7 +1295,7 @@
         <v>Test Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:02:59</v>
+        <v>26/10/2026, 17:05:25</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Status:</v>
@@ -1635,13 +1605,13 @@
         <v>Sustained phase duration (s)</v>
       </c>
       <c r="B23" s="5">
-        <v>20.21</v>
+        <v>20.29</v>
       </c>
       <c r="D23" s="13" t="str">
         <v>Throughput (req/s)</v>
       </c>
       <c r="E23" s="13" t="str">
-        <v>150.04 (≥ 5)</v>
+        <v>119.18 (≥ 5)</v>
       </c>
       <c r="F23" s="25" t="str">
         <v>PASS</v>
@@ -1652,13 +1622,13 @@
         <v>Total HTTP requests</v>
       </c>
       <c r="B24" s="5">
-        <v>3033</v>
+        <v>2418</v>
       </c>
       <c r="D24" s="17" t="str">
         <v>p95 latency (ms)</v>
       </c>
       <c r="E24" s="17" t="str">
-        <v>606.2 (≤ 3000)</v>
+        <v>730.4 (≤ 3000)</v>
       </c>
       <c r="F24" s="25" t="str">
         <v>PASS</v>
@@ -1669,7 +1639,7 @@
         <v>Throughput (req/s)</v>
       </c>
       <c r="B25" s="5">
-        <v>150.04</v>
+        <v>119.18</v>
       </c>
       <c r="D25" s="13" t="str">
         <v>Error rate (%)</v>
@@ -1686,7 +1656,7 @@
         <v>Average latency (ms)</v>
       </c>
       <c r="B26" s="5">
-        <v>132.6</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="27">
@@ -1694,7 +1664,7 @@
         <v>p95 latency (ms)</v>
       </c>
       <c r="B27" s="5">
-        <v>606.2</v>
+        <v>730.4</v>
       </c>
     </row>
     <row r="28">
@@ -1702,7 +1672,7 @@
         <v>p99 latency (ms)</v>
       </c>
       <c r="B28" s="5">
-        <v>643.9</v>
+        <v>793.9</v>
       </c>
     </row>
     <row r="29">
@@ -1718,7 +1688,7 @@
         <v>Data transferred (MB)</v>
       </c>
       <c r="B30" s="5">
-        <v>2497.7</v>
+        <v>1985.5</v>
       </c>
     </row>
   </sheetData>
@@ -1825,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="13">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H3" s="13">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I3" s="13">
         <v>1500</v>
@@ -1860,10 +1830,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="17">
-        <v>465</v>
+        <v>577</v>
       </c>
       <c r="H4" s="17">
-        <v>465</v>
+        <v>577</v>
       </c>
       <c r="I4" s="17">
         <v>2500</v>
@@ -1895,10 +1865,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="13">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H5" s="13">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="I5" s="13">
         <v>2000</v>
@@ -1930,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H6" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I6" s="17">
         <v>1200</v>
@@ -1965,10 +1935,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="13">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H7" s="13">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="I7" s="13">
         <v>1500</v>
@@ -2000,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="17">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H8" s="17">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I8" s="17">
         <v>1500</v>
@@ -2035,10 +2005,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="13">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H9" s="13">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I9" s="13">
         <v>2000</v>
@@ -2070,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="17">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H10" s="17">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I10" s="17">
         <v>1500</v>
@@ -2105,10 +2075,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="13">
-        <v>454</v>
+        <v>579</v>
       </c>
       <c r="H11" s="13">
-        <v>454</v>
+        <v>579</v>
       </c>
       <c r="I11" s="13">
         <v>2500</v>
@@ -2140,10 +2110,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="17">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H12" s="17">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I12" s="17">
         <v>1500</v>
@@ -2175,10 +2145,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="13">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="H13" s="13">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I13" s="13">
         <v>2000</v>
@@ -2210,10 +2180,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="17">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H14" s="17">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I14" s="17">
         <v>1200</v>
@@ -2245,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="13">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="H15" s="13">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I15" s="13">
         <v>1500</v>
@@ -2280,10 +2250,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="17">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H16" s="17">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I16" s="17">
         <v>1500</v>
@@ -2315,10 +2285,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="13">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H17" s="13">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I17" s="13">
         <v>2000</v>
@@ -2350,10 +2320,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="17">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="H18" s="17">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I18" s="17">
         <v>1500</v>
@@ -2385,10 +2355,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="13">
-        <v>412</v>
+        <v>542</v>
       </c>
       <c r="H19" s="13">
-        <v>412</v>
+        <v>542</v>
       </c>
       <c r="I19" s="13">
         <v>2500</v>
@@ -2420,10 +2390,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="17">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="H20" s="17">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="I20" s="17">
         <v>2000</v>
@@ -2455,10 +2425,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="13">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H21" s="13">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="I21" s="13">
         <v>1200</v>
@@ -2490,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="17">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H22" s="17">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="I22" s="17">
         <v>1500</v>
@@ -2525,10 +2495,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="13">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="H23" s="13">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I23" s="13">
         <v>1500</v>
@@ -2560,10 +2530,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H24" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I24" s="17">
         <v>2000</v>
@@ -2595,10 +2565,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="13">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H25" s="13">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I25" s="13">
         <v>1500</v>
@@ -2630,10 +2600,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="17">
-        <v>429</v>
+        <v>583</v>
       </c>
       <c r="H26" s="17">
-        <v>429</v>
+        <v>583</v>
       </c>
       <c r="I26" s="17">
         <v>2500</v>
@@ -2665,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="13">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H27" s="13">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I27" s="13">
         <v>2000</v>
@@ -2700,10 +2670,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="17">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H28" s="17">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I28" s="17">
         <v>1200</v>
@@ -2735,10 +2705,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="13">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H29" s="13">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I29" s="13">
         <v>1500</v>
@@ -2770,10 +2740,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="17">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H30" s="17">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I30" s="17">
         <v>1500</v>
@@ -2805,10 +2775,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="13">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H31" s="13">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I31" s="13">
         <v>2000</v>
@@ -2840,10 +2810,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="17">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H32" s="17">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I32" s="17">
         <v>1500</v>
@@ -2875,10 +2845,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="13">
-        <v>435</v>
+        <v>559</v>
       </c>
       <c r="H33" s="13">
-        <v>435</v>
+        <v>559</v>
       </c>
       <c r="I33" s="13">
         <v>2500</v>
@@ -2910,10 +2880,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="17">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="H34" s="17">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I34" s="17">
         <v>1500</v>
@@ -2945,10 +2915,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="13">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="H35" s="13">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="I35" s="13">
         <v>2000</v>
@@ -2980,10 +2950,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H36" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I36" s="17">
         <v>1200</v>
@@ -3015,10 +2985,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="13">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H37" s="13">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I37" s="13">
         <v>1500</v>
@@ -3050,10 +3020,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="17">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H38" s="17">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I38" s="17">
         <v>1500</v>
@@ -3120,10 +3090,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H40" s="17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I40" s="17">
         <v>1500</v>
@@ -3155,10 +3125,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="13">
-        <v>415</v>
+        <v>547</v>
       </c>
       <c r="H41" s="13">
-        <v>415</v>
+        <v>547</v>
       </c>
       <c r="I41" s="13">
         <v>2500</v>
@@ -3190,10 +3160,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="17">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="H42" s="17">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="I42" s="17">
         <v>2000</v>
@@ -3225,10 +3195,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="13">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H43" s="13">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I43" s="13">
         <v>1200</v>
@@ -3260,10 +3230,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="17">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H44" s="17">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I44" s="17">
         <v>1500</v>
@@ -3295,10 +3265,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="13">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H45" s="13">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I45" s="13">
         <v>1500</v>
@@ -3330,10 +3300,10 @@
         <v>1</v>
       </c>
       <c r="G46" s="17">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H46" s="17">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I46" s="17">
         <v>2000</v>
@@ -3365,10 +3335,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="13">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H47" s="13">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I47" s="13">
         <v>1500</v>
@@ -3400,10 +3370,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="17">
-        <v>399</v>
+        <v>550</v>
       </c>
       <c r="H48" s="17">
-        <v>399</v>
+        <v>550</v>
       </c>
       <c r="I48" s="17">
         <v>2500</v>
@@ -3435,10 +3405,10 @@
         <v>1</v>
       </c>
       <c r="G49" s="13">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H49" s="13">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I49" s="13">
         <v>2000</v>
@@ -3470,10 +3440,10 @@
         <v>1</v>
       </c>
       <c r="G50" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H50" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I50" s="17">
         <v>1200</v>
@@ -3505,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H51" s="13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I51" s="13">
         <v>1500</v>
@@ -3540,10 +3510,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H52" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I52" s="17">
         <v>1500</v>
@@ -3575,10 +3545,10 @@
         <v>1</v>
       </c>
       <c r="G53" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H53" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I53" s="13">
         <v>2000</v>
@@ -3610,10 +3580,10 @@
         <v>1</v>
       </c>
       <c r="G54" s="17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H54" s="17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I54" s="17">
         <v>1500</v>
@@ -3645,10 +3615,10 @@
         <v>1</v>
       </c>
       <c r="G55" s="13">
-        <v>410</v>
+        <v>545</v>
       </c>
       <c r="H55" s="13">
-        <v>410</v>
+        <v>545</v>
       </c>
       <c r="I55" s="13">
         <v>2500</v>
@@ -3680,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="G56" s="17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H56" s="17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I56" s="17">
         <v>1500</v>
@@ -3715,10 +3685,10 @@
         <v>1</v>
       </c>
       <c r="G57" s="13">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H57" s="13">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I57" s="13">
         <v>2000</v>
@@ -3750,10 +3720,10 @@
         <v>1</v>
       </c>
       <c r="G58" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H58" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I58" s="17">
         <v>1200</v>
@@ -3785,10 +3755,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H59" s="13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I59" s="13">
         <v>1500</v>
@@ -3820,10 +3790,10 @@
         <v>1</v>
       </c>
       <c r="G60" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H60" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I60" s="17">
         <v>1500</v>
@@ -3855,10 +3825,10 @@
         <v>1</v>
       </c>
       <c r="G61" s="13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H61" s="13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I61" s="13">
         <v>2000</v>
@@ -3890,10 +3860,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="17">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H62" s="17">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I62" s="17">
         <v>1500</v>
@@ -3925,10 +3895,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="13">
-        <v>396</v>
+        <v>517</v>
       </c>
       <c r="H63" s="13">
-        <v>396</v>
+        <v>517</v>
       </c>
       <c r="I63" s="13">
         <v>2500</v>
@@ -3960,10 +3930,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="17">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="H64" s="17">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I64" s="17">
         <v>2000</v>
@@ -3995,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="13">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H65" s="13">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I65" s="13">
         <v>1200</v>
@@ -4030,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="17">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H66" s="17">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I66" s="17">
         <v>1500</v>
@@ -4065,10 +4035,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="13">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H67" s="13">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I67" s="13">
         <v>1500</v>
@@ -4100,10 +4070,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H68" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I68" s="17">
         <v>2000</v>
@@ -4135,10 +4105,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="13">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H69" s="13">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I69" s="13">
         <v>1500</v>
@@ -4170,10 +4140,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="17">
-        <v>373</v>
+        <v>505</v>
       </c>
       <c r="H70" s="17">
-        <v>373</v>
+        <v>505</v>
       </c>
       <c r="I70" s="17">
         <v>2500</v>
@@ -4205,10 +4175,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="13">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H71" s="13">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I71" s="13">
         <v>2000</v>
@@ -4240,10 +4210,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="17">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H72" s="17">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I72" s="17">
         <v>1200</v>
@@ -4275,10 +4245,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H73" s="13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I73" s="13">
         <v>1500</v>
@@ -4310,10 +4280,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H74" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I74" s="17">
         <v>1500</v>
@@ -4345,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="G75" s="13">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H75" s="13">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="I75" s="13">
         <v>2000</v>
@@ -4380,10 +4350,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="17">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H76" s="17">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="I76" s="17">
         <v>1500</v>
@@ -4415,10 +4385,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="13">
-        <v>384</v>
+        <v>479</v>
       </c>
       <c r="H77" s="13">
-        <v>384</v>
+        <v>479</v>
       </c>
       <c r="I77" s="13">
         <v>2500</v>
@@ -4450,10 +4420,10 @@
         <v>1</v>
       </c>
       <c r="G78" s="17">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H78" s="17">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I78" s="17">
         <v>1500</v>
@@ -4485,10 +4455,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="13">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H79" s="13">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I79" s="13">
         <v>2000</v>
@@ -4520,10 +4490,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H80" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I80" s="17">
         <v>1200</v>
@@ -4555,10 +4525,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H81" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I81" s="13">
         <v>1500</v>
@@ -4590,10 +4560,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="17">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H82" s="17">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I82" s="17">
         <v>1500</v>
@@ -4625,10 +4595,10 @@
         <v>1</v>
       </c>
       <c r="G83" s="13">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H83" s="13">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I83" s="13">
         <v>2000</v>
@@ -4660,10 +4630,10 @@
         <v>1</v>
       </c>
       <c r="G84" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H84" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I84" s="17">
         <v>1500</v>
@@ -4695,10 +4665,10 @@
         <v>1</v>
       </c>
       <c r="G85" s="13">
-        <v>383</v>
+        <v>445</v>
       </c>
       <c r="H85" s="13">
-        <v>383</v>
+        <v>445</v>
       </c>
       <c r="I85" s="13">
         <v>2500</v>
@@ -4730,10 +4700,10 @@
         <v>1</v>
       </c>
       <c r="G86" s="17">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H86" s="17">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I86" s="17">
         <v>2000</v>
@@ -4765,10 +4735,10 @@
         <v>1</v>
       </c>
       <c r="G87" s="13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H87" s="13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I87" s="13">
         <v>1200</v>
@@ -4800,10 +4770,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="17">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H88" s="17">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I88" s="17">
         <v>1500</v>
@@ -4905,10 +4875,10 @@
         <v>1</v>
       </c>
       <c r="G91" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H91" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I91" s="13">
         <v>1500</v>
@@ -4940,10 +4910,10 @@
         <v>1</v>
       </c>
       <c r="G92" s="17">
-        <v>378</v>
+        <v>459</v>
       </c>
       <c r="H92" s="17">
-        <v>378</v>
+        <v>459</v>
       </c>
       <c r="I92" s="17">
         <v>2500</v>
@@ -4975,10 +4945,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="13">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H93" s="13">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I93" s="13">
         <v>2000</v>
@@ -5010,10 +4980,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="17">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H94" s="17">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I94" s="17">
         <v>1200</v>
@@ -5045,10 +5015,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H95" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I95" s="13">
         <v>1500</v>
@@ -5080,10 +5050,10 @@
         <v>1</v>
       </c>
       <c r="G96" s="17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H96" s="17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I96" s="17">
         <v>1500</v>
@@ -5115,10 +5085,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H97" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I97" s="13">
         <v>2000</v>
@@ -5150,10 +5120,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H98" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I98" s="17">
         <v>1500</v>
@@ -5185,10 +5155,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="13">
-        <v>390</v>
+        <v>469</v>
       </c>
       <c r="H99" s="13">
-        <v>390</v>
+        <v>469</v>
       </c>
       <c r="I99" s="13">
         <v>2500</v>
@@ -5220,10 +5190,10 @@
         <v>1</v>
       </c>
       <c r="G100" s="17">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H100" s="17">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I100" s="17">
         <v>1500</v>
@@ -5255,10 +5225,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="13">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H101" s="13">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I101" s="13">
         <v>2000</v>
@@ -5290,10 +5260,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H102" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I102" s="17">
         <v>1200</v>
@@ -5325,10 +5295,10 @@
         <v>1</v>
       </c>
       <c r="G103" s="13">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H103" s="13">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I103" s="13">
         <v>1500</v>
@@ -5395,10 +5365,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="13">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H105" s="13">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I105" s="13">
         <v>2000</v>
@@ -5430,10 +5400,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H106" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I106" s="17">
         <v>1500</v>
@@ -5465,10 +5435,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="13">
-        <v>384</v>
+        <v>497</v>
       </c>
       <c r="H107" s="13">
-        <v>384</v>
+        <v>497</v>
       </c>
       <c r="I107" s="13">
         <v>2500</v>
@@ -5500,10 +5470,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="17">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H108" s="17">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I108" s="17">
         <v>2000</v>
@@ -5535,10 +5505,10 @@
         <v>1</v>
       </c>
       <c r="G109" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H109" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I109" s="13">
         <v>1200</v>
@@ -5570,10 +5540,10 @@
         <v>1</v>
       </c>
       <c r="G110" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H110" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I110" s="17">
         <v>1500</v>
@@ -5605,10 +5575,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="13">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H111" s="13">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I111" s="13">
         <v>1500</v>
@@ -5675,10 +5645,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H113" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I113" s="13">
         <v>1500</v>
@@ -5710,10 +5680,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="17">
-        <v>355</v>
+        <v>492</v>
       </c>
       <c r="H114" s="17">
-        <v>355</v>
+        <v>492</v>
       </c>
       <c r="I114" s="17">
         <v>2500</v>
@@ -5745,10 +5715,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="13">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H115" s="13">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I115" s="13">
         <v>2000</v>
@@ -5780,10 +5750,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H116" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I116" s="17">
         <v>1200</v>
@@ -5815,10 +5785,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H117" s="13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I117" s="13">
         <v>1500</v>
@@ -5850,10 +5820,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="17">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H118" s="17">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I118" s="17">
         <v>1500</v>
@@ -5885,10 +5855,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H119" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I119" s="13">
         <v>2000</v>
@@ -5920,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H120" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I120" s="17">
         <v>1500</v>
@@ -5955,10 +5925,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="13">
-        <v>396</v>
+        <v>507</v>
       </c>
       <c r="H121" s="13">
-        <v>396</v>
+        <v>507</v>
       </c>
       <c r="I121" s="13">
         <v>2500</v>
@@ -5990,10 +5960,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="17">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H122" s="17">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I122" s="17">
         <v>1500</v>
@@ -6025,10 +5995,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="13">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H123" s="13">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I123" s="13">
         <v>2000</v>
@@ -6060,10 +6030,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="17">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H124" s="17">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I124" s="17">
         <v>1200</v>
@@ -6095,10 +6065,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H125" s="13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I125" s="13">
         <v>1500</v>
@@ -6130,10 +6100,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H126" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I126" s="17">
         <v>1500</v>
@@ -6200,10 +6170,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="17">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H128" s="17">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I128" s="17">
         <v>1500</v>
@@ -6235,10 +6205,10 @@
         <v>1</v>
       </c>
       <c r="G129" s="13">
-        <v>405</v>
+        <v>477</v>
       </c>
       <c r="H129" s="13">
-        <v>405</v>
+        <v>477</v>
       </c>
       <c r="I129" s="13">
         <v>2500</v>
@@ -6270,10 +6240,10 @@
         <v>1</v>
       </c>
       <c r="G130" s="17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H130" s="17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I130" s="17">
         <v>2000</v>
@@ -6305,10 +6275,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I131" s="13">
         <v>1200</v>
@@ -6340,10 +6310,10 @@
         <v>1</v>
       </c>
       <c r="G132" s="17">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H132" s="17">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I132" s="17">
         <v>1500</v>
@@ -6375,10 +6345,10 @@
         <v>1</v>
       </c>
       <c r="G133" s="13">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H133" s="13">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I133" s="13">
         <v>1500</v>
@@ -6410,10 +6380,10 @@
         <v>1</v>
       </c>
       <c r="G134" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H134" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I134" s="17">
         <v>2000</v>
@@ -6445,10 +6415,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H135" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I135" s="13">
         <v>1500</v>
@@ -6480,10 +6450,10 @@
         <v>1</v>
       </c>
       <c r="G136" s="17">
-        <v>391</v>
+        <v>475</v>
       </c>
       <c r="H136" s="17">
-        <v>391</v>
+        <v>475</v>
       </c>
       <c r="I136" s="17">
         <v>2500</v>
@@ -6515,10 +6485,10 @@
         <v>1</v>
       </c>
       <c r="G137" s="13">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H137" s="13">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I137" s="13">
         <v>2000</v>
@@ -6550,10 +6520,10 @@
         <v>1</v>
       </c>
       <c r="G138" s="17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H138" s="17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I138" s="17">
         <v>1200</v>
@@ -6585,10 +6555,10 @@
         <v>1</v>
       </c>
       <c r="G139" s="13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H139" s="13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I139" s="13">
         <v>1500</v>
@@ -6620,10 +6590,10 @@
         <v>1</v>
       </c>
       <c r="G140" s="17">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H140" s="17">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I140" s="17">
         <v>1500</v>
@@ -6655,10 +6625,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="13">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H141" s="13">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I141" s="13">
         <v>2000</v>
@@ -6690,10 +6660,10 @@
         <v>1</v>
       </c>
       <c r="G142" s="17">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H142" s="17">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I142" s="17">
         <v>1500</v>
@@ -6725,10 +6695,10 @@
         <v>1</v>
       </c>
       <c r="G143" s="13">
-        <v>367</v>
+        <v>457</v>
       </c>
       <c r="H143" s="13">
-        <v>367</v>
+        <v>457</v>
       </c>
       <c r="I143" s="13">
         <v>2500</v>
@@ -6830,10 +6800,10 @@
         <v>1</v>
       </c>
       <c r="G146" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H146" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I146" s="17">
         <v>1200</v>
@@ -6865,10 +6835,10 @@
         <v>1</v>
       </c>
       <c r="G147" s="13">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H147" s="13">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I147" s="13">
         <v>1500</v>
@@ -6900,10 +6870,10 @@
         <v>1</v>
       </c>
       <c r="G148" s="17">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H148" s="17">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I148" s="17">
         <v>1500</v>
@@ -6935,10 +6905,10 @@
         <v>1</v>
       </c>
       <c r="G149" s="13">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H149" s="13">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I149" s="13">
         <v>2000</v>
@@ -6970,10 +6940,10 @@
         <v>1</v>
       </c>
       <c r="G150" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H150" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I150" s="17">
         <v>1500</v>
@@ -7005,10 +6975,10 @@
         <v>1</v>
       </c>
       <c r="G151" s="13">
-        <v>355</v>
+        <v>443</v>
       </c>
       <c r="H151" s="13">
-        <v>355</v>
+        <v>443</v>
       </c>
       <c r="I151" s="13">
         <v>2500</v>
@@ -7040,10 +7010,10 @@
         <v>1</v>
       </c>
       <c r="G152" s="17">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H152" s="17">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I152" s="17">
         <v>2000</v>
@@ -7075,10 +7045,10 @@
         <v>1</v>
       </c>
       <c r="G153" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H153" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I153" s="13">
         <v>1200</v>
@@ -7110,10 +7080,10 @@
         <v>1</v>
       </c>
       <c r="G154" s="17">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H154" s="17">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I154" s="17">
         <v>1500</v>
@@ -7145,10 +7115,10 @@
         <v>1</v>
       </c>
       <c r="G155" s="13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H155" s="13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I155" s="13">
         <v>1500</v>
@@ -7180,10 +7150,10 @@
         <v>1</v>
       </c>
       <c r="G156" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H156" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I156" s="17">
         <v>2000</v>
@@ -7215,10 +7185,10 @@
         <v>1</v>
       </c>
       <c r="G157" s="13">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H157" s="13">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I157" s="13">
         <v>1500</v>
@@ -7250,10 +7220,10 @@
         <v>1</v>
       </c>
       <c r="G158" s="17">
-        <v>324</v>
+        <v>434</v>
       </c>
       <c r="H158" s="17">
-        <v>324</v>
+        <v>434</v>
       </c>
       <c r="I158" s="17">
         <v>2500</v>
@@ -7285,10 +7255,10 @@
         <v>1</v>
       </c>
       <c r="G159" s="13">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H159" s="13">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I159" s="13">
         <v>2000</v>
@@ -7320,10 +7290,10 @@
         <v>1</v>
       </c>
       <c r="G160" s="17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H160" s="17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I160" s="17">
         <v>1200</v>
@@ -7355,10 +7325,10 @@
         <v>1</v>
       </c>
       <c r="G161" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H161" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I161" s="13">
         <v>1500</v>
@@ -7390,10 +7360,10 @@
         <v>1</v>
       </c>
       <c r="G162" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H162" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I162" s="17">
         <v>1500</v>
@@ -7425,10 +7395,10 @@
         <v>1</v>
       </c>
       <c r="G163" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H163" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I163" s="13">
         <v>2000</v>
@@ -7495,10 +7465,10 @@
         <v>1</v>
       </c>
       <c r="G165" s="13">
-        <v>318</v>
+        <v>407</v>
       </c>
       <c r="H165" s="13">
-        <v>318</v>
+        <v>407</v>
       </c>
       <c r="I165" s="13">
         <v>2500</v>
@@ -7530,10 +7500,10 @@
         <v>1</v>
       </c>
       <c r="G166" s="17">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H166" s="17">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I166" s="17">
         <v>1500</v>
@@ -7565,10 +7535,10 @@
         <v>1</v>
       </c>
       <c r="G167" s="13">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H167" s="13">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I167" s="13">
         <v>2000</v>
@@ -7600,10 +7570,10 @@
         <v>1</v>
       </c>
       <c r="G168" s="17">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H168" s="17">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I168" s="17">
         <v>1200</v>
@@ -7635,10 +7605,10 @@
         <v>1</v>
       </c>
       <c r="G169" s="13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I169" s="13">
         <v>1500</v>
@@ -7670,10 +7640,10 @@
         <v>1</v>
       </c>
       <c r="G170" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H170" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I170" s="17">
         <v>1500</v>
@@ -7705,10 +7675,10 @@
         <v>1</v>
       </c>
       <c r="G171" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H171" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I171" s="13">
         <v>2000</v>
@@ -7740,10 +7710,10 @@
         <v>1</v>
       </c>
       <c r="G172" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H172" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I172" s="17">
         <v>1500</v>
@@ -7775,10 +7745,10 @@
         <v>1</v>
       </c>
       <c r="G173" s="13">
-        <v>292</v>
+        <v>413</v>
       </c>
       <c r="H173" s="13">
-        <v>292</v>
+        <v>413</v>
       </c>
       <c r="I173" s="13">
         <v>2500</v>
@@ -7810,10 +7780,10 @@
         <v>1</v>
       </c>
       <c r="G174" s="17">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H174" s="17">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I174" s="17">
         <v>2000</v>
@@ -7845,10 +7815,10 @@
         <v>1</v>
       </c>
       <c r="G175" s="13">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H175" s="13">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I175" s="13">
         <v>1200</v>
@@ -7880,10 +7850,10 @@
         <v>1</v>
       </c>
       <c r="G176" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H176" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I176" s="17">
         <v>1500</v>
@@ -7915,10 +7885,10 @@
         <v>1</v>
       </c>
       <c r="G177" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H177" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I177" s="13">
         <v>1500</v>
@@ -7950,10 +7920,10 @@
         <v>1</v>
       </c>
       <c r="G178" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H178" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I178" s="17">
         <v>2000</v>
@@ -7985,10 +7955,10 @@
         <v>1</v>
       </c>
       <c r="G179" s="13">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H179" s="13">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I179" s="13">
         <v>1500</v>
@@ -8020,10 +7990,10 @@
         <v>1</v>
       </c>
       <c r="G180" s="17">
-        <v>285</v>
+        <v>420</v>
       </c>
       <c r="H180" s="17">
-        <v>285</v>
+        <v>420</v>
       </c>
       <c r="I180" s="17">
         <v>2500</v>
@@ -8055,10 +8025,10 @@
         <v>1</v>
       </c>
       <c r="G181" s="13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H181" s="13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I181" s="13">
         <v>2000</v>
@@ -8090,10 +8060,10 @@
         <v>1</v>
       </c>
       <c r="G182" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H182" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I182" s="17">
         <v>1200</v>
@@ -8125,10 +8095,10 @@
         <v>1</v>
       </c>
       <c r="G183" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H183" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I183" s="13">
         <v>1500</v>
@@ -8195,10 +8165,10 @@
         <v>1</v>
       </c>
       <c r="G185" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H185" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I185" s="13">
         <v>2000</v>
@@ -8230,10 +8200,10 @@
         <v>1</v>
       </c>
       <c r="G186" s="17">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H186" s="17">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="I186" s="17">
         <v>1500</v>
@@ -8265,10 +8235,10 @@
         <v>1</v>
       </c>
       <c r="G187" s="13">
-        <v>278</v>
+        <v>403</v>
       </c>
       <c r="H187" s="13">
-        <v>278</v>
+        <v>403</v>
       </c>
       <c r="I187" s="13">
         <v>2500</v>
@@ -8300,10 +8270,10 @@
         <v>1</v>
       </c>
       <c r="G188" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H188" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I188" s="17">
         <v>1500</v>
@@ -8335,10 +8305,10 @@
         <v>1</v>
       </c>
       <c r="G189" s="13">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="H189" s="13">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I189" s="13">
         <v>2000</v>
@@ -8370,10 +8340,10 @@
         <v>1</v>
       </c>
       <c r="G190" s="17">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H190" s="17">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I190" s="17">
         <v>1200</v>
@@ -8405,10 +8375,10 @@
         <v>1</v>
       </c>
       <c r="G191" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H191" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I191" s="13">
         <v>1500</v>
@@ -8440,10 +8410,10 @@
         <v>1</v>
       </c>
       <c r="G192" s="17">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H192" s="17">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I192" s="17">
         <v>1500</v>
@@ -8475,10 +8445,10 @@
         <v>1</v>
       </c>
       <c r="G193" s="13">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H193" s="13">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I193" s="13">
         <v>2000</v>
@@ -8510,10 +8480,10 @@
         <v>1</v>
       </c>
       <c r="G194" s="17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H194" s="17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I194" s="17">
         <v>1500</v>
@@ -8545,10 +8515,10 @@
         <v>1</v>
       </c>
       <c r="G195" s="13">
-        <v>293</v>
+        <v>400</v>
       </c>
       <c r="H195" s="13">
-        <v>293</v>
+        <v>400</v>
       </c>
       <c r="I195" s="13">
         <v>2500</v>
@@ -8580,10 +8550,10 @@
         <v>1</v>
       </c>
       <c r="G196" s="17">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H196" s="17">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I196" s="17">
         <v>2000</v>
@@ -8615,10 +8585,10 @@
         <v>1</v>
       </c>
       <c r="G197" s="13">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H197" s="13">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I197" s="13">
         <v>1200</v>
@@ -8650,10 +8620,10 @@
         <v>1</v>
       </c>
       <c r="G198" s="17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H198" s="17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I198" s="17">
         <v>1500</v>
@@ -8685,10 +8655,10 @@
         <v>1</v>
       </c>
       <c r="G199" s="13">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H199" s="13">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I199" s="13">
         <v>1500</v>
@@ -8720,10 +8690,10 @@
         <v>1</v>
       </c>
       <c r="G200" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H200" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I200" s="17">
         <v>2000</v>
@@ -8755,10 +8725,10 @@
         <v>1</v>
       </c>
       <c r="G201" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H201" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I201" s="13">
         <v>1500</v>
@@ -8790,10 +8760,10 @@
         <v>1</v>
       </c>
       <c r="G202" s="17">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="H202" s="17">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="I202" s="17">
         <v>2500</v>
@@ -8825,10 +8795,10 @@
         <v>1</v>
       </c>
       <c r="G203" s="13">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H203" s="13">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I203" s="13">
         <v>2000</v>
@@ -8860,10 +8830,10 @@
         <v>1</v>
       </c>
       <c r="G204" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H204" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I204" s="17">
         <v>1200</v>
@@ -8895,10 +8865,10 @@
         <v>1</v>
       </c>
       <c r="G205" s="13">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H205" s="13">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I205" s="13">
         <v>1500</v>
@@ -8930,10 +8900,10 @@
         <v>1</v>
       </c>
       <c r="G206" s="17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H206" s="17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I206" s="17">
         <v>1500</v>
@@ -8965,10 +8935,10 @@
         <v>1</v>
       </c>
       <c r="G207" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H207" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I207" s="13">
         <v>2000</v>
@@ -9000,10 +8970,10 @@
         <v>1</v>
       </c>
       <c r="G208" s="17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H208" s="17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I208" s="17">
         <v>1500</v>
@@ -9035,10 +9005,10 @@
         <v>1</v>
       </c>
       <c r="G209" s="13">
-        <v>300</v>
+        <v>379</v>
       </c>
       <c r="H209" s="13">
-        <v>300</v>
+        <v>379</v>
       </c>
       <c r="I209" s="13">
         <v>2500</v>
@@ -9070,10 +9040,10 @@
         <v>1</v>
       </c>
       <c r="G210" s="17">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H210" s="17">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I210" s="17">
         <v>1500</v>
@@ -9105,10 +9075,10 @@
         <v>1</v>
       </c>
       <c r="G211" s="13">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H211" s="13">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I211" s="13">
         <v>2000</v>
@@ -9140,10 +9110,10 @@
         <v>1</v>
       </c>
       <c r="G212" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H212" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I212" s="17">
         <v>1200</v>
@@ -9175,10 +9145,10 @@
         <v>1</v>
       </c>
       <c r="G213" s="13">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H213" s="13">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I213" s="13">
         <v>1500</v>
@@ -9245,10 +9215,10 @@
         <v>1</v>
       </c>
       <c r="G215" s="13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H215" s="13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I215" s="13">
         <v>2000</v>
@@ -9280,10 +9250,10 @@
         <v>1</v>
       </c>
       <c r="G216" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H216" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I216" s="17">
         <v>1500</v>
@@ -9315,10 +9285,10 @@
         <v>1</v>
       </c>
       <c r="G217" s="13">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="H217" s="13">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="I217" s="13">
         <v>2500</v>
@@ -9350,10 +9320,10 @@
         <v>1</v>
       </c>
       <c r="G218" s="17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H218" s="17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I218" s="17">
         <v>2000</v>
@@ -9385,10 +9355,10 @@
         <v>1</v>
       </c>
       <c r="G219" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H219" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I219" s="13">
         <v>1200</v>
@@ -9420,10 +9390,10 @@
         <v>1</v>
       </c>
       <c r="G220" s="17">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H220" s="17">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I220" s="17">
         <v>1500</v>
@@ -9455,10 +9425,10 @@
         <v>1</v>
       </c>
       <c r="G221" s="13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H221" s="13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I221" s="13">
         <v>1500</v>
@@ -9490,10 +9460,10 @@
         <v>1</v>
       </c>
       <c r="G222" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H222" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I222" s="17">
         <v>2000</v>
@@ -9525,10 +9495,10 @@
         <v>1</v>
       </c>
       <c r="G223" s="13">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H223" s="13">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I223" s="13">
         <v>1500</v>
@@ -9560,10 +9530,10 @@
         <v>1</v>
       </c>
       <c r="G224" s="17">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="H224" s="17">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="I224" s="17">
         <v>2500</v>
@@ -9595,10 +9565,10 @@
         <v>1</v>
       </c>
       <c r="G225" s="13">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H225" s="13">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I225" s="13">
         <v>2000</v>
@@ -9630,10 +9600,10 @@
         <v>1</v>
       </c>
       <c r="G226" s="17">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H226" s="17">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I226" s="17">
         <v>1200</v>
@@ -9665,10 +9635,10 @@
         <v>1</v>
       </c>
       <c r="G227" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H227" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I227" s="13">
         <v>1500</v>
@@ -9700,10 +9670,10 @@
         <v>1</v>
       </c>
       <c r="G228" s="17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H228" s="17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I228" s="17">
         <v>1500</v>
@@ -9735,10 +9705,10 @@
         <v>1</v>
       </c>
       <c r="G229" s="13">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H229" s="13">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I229" s="13">
         <v>2000</v>
@@ -9770,10 +9740,10 @@
         <v>1</v>
       </c>
       <c r="G230" s="17">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H230" s="17">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I230" s="17">
         <v>1500</v>
@@ -9805,10 +9775,10 @@
         <v>1</v>
       </c>
       <c r="G231" s="13">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="H231" s="13">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="I231" s="13">
         <v>2500</v>
@@ -9840,10 +9810,10 @@
         <v>1</v>
       </c>
       <c r="G232" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H232" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I232" s="17">
         <v>1500</v>
@@ -9875,10 +9845,10 @@
         <v>1</v>
       </c>
       <c r="G233" s="13">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="H233" s="13">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="I233" s="13">
         <v>2000</v>
@@ -9910,10 +9880,10 @@
         <v>1</v>
       </c>
       <c r="G234" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H234" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I234" s="17">
         <v>1200</v>
@@ -9945,10 +9915,10 @@
         <v>1</v>
       </c>
       <c r="G235" s="13">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H235" s="13">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I235" s="13">
         <v>1500</v>
@@ -9980,10 +9950,10 @@
         <v>1</v>
       </c>
       <c r="G236" s="17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H236" s="17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I236" s="17">
         <v>1500</v>
@@ -10015,10 +9985,10 @@
         <v>1</v>
       </c>
       <c r="G237" s="13">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H237" s="13">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I237" s="13">
         <v>2000</v>
@@ -10050,10 +10020,10 @@
         <v>1</v>
       </c>
       <c r="G238" s="17">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H238" s="17">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I238" s="17">
         <v>1500</v>
@@ -10085,10 +10055,10 @@
         <v>1</v>
       </c>
       <c r="G239" s="13">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="H239" s="13">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="I239" s="13">
         <v>2500</v>
@@ -10120,10 +10090,10 @@
         <v>1</v>
       </c>
       <c r="G240" s="17">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H240" s="17">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I240" s="17">
         <v>2000</v>
@@ -10155,10 +10125,10 @@
         <v>1</v>
       </c>
       <c r="G241" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H241" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I241" s="13">
         <v>1200</v>
@@ -10190,10 +10160,10 @@
         <v>1</v>
       </c>
       <c r="G242" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H242" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I242" s="17">
         <v>1500</v>
@@ -10225,10 +10195,10 @@
         <v>1</v>
       </c>
       <c r="G243" s="13">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H243" s="13">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I243" s="13">
         <v>1500</v>
@@ -10260,10 +10230,10 @@
         <v>1</v>
       </c>
       <c r="G244" s="17">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H244" s="17">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I244" s="17">
         <v>2000</v>
@@ -10295,10 +10265,10 @@
         <v>1</v>
       </c>
       <c r="G245" s="13">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H245" s="13">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I245" s="13">
         <v>1500</v>
@@ -10330,10 +10300,10 @@
         <v>1</v>
       </c>
       <c r="G246" s="17">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="H246" s="17">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="I246" s="17">
         <v>2500</v>
@@ -10365,10 +10335,10 @@
         <v>1</v>
       </c>
       <c r="G247" s="13">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H247" s="13">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I247" s="13">
         <v>2000</v>
@@ -10400,10 +10370,10 @@
         <v>1</v>
       </c>
       <c r="G248" s="17">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H248" s="17">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I248" s="17">
         <v>1200</v>
@@ -10435,10 +10405,10 @@
         <v>1</v>
       </c>
       <c r="G249" s="13">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H249" s="13">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I249" s="13">
         <v>1500</v>
@@ -10470,10 +10440,10 @@
         <v>1</v>
       </c>
       <c r="G250" s="17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H250" s="17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I250" s="17">
         <v>1500</v>
@@ -10505,10 +10475,10 @@
         <v>1</v>
       </c>
       <c r="G251" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H251" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I251" s="13">
         <v>2000</v>
@@ -10540,10 +10510,10 @@
         <v>1</v>
       </c>
       <c r="G252" s="17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H252" s="17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I252" s="17">
         <v>1500</v>
@@ -10575,10 +10545,10 @@
         <v>1</v>
       </c>
       <c r="G253" s="13">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="H253" s="13">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="I253" s="13">
         <v>2500</v>
@@ -10610,10 +10580,10 @@
         <v>1</v>
       </c>
       <c r="G254" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H254" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I254" s="17">
         <v>1500</v>
@@ -10645,10 +10615,10 @@
         <v>1</v>
       </c>
       <c r="G255" s="13">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H255" s="13">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I255" s="13">
         <v>2000</v>
@@ -10715,10 +10685,10 @@
         <v>1</v>
       </c>
       <c r="G257" s="13">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H257" s="13">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I257" s="13">
         <v>1500</v>
@@ -10750,10 +10720,10 @@
         <v>1</v>
       </c>
       <c r="G258" s="17">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H258" s="17">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I258" s="17">
         <v>1500</v>
@@ -10785,10 +10755,10 @@
         <v>1</v>
       </c>
       <c r="G259" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H259" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I259" s="13">
         <v>2000</v>
@@ -10820,10 +10790,10 @@
         <v>1</v>
       </c>
       <c r="G260" s="17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H260" s="17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I260" s="17">
         <v>1500</v>
@@ -10855,10 +10825,10 @@
         <v>1</v>
       </c>
       <c r="G261" s="13">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="H261" s="13">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="I261" s="13">
         <v>2500</v>
@@ -10890,10 +10860,10 @@
         <v>1</v>
       </c>
       <c r="G262" s="17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H262" s="17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I262" s="17">
         <v>2000</v>
@@ -10960,10 +10930,10 @@
         <v>1</v>
       </c>
       <c r="G264" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H264" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I264" s="17">
         <v>1500</v>
@@ -10995,10 +10965,10 @@
         <v>1</v>
       </c>
       <c r="G265" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I265" s="13">
         <v>1500</v>
@@ -11030,10 +11000,10 @@
         <v>1</v>
       </c>
       <c r="G266" s="17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H266" s="17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I266" s="17">
         <v>2000</v>
@@ -11065,10 +11035,10 @@
         <v>1</v>
       </c>
       <c r="G267" s="13">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H267" s="13">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I267" s="13">
         <v>1500</v>
@@ -11100,10 +11070,10 @@
         <v>1</v>
       </c>
       <c r="G268" s="17">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="H268" s="17">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="I268" s="17">
         <v>2500</v>
@@ -11170,10 +11140,10 @@
         <v>1</v>
       </c>
       <c r="G270" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H270" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I270" s="17">
         <v>1200</v>
@@ -11205,10 +11175,10 @@
         <v>1</v>
       </c>
       <c r="G271" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H271" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I271" s="13">
         <v>1500</v>
@@ -11240,10 +11210,10 @@
         <v>1</v>
       </c>
       <c r="G272" s="17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H272" s="17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I272" s="17">
         <v>1500</v>
@@ -11275,10 +11245,10 @@
         <v>1</v>
       </c>
       <c r="G273" s="13">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H273" s="13">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I273" s="13">
         <v>2000</v>
@@ -11310,10 +11280,10 @@
         <v>1</v>
       </c>
       <c r="G274" s="17">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H274" s="17">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I274" s="17">
         <v>1500</v>
@@ -11345,10 +11315,10 @@
         <v>1</v>
       </c>
       <c r="G275" s="13">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="H275" s="13">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="I275" s="13">
         <v>2500</v>
@@ -11380,10 +11350,10 @@
         <v>1</v>
       </c>
       <c r="G276" s="17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H276" s="17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I276" s="17">
         <v>1500</v>
@@ -11415,10 +11385,10 @@
         <v>1</v>
       </c>
       <c r="G277" s="13">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H277" s="13">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I277" s="13">
         <v>2000</v>
@@ -11450,10 +11420,10 @@
         <v>1</v>
       </c>
       <c r="G278" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H278" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I278" s="17">
         <v>1200</v>
@@ -11485,10 +11455,10 @@
         <v>1</v>
       </c>
       <c r="G279" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H279" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I279" s="13">
         <v>1500</v>
@@ -11520,10 +11490,10 @@
         <v>1</v>
       </c>
       <c r="G280" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H280" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I280" s="17">
         <v>1500</v>
@@ -11555,10 +11525,10 @@
         <v>1</v>
       </c>
       <c r="G281" s="13">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H281" s="13">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I281" s="13">
         <v>2000</v>
@@ -11590,10 +11560,10 @@
         <v>1</v>
       </c>
       <c r="G282" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H282" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I282" s="17">
         <v>1500</v>
@@ -11625,10 +11595,10 @@
         <v>1</v>
       </c>
       <c r="G283" s="13">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="H283" s="13">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="I283" s="13">
         <v>2500</v>
@@ -11660,10 +11630,10 @@
         <v>1</v>
       </c>
       <c r="G284" s="17">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="H284" s="17">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="I284" s="17">
         <v>2000</v>
@@ -11695,10 +11665,10 @@
         <v>1</v>
       </c>
       <c r="G285" s="13">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H285" s="13">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I285" s="13">
         <v>1200</v>
@@ -11730,10 +11700,10 @@
         <v>1</v>
       </c>
       <c r="G286" s="17">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H286" s="17">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I286" s="17">
         <v>1500</v>
@@ -11765,10 +11735,10 @@
         <v>1</v>
       </c>
       <c r="G287" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H287" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I287" s="13">
         <v>1500</v>
@@ -11800,10 +11770,10 @@
         <v>1</v>
       </c>
       <c r="G288" s="17">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H288" s="17">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I288" s="17">
         <v>2000</v>
@@ -11835,10 +11805,10 @@
         <v>1</v>
       </c>
       <c r="G289" s="13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H289" s="13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I289" s="13">
         <v>1500</v>
@@ -11870,10 +11840,10 @@
         <v>1</v>
       </c>
       <c r="G290" s="17">
-        <v>167</v>
+        <v>211</v>
       </c>
       <c r="H290" s="17">
-        <v>167</v>
+        <v>211</v>
       </c>
       <c r="I290" s="17">
         <v>2500</v>
@@ -11905,10 +11875,10 @@
         <v>1</v>
       </c>
       <c r="G291" s="13">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H291" s="13">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I291" s="13">
         <v>2000</v>
@@ -11940,10 +11910,10 @@
         <v>1</v>
       </c>
       <c r="G292" s="17">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H292" s="17">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I292" s="17">
         <v>1200</v>
@@ -11975,10 +11945,10 @@
         <v>1</v>
       </c>
       <c r="G293" s="13">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H293" s="13">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I293" s="13">
         <v>1500</v>
@@ -12010,10 +11980,10 @@
         <v>1</v>
       </c>
       <c r="G294" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H294" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I294" s="17">
         <v>1500</v>
@@ -12045,10 +12015,10 @@
         <v>1</v>
       </c>
       <c r="G295" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H295" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I295" s="13">
         <v>2000</v>
@@ -12080,10 +12050,10 @@
         <v>1</v>
       </c>
       <c r="G296" s="17">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H296" s="17">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I296" s="17">
         <v>1500</v>
@@ -12115,10 +12085,10 @@
         <v>1</v>
       </c>
       <c r="G297" s="13">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="H297" s="13">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="I297" s="13">
         <v>2500</v>
@@ -12150,10 +12120,10 @@
         <v>1</v>
       </c>
       <c r="G298" s="17">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H298" s="17">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I298" s="17">
         <v>1500</v>
@@ -12185,10 +12155,10 @@
         <v>1</v>
       </c>
       <c r="G299" s="13">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H299" s="13">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I299" s="13">
         <v>2000</v>
@@ -12255,10 +12225,10 @@
         <v>1</v>
       </c>
       <c r="G301" s="13">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H301" s="13">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I301" s="13">
         <v>1500</v>
@@ -12290,10 +12260,10 @@
         <v>1</v>
       </c>
       <c r="G302" s="17">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H302" s="17">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I302" s="17">
         <v>2000</v>
@@ -12322,13 +12292,13 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F303" s="13">
-        <v>3033</v>
+        <v>2418</v>
       </c>
       <c r="G303" s="13">
-        <v>132.6</v>
+        <v>166.5</v>
       </c>
       <c r="H303" s="13">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="I303" s="13">
         <v>3000</v>
@@ -12357,13 +12327,13 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F304" s="17">
-        <v>3033</v>
+        <v>2418</v>
       </c>
       <c r="G304" s="17">
-        <v>606.2</v>
+        <v>730.4</v>
       </c>
       <c r="H304" s="17">
-        <v>606</v>
+        <v>730</v>
       </c>
       <c r="I304" s="17">
         <v>3000</v>
@@ -12392,7 +12362,7 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F305" s="13">
-        <v>3033</v>
+        <v>2418</v>
       </c>
       <c r="G305" s="13">
         <v>0</v>
@@ -12473,10 +12443,10 @@
         <v>HTML shell response under cold load</v>
       </c>
       <c r="C5" s="33" t="str">
-        <v>27 / 100</v>
-      </c>
-      <c r="D5" s="34" t="str">
-        <v>PARTIAL COMPLIANCE — Review</v>
+        <v>100 / 100</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <v>FULL COMPLIANCE — Verified</v>
       </c>
     </row>
     <row r="6">
@@ -12487,10 +12457,10 @@
         <v>p95 latency across the static asset surface</v>
       </c>
       <c r="C6" s="31" t="str">
-        <v>20 / 100</v>
-      </c>
-      <c r="D6" s="34" t="str">
-        <v>PARTIAL COMPLIANCE — Review</v>
+        <v>100 / 100</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <v>FULL COMPLIANCE — Verified</v>
       </c>
     </row>
     <row r="7">
@@ -12529,10 +12499,10 @@
         <v>JavaScript bundle delivery latency</v>
       </c>
       <c r="C9" s="33" t="str">
-        <v>17 / 100</v>
-      </c>
-      <c r="D9" s="34" t="str">
-        <v>PARTIAL COMPLIANCE — Review</v>
+        <v>100 / 100</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <v>FULL COMPLIANCE — Verified</v>
       </c>
     </row>
     <row r="10">
@@ -12543,10 +12513,10 @@
         <v>Static asset cache / reload behaviour</v>
       </c>
       <c r="C10" s="31" t="str">
-        <v>3 / 100</v>
-      </c>
-      <c r="D10" s="34" t="str">
-        <v>PARTIAL COMPLIANCE — Review</v>
+        <v>100 / 100</v>
+      </c>
+      <c r="D10" s="7" t="str">
+        <v>FULL COMPLIANCE — Verified</v>
       </c>
     </row>
     <row r="11">
@@ -12605,7 +12575,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B4" s="5">
-        <v>20.21</v>
+        <v>20.29</v>
       </c>
       <c r="D4" s="13" t="str">
         <v>&lt; 50 ms</v>
@@ -12616,7 +12586,7 @@
         <v>Requests</v>
       </c>
       <c r="B5" s="5">
-        <v>3033</v>
+        <v>2418</v>
       </c>
       <c r="D5" s="17" t="str">
         <v>50–100 ms</v>
@@ -12627,7 +12597,7 @@
         <v>Throughput (req/s)</v>
       </c>
       <c r="B6" s="5">
-        <v>150.04</v>
+        <v>119.18</v>
       </c>
       <c r="D6" s="13" t="str">
         <v>100–200 ms</v>
@@ -12638,7 +12608,7 @@
         <v>Data transfer (Mbps)</v>
       </c>
       <c r="B7" s="5">
-        <v>988.51</v>
+        <v>782.92</v>
       </c>
       <c r="D7" s="17" t="str">
         <v>200–500 ms</v>
@@ -12649,7 +12619,7 @@
         <v>Average latency (ms)</v>
       </c>
       <c r="B8" s="5">
-        <v>132.6</v>
+        <v>166.5</v>
       </c>
       <c r="D8" s="13" t="str">
         <v>500–1000 ms</v>
@@ -12660,7 +12630,7 @@
         <v>p50 latency (ms)</v>
       </c>
       <c r="B9" s="5">
-        <v>31.2</v>
+        <v>43.8</v>
       </c>
       <c r="D9" s="17" t="str">
         <v>&gt; 1000 ms</v>
@@ -12671,7 +12641,7 @@
         <v>p95 latency (ms)</v>
       </c>
       <c r="B10" s="5">
-        <v>606.2</v>
+        <v>730.4</v>
       </c>
     </row>
     <row r="11">
@@ -12679,7 +12649,7 @@
         <v>p99 latency (ms)</v>
       </c>
       <c r="B11" s="5">
-        <v>643.9</v>
+        <v>793.9</v>
       </c>
     </row>
     <row r="12">
@@ -12687,7 +12657,7 @@
         <v>Max latency (ms)</v>
       </c>
       <c r="B12" s="5">
-        <v>680.3</v>
+        <v>984.9</v>
       </c>
     </row>
     <row r="13">
@@ -12775,7 +12745,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B8" s="13" t="str">
-        <v>40364866245</v>
+        <v>40365246274</v>
       </c>
     </row>
     <row r="9">
@@ -12799,7 +12769,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B11" s="17" t="str">
-        <v>0548411</v>
+        <v>8074ec1</v>
       </c>
     </row>
     <row r="12">
@@ -12807,7 +12777,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B12" s="13" t="str">
-        <v>2026-10-26T17:02:59.584Z</v>
+        <v>2026-10-26T17:05:25.957Z</v>
       </c>
     </row>
     <row r="13">
@@ -12815,7 +12785,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B13" s="17" t="str">
-        <v>2026-10-26T17:03:21.753Z</v>
+        <v>2026-10-26T17:05:48.650Z</v>
       </c>
     </row>
     <row r="14">
@@ -12847,7 +12817,7 @@
         <v>Sustained duration (s)</v>
       </c>
       <c r="B17" s="17">
-        <v>20.21</v>
+        <v>20.29</v>
       </c>
     </row>
     <row r="18">

--- a/reports/Load_Test_Analysis_Report.xlsx
+++ b/reports/Load_Test_Analysis_Report.xlsx
@@ -1295,7 +1295,7 @@
         <v>Test Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:05:25</v>
+        <v>26/10/2026, 17:13:56</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Status:</v>
@@ -1605,13 +1605,13 @@
         <v>Sustained phase duration (s)</v>
       </c>
       <c r="B23" s="5">
-        <v>20.29</v>
+        <v>20.32</v>
       </c>
       <c r="D23" s="13" t="str">
         <v>Throughput (req/s)</v>
       </c>
       <c r="E23" s="13" t="str">
-        <v>119.18 (≥ 5)</v>
+        <v>124.23 (≥ 5)</v>
       </c>
       <c r="F23" s="25" t="str">
         <v>PASS</v>
@@ -1622,13 +1622,13 @@
         <v>Total HTTP requests</v>
       </c>
       <c r="B24" s="5">
-        <v>2418</v>
+        <v>2525</v>
       </c>
       <c r="D24" s="17" t="str">
         <v>p95 latency (ms)</v>
       </c>
       <c r="E24" s="17" t="str">
-        <v>730.4 (≤ 3000)</v>
+        <v>720.8 (≤ 3000)</v>
       </c>
       <c r="F24" s="25" t="str">
         <v>PASS</v>
@@ -1639,7 +1639,7 @@
         <v>Throughput (req/s)</v>
       </c>
       <c r="B25" s="5">
-        <v>119.18</v>
+        <v>124.23</v>
       </c>
       <c r="D25" s="13" t="str">
         <v>Error rate (%)</v>
@@ -1656,7 +1656,7 @@
         <v>Average latency (ms)</v>
       </c>
       <c r="B26" s="5">
-        <v>166.5</v>
+        <v>159.9</v>
       </c>
     </row>
     <row r="27">
@@ -1664,7 +1664,7 @@
         <v>p95 latency (ms)</v>
       </c>
       <c r="B27" s="5">
-        <v>730.4</v>
+        <v>720.8</v>
       </c>
     </row>
     <row r="28">
@@ -1672,7 +1672,7 @@
         <v>p99 latency (ms)</v>
       </c>
       <c r="B28" s="5">
-        <v>793.9</v>
+        <v>775.2</v>
       </c>
     </row>
     <row r="29">
@@ -1688,7 +1688,7 @@
         <v>Data transferred (MB)</v>
       </c>
       <c r="B30" s="5">
-        <v>1985.5</v>
+        <v>2075</v>
       </c>
     </row>
   </sheetData>
@@ -1795,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="13">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="H3" s="13">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="I3" s="13">
         <v>1500</v>
@@ -1821,19 +1821,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D4" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E4" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F4" s="17">
         <v>1</v>
       </c>
       <c r="G4" s="17">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="H4" s="17">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="I4" s="17">
         <v>2500</v>
@@ -1865,10 +1865,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="13">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H5" s="13">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I5" s="13">
         <v>2000</v>
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H6" s="17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I6" s="17">
         <v>1200</v>
@@ -1935,10 +1935,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="13">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="H7" s="13">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="I7" s="13">
         <v>1500</v>
@@ -1970,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="17">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H8" s="17">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I8" s="17">
         <v>1500</v>
@@ -2005,10 +2005,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="13">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H9" s="13">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I9" s="13">
         <v>2000</v>
@@ -2040,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="17">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="H10" s="17">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I10" s="17">
         <v>1500</v>
@@ -2066,19 +2066,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D11" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E11" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F11" s="13">
         <v>1</v>
       </c>
       <c r="G11" s="13">
-        <v>579</v>
+        <v>675</v>
       </c>
       <c r="H11" s="13">
-        <v>579</v>
+        <v>675</v>
       </c>
       <c r="I11" s="13">
         <v>2500</v>
@@ -2110,10 +2110,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="17">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H12" s="17">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I12" s="17">
         <v>1500</v>
@@ -2145,10 +2145,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="13">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="H13" s="13">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="I13" s="13">
         <v>2000</v>
@@ -2215,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="13">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H15" s="13">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I15" s="13">
         <v>1500</v>
@@ -2250,10 +2250,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="17">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="H16" s="17">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="I16" s="17">
         <v>1500</v>
@@ -2285,10 +2285,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="13">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H17" s="13">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I17" s="13">
         <v>2000</v>
@@ -2320,10 +2320,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H18" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I18" s="17">
         <v>1500</v>
@@ -2346,19 +2346,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D19" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E19" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F19" s="13">
         <v>1</v>
       </c>
       <c r="G19" s="13">
-        <v>542</v>
+        <v>603</v>
       </c>
       <c r="H19" s="13">
-        <v>542</v>
+        <v>603</v>
       </c>
       <c r="I19" s="13">
         <v>2500</v>
@@ -2390,10 +2390,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="17">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H20" s="17">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="I20" s="17">
         <v>2000</v>
@@ -2425,10 +2425,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="13">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H21" s="13">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I21" s="13">
         <v>1200</v>
@@ -2460,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="17">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H22" s="17">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="I22" s="17">
         <v>1500</v>
@@ -2495,10 +2495,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="13">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H23" s="13">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I23" s="13">
         <v>1500</v>
@@ -2530,10 +2530,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="17">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H24" s="17">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I24" s="17">
         <v>2000</v>
@@ -2565,10 +2565,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="13">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H25" s="13">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I25" s="13">
         <v>1500</v>
@@ -2591,19 +2591,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D26" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E26" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F26" s="17">
         <v>1</v>
       </c>
       <c r="G26" s="17">
-        <v>583</v>
+        <v>486</v>
       </c>
       <c r="H26" s="17">
-        <v>583</v>
+        <v>486</v>
       </c>
       <c r="I26" s="17">
         <v>2500</v>
@@ -2635,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="13">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="H27" s="13">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I27" s="13">
         <v>2000</v>
@@ -2670,10 +2670,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="17">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H28" s="17">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I28" s="17">
         <v>1200</v>
@@ -2705,10 +2705,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="13">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H29" s="13">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I29" s="13">
         <v>1500</v>
@@ -2740,10 +2740,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H30" s="17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I30" s="17">
         <v>1500</v>
@@ -2775,10 +2775,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="13">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H31" s="13">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I31" s="13">
         <v>2000</v>
@@ -2810,10 +2810,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="17">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H32" s="17">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I32" s="17">
         <v>1500</v>
@@ -2836,19 +2836,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D33" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E33" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F33" s="13">
         <v>1</v>
       </c>
       <c r="G33" s="13">
-        <v>559</v>
+        <v>473</v>
       </c>
       <c r="H33" s="13">
-        <v>559</v>
+        <v>473</v>
       </c>
       <c r="I33" s="13">
         <v>2500</v>
@@ -2880,10 +2880,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="17">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H34" s="17">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I34" s="17">
         <v>1500</v>
@@ -2915,10 +2915,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="13">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H35" s="13">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I35" s="13">
         <v>2000</v>
@@ -2950,10 +2950,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H36" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I36" s="17">
         <v>1200</v>
@@ -2985,10 +2985,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="13">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H37" s="13">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I37" s="13">
         <v>1500</v>
@@ -3020,10 +3020,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H38" s="17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I38" s="17">
         <v>1500</v>
@@ -3055,10 +3055,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="13">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H39" s="13">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I39" s="13">
         <v>2000</v>
@@ -3090,10 +3090,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="17">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H40" s="17">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I40" s="17">
         <v>1500</v>
@@ -3116,19 +3116,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D41" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E41" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F41" s="13">
         <v>1</v>
       </c>
       <c r="G41" s="13">
-        <v>547</v>
+        <v>660</v>
       </c>
       <c r="H41" s="13">
-        <v>547</v>
+        <v>660</v>
       </c>
       <c r="I41" s="13">
         <v>2500</v>
@@ -3160,10 +3160,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H42" s="17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I42" s="17">
         <v>2000</v>
@@ -3195,10 +3195,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H43" s="13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I43" s="13">
         <v>1200</v>
@@ -3265,10 +3265,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="13">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H45" s="13">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I45" s="13">
         <v>1500</v>
@@ -3300,10 +3300,10 @@
         <v>1</v>
       </c>
       <c r="G46" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H46" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I46" s="17">
         <v>2000</v>
@@ -3335,10 +3335,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="13">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H47" s="13">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I47" s="13">
         <v>1500</v>
@@ -3361,19 +3361,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D48" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E48" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F48" s="17">
         <v>1</v>
       </c>
       <c r="G48" s="17">
-        <v>550</v>
+        <v>437</v>
       </c>
       <c r="H48" s="17">
-        <v>550</v>
+        <v>437</v>
       </c>
       <c r="I48" s="17">
         <v>2500</v>
@@ -3405,10 +3405,10 @@
         <v>1</v>
       </c>
       <c r="G49" s="13">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H49" s="13">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I49" s="13">
         <v>2000</v>
@@ -3440,10 +3440,10 @@
         <v>1</v>
       </c>
       <c r="G50" s="17">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H50" s="17">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I50" s="17">
         <v>1200</v>
@@ -3475,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="13">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H51" s="13">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I51" s="13">
         <v>1500</v>
@@ -3510,10 +3510,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="17">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H52" s="17">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I52" s="17">
         <v>1500</v>
@@ -3545,10 +3545,10 @@
         <v>1</v>
       </c>
       <c r="G53" s="13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H53" s="13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I53" s="13">
         <v>2000</v>
@@ -3580,10 +3580,10 @@
         <v>1</v>
       </c>
       <c r="G54" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H54" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I54" s="17">
         <v>1500</v>
@@ -3606,19 +3606,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D55" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E55" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F55" s="13">
         <v>1</v>
       </c>
       <c r="G55" s="13">
-        <v>545</v>
+        <v>439</v>
       </c>
       <c r="H55" s="13">
-        <v>545</v>
+        <v>439</v>
       </c>
       <c r="I55" s="13">
         <v>2500</v>
@@ -3650,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="G56" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H56" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I56" s="17">
         <v>1500</v>
@@ -3685,10 +3685,10 @@
         <v>1</v>
       </c>
       <c r="G57" s="13">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H57" s="13">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I57" s="13">
         <v>2000</v>
@@ -3720,10 +3720,10 @@
         <v>1</v>
       </c>
       <c r="G58" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H58" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I58" s="17">
         <v>1200</v>
@@ -3755,10 +3755,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H59" s="13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I59" s="13">
         <v>1500</v>
@@ -3825,10 +3825,10 @@
         <v>1</v>
       </c>
       <c r="G61" s="13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H61" s="13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I61" s="13">
         <v>2000</v>
@@ -3860,10 +3860,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="17">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H62" s="17">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I62" s="17">
         <v>1500</v>
@@ -3886,19 +3886,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D63" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E63" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F63" s="13">
         <v>1</v>
       </c>
       <c r="G63" s="13">
-        <v>517</v>
+        <v>416</v>
       </c>
       <c r="H63" s="13">
-        <v>517</v>
+        <v>416</v>
       </c>
       <c r="I63" s="13">
         <v>2500</v>
@@ -3930,10 +3930,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="17">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="H64" s="17">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I64" s="17">
         <v>2000</v>
@@ -3965,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H65" s="13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I65" s="13">
         <v>1200</v>
@@ -4000,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H66" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I66" s="17">
         <v>1500</v>
@@ -4035,10 +4035,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="13">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H67" s="13">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I67" s="13">
         <v>1500</v>
@@ -4070,10 +4070,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="17">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H68" s="17">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I68" s="17">
         <v>2000</v>
@@ -4105,10 +4105,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="13">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H69" s="13">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I69" s="13">
         <v>1500</v>
@@ -4131,19 +4131,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D70" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E70" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F70" s="17">
         <v>1</v>
       </c>
       <c r="G70" s="17">
-        <v>505</v>
+        <v>431</v>
       </c>
       <c r="H70" s="17">
-        <v>505</v>
+        <v>431</v>
       </c>
       <c r="I70" s="17">
         <v>2500</v>
@@ -4175,10 +4175,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="13">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H71" s="13">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I71" s="13">
         <v>2000</v>
@@ -4210,10 +4210,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="17">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H72" s="17">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I72" s="17">
         <v>1200</v>
@@ -4245,10 +4245,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H73" s="13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I73" s="13">
         <v>1500</v>
@@ -4280,10 +4280,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="17">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H74" s="17">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I74" s="17">
         <v>1500</v>
@@ -4315,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="G75" s="13">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H75" s="13">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="I75" s="13">
         <v>2000</v>
@@ -4350,10 +4350,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="17">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H76" s="17">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I76" s="17">
         <v>1500</v>
@@ -4376,10 +4376,10 @@
         <v>CAT-02</v>
       </c>
       <c r="D77" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E77" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F77" s="13">
         <v>1</v>
@@ -4420,10 +4420,10 @@
         <v>1</v>
       </c>
       <c r="G78" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H78" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I78" s="17">
         <v>1500</v>
@@ -4455,10 +4455,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="13">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H79" s="13">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I79" s="13">
         <v>2000</v>
@@ -4490,10 +4490,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H80" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I80" s="17">
         <v>1200</v>
@@ -4525,10 +4525,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H81" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I81" s="13">
         <v>1500</v>
@@ -4560,10 +4560,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H82" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I82" s="17">
         <v>1500</v>
@@ -4595,10 +4595,10 @@
         <v>1</v>
       </c>
       <c r="G83" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H83" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I83" s="13">
         <v>2000</v>
@@ -4630,10 +4630,10 @@
         <v>1</v>
       </c>
       <c r="G84" s="17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H84" s="17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I84" s="17">
         <v>1500</v>
@@ -4656,19 +4656,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D85" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E85" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F85" s="13">
         <v>1</v>
       </c>
       <c r="G85" s="13">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="H85" s="13">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="I85" s="13">
         <v>2500</v>
@@ -4700,10 +4700,10 @@
         <v>1</v>
       </c>
       <c r="G86" s="17">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H86" s="17">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I86" s="17">
         <v>2000</v>
@@ -4735,10 +4735,10 @@
         <v>1</v>
       </c>
       <c r="G87" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H87" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I87" s="13">
         <v>1200</v>
@@ -4770,10 +4770,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H88" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I88" s="17">
         <v>1500</v>
@@ -4805,10 +4805,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I89" s="13">
         <v>1500</v>
@@ -4875,10 +4875,10 @@
         <v>1</v>
       </c>
       <c r="G91" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H91" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I91" s="13">
         <v>1500</v>
@@ -4901,19 +4901,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D92" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E92" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F92" s="17">
         <v>1</v>
       </c>
       <c r="G92" s="17">
-        <v>459</v>
+        <v>495</v>
       </c>
       <c r="H92" s="17">
-        <v>459</v>
+        <v>495</v>
       </c>
       <c r="I92" s="17">
         <v>2500</v>
@@ -4945,10 +4945,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H93" s="13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I93" s="13">
         <v>2000</v>
@@ -4980,10 +4980,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H94" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I94" s="17">
         <v>1200</v>
@@ -5015,10 +5015,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H95" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I95" s="13">
         <v>1500</v>
@@ -5050,10 +5050,10 @@
         <v>1</v>
       </c>
       <c r="G96" s="17">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H96" s="17">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I96" s="17">
         <v>1500</v>
@@ -5085,10 +5085,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="13">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H97" s="13">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I97" s="13">
         <v>2000</v>
@@ -5120,10 +5120,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="17">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H98" s="17">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I98" s="17">
         <v>1500</v>
@@ -5146,19 +5146,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D99" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E99" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F99" s="13">
         <v>1</v>
       </c>
       <c r="G99" s="13">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="H99" s="13">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="I99" s="13">
         <v>2500</v>
@@ -5225,10 +5225,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="13">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H101" s="13">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I101" s="13">
         <v>2000</v>
@@ -5260,10 +5260,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H102" s="17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I102" s="17">
         <v>1200</v>
@@ -5295,10 +5295,10 @@
         <v>1</v>
       </c>
       <c r="G103" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H103" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I103" s="13">
         <v>1500</v>
@@ -5330,10 +5330,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H104" s="17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I104" s="17">
         <v>1500</v>
@@ -5365,10 +5365,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H105" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I105" s="13">
         <v>2000</v>
@@ -5400,10 +5400,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H106" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I106" s="17">
         <v>1500</v>
@@ -5426,19 +5426,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D107" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E107" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F107" s="13">
         <v>1</v>
       </c>
       <c r="G107" s="13">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="H107" s="13">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="I107" s="13">
         <v>2500</v>
@@ -5470,10 +5470,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="17">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H108" s="17">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I108" s="17">
         <v>2000</v>
@@ -5540,10 +5540,10 @@
         <v>1</v>
       </c>
       <c r="G110" s="17">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H110" s="17">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I110" s="17">
         <v>1500</v>
@@ -5575,10 +5575,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="13">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H111" s="13">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I111" s="13">
         <v>1500</v>
@@ -5610,10 +5610,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H112" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I112" s="17">
         <v>2000</v>
@@ -5645,10 +5645,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H113" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I113" s="13">
         <v>1500</v>
@@ -5671,19 +5671,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D114" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E114" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F114" s="17">
         <v>1</v>
       </c>
       <c r="G114" s="17">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="H114" s="17">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="I114" s="17">
         <v>2500</v>
@@ -5715,10 +5715,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="13">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H115" s="13">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I115" s="13">
         <v>2000</v>
@@ -5750,10 +5750,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H116" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I116" s="17">
         <v>1200</v>
@@ -5785,10 +5785,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="13">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H117" s="13">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I117" s="13">
         <v>1500</v>
@@ -5820,10 +5820,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H118" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I118" s="17">
         <v>1500</v>
@@ -5855,10 +5855,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H119" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I119" s="13">
         <v>2000</v>
@@ -5890,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H120" s="17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I120" s="17">
         <v>1500</v>
@@ -5916,19 +5916,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D121" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E121" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F121" s="13">
         <v>1</v>
       </c>
       <c r="G121" s="13">
-        <v>507</v>
+        <v>454</v>
       </c>
       <c r="H121" s="13">
-        <v>507</v>
+        <v>454</v>
       </c>
       <c r="I121" s="13">
         <v>2500</v>
@@ -5960,10 +5960,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H122" s="17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I122" s="17">
         <v>1500</v>
@@ -5995,10 +5995,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="13">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H123" s="13">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I123" s="13">
         <v>2000</v>
@@ -6030,10 +6030,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H124" s="17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I124" s="17">
         <v>1200</v>
@@ -6065,10 +6065,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="13">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H125" s="13">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I125" s="13">
         <v>1500</v>
@@ -6100,10 +6100,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="17">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H126" s="17">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I126" s="17">
         <v>1500</v>
@@ -6135,10 +6135,10 @@
         <v>1</v>
       </c>
       <c r="G127" s="13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H127" s="13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I127" s="13">
         <v>2000</v>
@@ -6170,10 +6170,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="17">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H128" s="17">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="I128" s="17">
         <v>1500</v>
@@ -6196,19 +6196,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D129" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E129" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F129" s="13">
         <v>1</v>
       </c>
       <c r="G129" s="13">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="H129" s="13">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="I129" s="13">
         <v>2500</v>
@@ -6240,10 +6240,10 @@
         <v>1</v>
       </c>
       <c r="G130" s="17">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H130" s="17">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I130" s="17">
         <v>2000</v>
@@ -6275,10 +6275,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H131" s="13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I131" s="13">
         <v>1200</v>
@@ -6310,10 +6310,10 @@
         <v>1</v>
       </c>
       <c r="G132" s="17">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H132" s="17">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I132" s="17">
         <v>1500</v>
@@ -6345,10 +6345,10 @@
         <v>1</v>
       </c>
       <c r="G133" s="13">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H133" s="13">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I133" s="13">
         <v>1500</v>
@@ -6380,10 +6380,10 @@
         <v>1</v>
       </c>
       <c r="G134" s="17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H134" s="17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I134" s="17">
         <v>2000</v>
@@ -6415,10 +6415,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="13">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H135" s="13">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I135" s="13">
         <v>1500</v>
@@ -6441,19 +6441,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D136" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E136" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F136" s="17">
         <v>1</v>
       </c>
       <c r="G136" s="17">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="H136" s="17">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="I136" s="17">
         <v>2500</v>
@@ -6485,10 +6485,10 @@
         <v>1</v>
       </c>
       <c r="G137" s="13">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H137" s="13">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I137" s="13">
         <v>2000</v>
@@ -6520,10 +6520,10 @@
         <v>1</v>
       </c>
       <c r="G138" s="17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H138" s="17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I138" s="17">
         <v>1200</v>
@@ -6555,10 +6555,10 @@
         <v>1</v>
       </c>
       <c r="G139" s="13">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H139" s="13">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I139" s="13">
         <v>1500</v>
@@ -6590,10 +6590,10 @@
         <v>1</v>
       </c>
       <c r="G140" s="17">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H140" s="17">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I140" s="17">
         <v>1500</v>
@@ -6625,10 +6625,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="13">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H141" s="13">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I141" s="13">
         <v>2000</v>
@@ -6660,10 +6660,10 @@
         <v>1</v>
       </c>
       <c r="G142" s="17">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H142" s="17">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I142" s="17">
         <v>1500</v>
@@ -6686,19 +6686,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D143" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E143" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F143" s="13">
         <v>1</v>
       </c>
       <c r="G143" s="13">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="H143" s="13">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="I143" s="13">
         <v>2500</v>
@@ -6730,10 +6730,10 @@
         <v>1</v>
       </c>
       <c r="G144" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H144" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I144" s="17">
         <v>1500</v>
@@ -6765,10 +6765,10 @@
         <v>1</v>
       </c>
       <c r="G145" s="13">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H145" s="13">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I145" s="13">
         <v>2000</v>
@@ -6800,10 +6800,10 @@
         <v>1</v>
       </c>
       <c r="G146" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H146" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I146" s="17">
         <v>1200</v>
@@ -6835,10 +6835,10 @@
         <v>1</v>
       </c>
       <c r="G147" s="13">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H147" s="13">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I147" s="13">
         <v>1500</v>
@@ -6870,10 +6870,10 @@
         <v>1</v>
       </c>
       <c r="G148" s="17">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H148" s="17">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I148" s="17">
         <v>1500</v>
@@ -6905,10 +6905,10 @@
         <v>1</v>
       </c>
       <c r="G149" s="13">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H149" s="13">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I149" s="13">
         <v>2000</v>
@@ -6966,19 +6966,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D151" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E151" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F151" s="13">
         <v>1</v>
       </c>
       <c r="G151" s="13">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="H151" s="13">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="I151" s="13">
         <v>2500</v>
@@ -7010,10 +7010,10 @@
         <v>1</v>
       </c>
       <c r="G152" s="17">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H152" s="17">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I152" s="17">
         <v>2000</v>
@@ -7045,10 +7045,10 @@
         <v>1</v>
       </c>
       <c r="G153" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H153" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I153" s="13">
         <v>1200</v>
@@ -7080,10 +7080,10 @@
         <v>1</v>
       </c>
       <c r="G154" s="17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H154" s="17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I154" s="17">
         <v>1500</v>
@@ -7115,10 +7115,10 @@
         <v>1</v>
       </c>
       <c r="G155" s="13">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H155" s="13">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I155" s="13">
         <v>1500</v>
@@ -7150,10 +7150,10 @@
         <v>1</v>
       </c>
       <c r="G156" s="17">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H156" s="17">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I156" s="17">
         <v>2000</v>
@@ -7185,10 +7185,10 @@
         <v>1</v>
       </c>
       <c r="G157" s="13">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="I157" s="13">
         <v>1500</v>
@@ -7211,19 +7211,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D158" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E158" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F158" s="17">
         <v>1</v>
       </c>
       <c r="G158" s="17">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="H158" s="17">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="I158" s="17">
         <v>2500</v>
@@ -7255,10 +7255,10 @@
         <v>1</v>
       </c>
       <c r="G159" s="13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H159" s="13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I159" s="13">
         <v>2000</v>
@@ -7290,10 +7290,10 @@
         <v>1</v>
       </c>
       <c r="G160" s="17">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H160" s="17">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I160" s="17">
         <v>1200</v>
@@ -7325,10 +7325,10 @@
         <v>1</v>
       </c>
       <c r="G161" s="13">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H161" s="13">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I161" s="13">
         <v>1500</v>
@@ -7360,10 +7360,10 @@
         <v>1</v>
       </c>
       <c r="G162" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H162" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I162" s="17">
         <v>1500</v>
@@ -7395,10 +7395,10 @@
         <v>1</v>
       </c>
       <c r="G163" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H163" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I163" s="13">
         <v>2000</v>
@@ -7430,10 +7430,10 @@
         <v>1</v>
       </c>
       <c r="G164" s="17">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H164" s="17">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I164" s="17">
         <v>1500</v>
@@ -7456,19 +7456,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D165" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E165" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F165" s="13">
         <v>1</v>
       </c>
       <c r="G165" s="13">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="H165" s="13">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="I165" s="13">
         <v>2500</v>
@@ -7500,10 +7500,10 @@
         <v>1</v>
       </c>
       <c r="G166" s="17">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H166" s="17">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I166" s="17">
         <v>1500</v>
@@ -7535,10 +7535,10 @@
         <v>1</v>
       </c>
       <c r="G167" s="13">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H167" s="13">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I167" s="13">
         <v>2000</v>
@@ -7570,10 +7570,10 @@
         <v>1</v>
       </c>
       <c r="G168" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H168" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I168" s="17">
         <v>1200</v>
@@ -7640,10 +7640,10 @@
         <v>1</v>
       </c>
       <c r="G170" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H170" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I170" s="17">
         <v>1500</v>
@@ -7710,10 +7710,10 @@
         <v>1</v>
       </c>
       <c r="G172" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H172" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I172" s="17">
         <v>1500</v>
@@ -7736,19 +7736,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D173" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E173" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F173" s="13">
         <v>1</v>
       </c>
       <c r="G173" s="13">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="H173" s="13">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="I173" s="13">
         <v>2500</v>
@@ -7780,10 +7780,10 @@
         <v>1</v>
       </c>
       <c r="G174" s="17">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H174" s="17">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I174" s="17">
         <v>2000</v>
@@ -7815,10 +7815,10 @@
         <v>1</v>
       </c>
       <c r="G175" s="13">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H175" s="13">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I175" s="13">
         <v>1200</v>
@@ -7850,10 +7850,10 @@
         <v>1</v>
       </c>
       <c r="G176" s="17">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H176" s="17">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I176" s="17">
         <v>1500</v>
@@ -7885,10 +7885,10 @@
         <v>1</v>
       </c>
       <c r="G177" s="13">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H177" s="13">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I177" s="13">
         <v>1500</v>
@@ -7920,10 +7920,10 @@
         <v>1</v>
       </c>
       <c r="G178" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H178" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I178" s="17">
         <v>2000</v>
@@ -7955,10 +7955,10 @@
         <v>1</v>
       </c>
       <c r="G179" s="13">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H179" s="13">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I179" s="13">
         <v>1500</v>
@@ -7981,19 +7981,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D180" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E180" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F180" s="17">
         <v>1</v>
       </c>
       <c r="G180" s="17">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H180" s="17">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="I180" s="17">
         <v>2500</v>
@@ -8025,10 +8025,10 @@
         <v>1</v>
       </c>
       <c r="G181" s="13">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H181" s="13">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I181" s="13">
         <v>2000</v>
@@ -8060,10 +8060,10 @@
         <v>1</v>
       </c>
       <c r="G182" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H182" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I182" s="17">
         <v>1200</v>
@@ -8095,10 +8095,10 @@
         <v>1</v>
       </c>
       <c r="G183" s="13">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H183" s="13">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I183" s="13">
         <v>1500</v>
@@ -8130,10 +8130,10 @@
         <v>1</v>
       </c>
       <c r="G184" s="17">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H184" s="17">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I184" s="17">
         <v>1500</v>
@@ -8165,10 +8165,10 @@
         <v>1</v>
       </c>
       <c r="G185" s="13">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H185" s="13">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I185" s="13">
         <v>2000</v>
@@ -8200,10 +8200,10 @@
         <v>1</v>
       </c>
       <c r="G186" s="17">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H186" s="17">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I186" s="17">
         <v>1500</v>
@@ -8226,19 +8226,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D187" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E187" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F187" s="13">
         <v>1</v>
       </c>
       <c r="G187" s="13">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="H187" s="13">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="I187" s="13">
         <v>2500</v>
@@ -8270,10 +8270,10 @@
         <v>1</v>
       </c>
       <c r="G188" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H188" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I188" s="17">
         <v>1500</v>
@@ -8305,10 +8305,10 @@
         <v>1</v>
       </c>
       <c r="G189" s="13">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H189" s="13">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I189" s="13">
         <v>2000</v>
@@ -8340,10 +8340,10 @@
         <v>1</v>
       </c>
       <c r="G190" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H190" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I190" s="17">
         <v>1200</v>
@@ -8410,10 +8410,10 @@
         <v>1</v>
       </c>
       <c r="G192" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H192" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I192" s="17">
         <v>1500</v>
@@ -8445,10 +8445,10 @@
         <v>1</v>
       </c>
       <c r="G193" s="13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H193" s="13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I193" s="13">
         <v>2000</v>
@@ -8480,10 +8480,10 @@
         <v>1</v>
       </c>
       <c r="G194" s="17">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H194" s="17">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I194" s="17">
         <v>1500</v>
@@ -8506,19 +8506,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D195" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E195" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F195" s="13">
         <v>1</v>
       </c>
       <c r="G195" s="13">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="H195" s="13">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="I195" s="13">
         <v>2500</v>
@@ -8550,10 +8550,10 @@
         <v>1</v>
       </c>
       <c r="G196" s="17">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H196" s="17">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I196" s="17">
         <v>2000</v>
@@ -8585,10 +8585,10 @@
         <v>1</v>
       </c>
       <c r="G197" s="13">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H197" s="13">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I197" s="13">
         <v>1200</v>
@@ -8620,10 +8620,10 @@
         <v>1</v>
       </c>
       <c r="G198" s="17">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H198" s="17">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I198" s="17">
         <v>1500</v>
@@ -8655,10 +8655,10 @@
         <v>1</v>
       </c>
       <c r="G199" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I199" s="13">
         <v>1500</v>
@@ -8690,10 +8690,10 @@
         <v>1</v>
       </c>
       <c r="G200" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H200" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I200" s="17">
         <v>2000</v>
@@ -8725,10 +8725,10 @@
         <v>1</v>
       </c>
       <c r="G201" s="13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H201" s="13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I201" s="13">
         <v>1500</v>
@@ -8751,19 +8751,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D202" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E202" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F202" s="17">
         <v>1</v>
       </c>
       <c r="G202" s="17">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="H202" s="17">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="I202" s="17">
         <v>2500</v>
@@ -8795,10 +8795,10 @@
         <v>1</v>
       </c>
       <c r="G203" s="13">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H203" s="13">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I203" s="13">
         <v>2000</v>
@@ -8830,10 +8830,10 @@
         <v>1</v>
       </c>
       <c r="G204" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H204" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I204" s="17">
         <v>1200</v>
@@ -8865,10 +8865,10 @@
         <v>1</v>
       </c>
       <c r="G205" s="13">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H205" s="13">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I205" s="13">
         <v>1500</v>
@@ -8900,10 +8900,10 @@
         <v>1</v>
       </c>
       <c r="G206" s="17">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H206" s="17">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I206" s="17">
         <v>1500</v>
@@ -8935,10 +8935,10 @@
         <v>1</v>
       </c>
       <c r="G207" s="13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H207" s="13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I207" s="13">
         <v>2000</v>
@@ -8970,10 +8970,10 @@
         <v>1</v>
       </c>
       <c r="G208" s="17">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H208" s="17">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I208" s="17">
         <v>1500</v>
@@ -8996,19 +8996,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D209" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E209" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F209" s="13">
         <v>1</v>
       </c>
       <c r="G209" s="13">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="H209" s="13">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I209" s="13">
         <v>2500</v>
@@ -9040,10 +9040,10 @@
         <v>1</v>
       </c>
       <c r="G210" s="17">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H210" s="17">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I210" s="17">
         <v>1500</v>
@@ -9075,10 +9075,10 @@
         <v>1</v>
       </c>
       <c r="G211" s="13">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H211" s="13">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I211" s="13">
         <v>2000</v>
@@ -9145,10 +9145,10 @@
         <v>1</v>
       </c>
       <c r="G213" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H213" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I213" s="13">
         <v>1500</v>
@@ -9180,10 +9180,10 @@
         <v>1</v>
       </c>
       <c r="G214" s="17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H214" s="17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I214" s="17">
         <v>1500</v>
@@ -9215,10 +9215,10 @@
         <v>1</v>
       </c>
       <c r="G215" s="13">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H215" s="13">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I215" s="13">
         <v>2000</v>
@@ -9276,19 +9276,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D217" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E217" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F217" s="13">
         <v>1</v>
       </c>
       <c r="G217" s="13">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="H217" s="13">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="I217" s="13">
         <v>2500</v>
@@ -9320,10 +9320,10 @@
         <v>1</v>
       </c>
       <c r="G218" s="17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H218" s="17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I218" s="17">
         <v>2000</v>
@@ -9390,10 +9390,10 @@
         <v>1</v>
       </c>
       <c r="G220" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H220" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I220" s="17">
         <v>1500</v>
@@ -9425,10 +9425,10 @@
         <v>1</v>
       </c>
       <c r="G221" s="13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H221" s="13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I221" s="13">
         <v>1500</v>
@@ -9495,10 +9495,10 @@
         <v>1</v>
       </c>
       <c r="G223" s="13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H223" s="13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I223" s="13">
         <v>1500</v>
@@ -9521,19 +9521,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D224" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E224" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F224" s="17">
         <v>1</v>
       </c>
       <c r="G224" s="17">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="H224" s="17">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="I224" s="17">
         <v>2500</v>
@@ -9565,10 +9565,10 @@
         <v>1</v>
       </c>
       <c r="G225" s="13">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H225" s="13">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I225" s="13">
         <v>2000</v>
@@ -9600,10 +9600,10 @@
         <v>1</v>
       </c>
       <c r="G226" s="17">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H226" s="17">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I226" s="17">
         <v>1200</v>
@@ -9635,10 +9635,10 @@
         <v>1</v>
       </c>
       <c r="G227" s="13">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H227" s="13">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I227" s="13">
         <v>1500</v>
@@ -9670,10 +9670,10 @@
         <v>1</v>
       </c>
       <c r="G228" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H228" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I228" s="17">
         <v>1500</v>
@@ -9705,10 +9705,10 @@
         <v>1</v>
       </c>
       <c r="G229" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I229" s="13">
         <v>2000</v>
@@ -9740,10 +9740,10 @@
         <v>1</v>
       </c>
       <c r="G230" s="17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H230" s="17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I230" s="17">
         <v>1500</v>
@@ -9766,19 +9766,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D231" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E231" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F231" s="13">
         <v>1</v>
       </c>
       <c r="G231" s="13">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="H231" s="13">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="I231" s="13">
         <v>2500</v>
@@ -9810,10 +9810,10 @@
         <v>1</v>
       </c>
       <c r="G232" s="17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H232" s="17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I232" s="17">
         <v>1500</v>
@@ -9845,10 +9845,10 @@
         <v>1</v>
       </c>
       <c r="G233" s="13">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H233" s="13">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I233" s="13">
         <v>2000</v>
@@ -9880,10 +9880,10 @@
         <v>1</v>
       </c>
       <c r="G234" s="17">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H234" s="17">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I234" s="17">
         <v>1200</v>
@@ -9915,10 +9915,10 @@
         <v>1</v>
       </c>
       <c r="G235" s="13">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H235" s="13">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I235" s="13">
         <v>1500</v>
@@ -9950,10 +9950,10 @@
         <v>1</v>
       </c>
       <c r="G236" s="17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H236" s="17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I236" s="17">
         <v>1500</v>
@@ -9985,10 +9985,10 @@
         <v>1</v>
       </c>
       <c r="G237" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I237" s="13">
         <v>2000</v>
@@ -10020,10 +10020,10 @@
         <v>1</v>
       </c>
       <c r="G238" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H238" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I238" s="17">
         <v>1500</v>
@@ -10046,19 +10046,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D239" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E239" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F239" s="13">
         <v>1</v>
       </c>
       <c r="G239" s="13">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="H239" s="13">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="I239" s="13">
         <v>2500</v>
@@ -10090,10 +10090,10 @@
         <v>1</v>
       </c>
       <c r="G240" s="17">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H240" s="17">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I240" s="17">
         <v>2000</v>
@@ -10125,10 +10125,10 @@
         <v>1</v>
       </c>
       <c r="G241" s="13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H241" s="13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I241" s="13">
         <v>1200</v>
@@ -10160,10 +10160,10 @@
         <v>1</v>
       </c>
       <c r="G242" s="17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H242" s="17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I242" s="17">
         <v>1500</v>
@@ -10195,10 +10195,10 @@
         <v>1</v>
       </c>
       <c r="G243" s="13">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H243" s="13">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I243" s="13">
         <v>1500</v>
@@ -10230,10 +10230,10 @@
         <v>1</v>
       </c>
       <c r="G244" s="17">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H244" s="17">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="I244" s="17">
         <v>2000</v>
@@ -10265,10 +10265,10 @@
         <v>1</v>
       </c>
       <c r="G245" s="13">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H245" s="13">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I245" s="13">
         <v>1500</v>
@@ -10291,19 +10291,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D246" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E246" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F246" s="17">
         <v>1</v>
       </c>
       <c r="G246" s="17">
-        <v>345</v>
+        <v>394</v>
       </c>
       <c r="H246" s="17">
-        <v>345</v>
+        <v>394</v>
       </c>
       <c r="I246" s="17">
         <v>2500</v>
@@ -10335,10 +10335,10 @@
         <v>1</v>
       </c>
       <c r="G247" s="13">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H247" s="13">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I247" s="13">
         <v>2000</v>
@@ -10370,10 +10370,10 @@
         <v>1</v>
       </c>
       <c r="G248" s="17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H248" s="17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I248" s="17">
         <v>1200</v>
@@ -10405,10 +10405,10 @@
         <v>1</v>
       </c>
       <c r="G249" s="13">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I249" s="13">
         <v>1500</v>
@@ -10475,10 +10475,10 @@
         <v>1</v>
       </c>
       <c r="G251" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H251" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I251" s="13">
         <v>2000</v>
@@ -10510,10 +10510,10 @@
         <v>1</v>
       </c>
       <c r="G252" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H252" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I252" s="17">
         <v>1500</v>
@@ -10536,19 +10536,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D253" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E253" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F253" s="13">
         <v>1</v>
       </c>
       <c r="G253" s="13">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="H253" s="13">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="I253" s="13">
         <v>2500</v>
@@ -10580,10 +10580,10 @@
         <v>1</v>
       </c>
       <c r="G254" s="17">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H254" s="17">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I254" s="17">
         <v>1500</v>
@@ -10615,10 +10615,10 @@
         <v>1</v>
       </c>
       <c r="G255" s="13">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H255" s="13">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I255" s="13">
         <v>2000</v>
@@ -10650,10 +10650,10 @@
         <v>1</v>
       </c>
       <c r="G256" s="17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H256" s="17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I256" s="17">
         <v>1200</v>
@@ -10685,10 +10685,10 @@
         <v>1</v>
       </c>
       <c r="G257" s="13">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I257" s="13">
         <v>1500</v>
@@ -10720,10 +10720,10 @@
         <v>1</v>
       </c>
       <c r="G258" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H258" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I258" s="17">
         <v>1500</v>
@@ -10755,10 +10755,10 @@
         <v>1</v>
       </c>
       <c r="G259" s="13">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H259" s="13">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I259" s="13">
         <v>2000</v>
@@ -10790,10 +10790,10 @@
         <v>1</v>
       </c>
       <c r="G260" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H260" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I260" s="17">
         <v>1500</v>
@@ -10816,19 +10816,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D261" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E261" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F261" s="13">
         <v>1</v>
       </c>
       <c r="G261" s="13">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="H261" s="13">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="I261" s="13">
         <v>2500</v>
@@ -10860,10 +10860,10 @@
         <v>1</v>
       </c>
       <c r="G262" s="17">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H262" s="17">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I262" s="17">
         <v>2000</v>
@@ -10895,10 +10895,10 @@
         <v>1</v>
       </c>
       <c r="G263" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H263" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I263" s="13">
         <v>1200</v>
@@ -10930,10 +10930,10 @@
         <v>1</v>
       </c>
       <c r="G264" s="17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H264" s="17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I264" s="17">
         <v>1500</v>
@@ -10965,10 +10965,10 @@
         <v>1</v>
       </c>
       <c r="G265" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H265" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I265" s="13">
         <v>1500</v>
@@ -11000,10 +11000,10 @@
         <v>1</v>
       </c>
       <c r="G266" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H266" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I266" s="17">
         <v>2000</v>
@@ -11035,10 +11035,10 @@
         <v>1</v>
       </c>
       <c r="G267" s="13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H267" s="13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I267" s="13">
         <v>1500</v>
@@ -11061,19 +11061,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D268" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E268" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F268" s="17">
         <v>1</v>
       </c>
       <c r="G268" s="17">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="H268" s="17">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="I268" s="17">
         <v>2500</v>
@@ -11105,10 +11105,10 @@
         <v>1</v>
       </c>
       <c r="G269" s="13">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H269" s="13">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I269" s="13">
         <v>2000</v>
@@ -11140,10 +11140,10 @@
         <v>1</v>
       </c>
       <c r="G270" s="17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H270" s="17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I270" s="17">
         <v>1200</v>
@@ -11175,10 +11175,10 @@
         <v>1</v>
       </c>
       <c r="G271" s="13">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H271" s="13">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I271" s="13">
         <v>1500</v>
@@ -11210,10 +11210,10 @@
         <v>1</v>
       </c>
       <c r="G272" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H272" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I272" s="17">
         <v>1500</v>
@@ -11245,10 +11245,10 @@
         <v>1</v>
       </c>
       <c r="G273" s="13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H273" s="13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I273" s="13">
         <v>2000</v>
@@ -11280,10 +11280,10 @@
         <v>1</v>
       </c>
       <c r="G274" s="17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H274" s="17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I274" s="17">
         <v>1500</v>
@@ -11306,19 +11306,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D275" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E275" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F275" s="13">
         <v>1</v>
       </c>
       <c r="G275" s="13">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H275" s="13">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I275" s="13">
         <v>2500</v>
@@ -11350,10 +11350,10 @@
         <v>1</v>
       </c>
       <c r="G276" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H276" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I276" s="17">
         <v>1500</v>
@@ -11385,10 +11385,10 @@
         <v>1</v>
       </c>
       <c r="G277" s="13">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H277" s="13">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I277" s="13">
         <v>2000</v>
@@ -11420,10 +11420,10 @@
         <v>1</v>
       </c>
       <c r="G278" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H278" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I278" s="17">
         <v>1200</v>
@@ -11455,10 +11455,10 @@
         <v>1</v>
       </c>
       <c r="G279" s="13">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H279" s="13">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I279" s="13">
         <v>1500</v>
@@ -11490,10 +11490,10 @@
         <v>1</v>
       </c>
       <c r="G280" s="17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H280" s="17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I280" s="17">
         <v>1500</v>
@@ -11525,10 +11525,10 @@
         <v>1</v>
       </c>
       <c r="G281" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H281" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I281" s="13">
         <v>2000</v>
@@ -11560,10 +11560,10 @@
         <v>1</v>
       </c>
       <c r="G282" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H282" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I282" s="17">
         <v>1500</v>
@@ -11586,19 +11586,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D283" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E283" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F283" s="13">
         <v>1</v>
       </c>
       <c r="G283" s="13">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="H283" s="13">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="I283" s="13">
         <v>2500</v>
@@ -11630,10 +11630,10 @@
         <v>1</v>
       </c>
       <c r="G284" s="17">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="H284" s="17">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="I284" s="17">
         <v>2000</v>
@@ -11665,10 +11665,10 @@
         <v>1</v>
       </c>
       <c r="G285" s="13">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H285" s="13">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I285" s="13">
         <v>1200</v>
@@ -11700,10 +11700,10 @@
         <v>1</v>
       </c>
       <c r="G286" s="17">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H286" s="17">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I286" s="17">
         <v>1500</v>
@@ -11735,10 +11735,10 @@
         <v>1</v>
       </c>
       <c r="G287" s="13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H287" s="13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I287" s="13">
         <v>1500</v>
@@ -11770,10 +11770,10 @@
         <v>1</v>
       </c>
       <c r="G288" s="17">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H288" s="17">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I288" s="17">
         <v>2000</v>
@@ -11805,10 +11805,10 @@
         <v>1</v>
       </c>
       <c r="G289" s="13">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H289" s="13">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I289" s="13">
         <v>1500</v>
@@ -11831,19 +11831,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D290" s="17" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E290" s="17" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F290" s="17">
         <v>1</v>
       </c>
       <c r="G290" s="17">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="H290" s="17">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="I290" s="17">
         <v>2500</v>
@@ -11875,10 +11875,10 @@
         <v>1</v>
       </c>
       <c r="G291" s="13">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H291" s="13">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I291" s="13">
         <v>2000</v>
@@ -11910,10 +11910,10 @@
         <v>1</v>
       </c>
       <c r="G292" s="17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H292" s="17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I292" s="17">
         <v>1200</v>
@@ -11945,10 +11945,10 @@
         <v>1</v>
       </c>
       <c r="G293" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H293" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I293" s="13">
         <v>1500</v>
@@ -11980,10 +11980,10 @@
         <v>1</v>
       </c>
       <c r="G294" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H294" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I294" s="17">
         <v>1500</v>
@@ -12015,10 +12015,10 @@
         <v>1</v>
       </c>
       <c r="G295" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H295" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I295" s="13">
         <v>2000</v>
@@ -12076,19 +12076,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D297" s="13" t="str">
-        <v>JavaScript bundle download · index-CM4Ltoba.js</v>
+        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
       </c>
       <c r="E297" s="13" t="str">
-        <v>GET /assets/index-CM4Ltoba.js</v>
+        <v>GET /assets/index-6NSHBj9Z.js</v>
       </c>
       <c r="F297" s="13">
         <v>1</v>
       </c>
       <c r="G297" s="13">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="H297" s="13">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="I297" s="13">
         <v>2500</v>
@@ -12120,10 +12120,10 @@
         <v>1</v>
       </c>
       <c r="G298" s="17">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H298" s="17">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I298" s="17">
         <v>1500</v>
@@ -12155,10 +12155,10 @@
         <v>1</v>
       </c>
       <c r="G299" s="13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H299" s="13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I299" s="13">
         <v>2000</v>
@@ -12190,10 +12190,10 @@
         <v>1</v>
       </c>
       <c r="G300" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H300" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I300" s="17">
         <v>1200</v>
@@ -12225,10 +12225,10 @@
         <v>1</v>
       </c>
       <c r="G301" s="13">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H301" s="13">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="I301" s="13">
         <v>1500</v>
@@ -12260,10 +12260,10 @@
         <v>1</v>
       </c>
       <c r="G302" s="17">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H302" s="17">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I302" s="17">
         <v>2000</v>
@@ -12292,13 +12292,13 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F303" s="13">
-        <v>2418</v>
+        <v>2525</v>
       </c>
       <c r="G303" s="13">
-        <v>166.5</v>
+        <v>159.9</v>
       </c>
       <c r="H303" s="13">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I303" s="13">
         <v>3000</v>
@@ -12327,13 +12327,13 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F304" s="17">
-        <v>2418</v>
+        <v>2525</v>
       </c>
       <c r="G304" s="17">
-        <v>730.4</v>
+        <v>720.8</v>
       </c>
       <c r="H304" s="17">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="I304" s="17">
         <v>3000</v>
@@ -12362,7 +12362,7 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F305" s="13">
-        <v>2418</v>
+        <v>2525</v>
       </c>
       <c r="G305" s="13">
         <v>0</v>
@@ -12575,7 +12575,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B4" s="5">
-        <v>20.29</v>
+        <v>20.32</v>
       </c>
       <c r="D4" s="13" t="str">
         <v>&lt; 50 ms</v>
@@ -12586,7 +12586,7 @@
         <v>Requests</v>
       </c>
       <c r="B5" s="5">
-        <v>2418</v>
+        <v>2525</v>
       </c>
       <c r="D5" s="17" t="str">
         <v>50–100 ms</v>
@@ -12597,7 +12597,7 @@
         <v>Throughput (req/s)</v>
       </c>
       <c r="B6" s="5">
-        <v>119.18</v>
+        <v>124.23</v>
       </c>
       <c r="D6" s="13" t="str">
         <v>100–200 ms</v>
@@ -12608,7 +12608,7 @@
         <v>Data transfer (Mbps)</v>
       </c>
       <c r="B7" s="5">
-        <v>782.92</v>
+        <v>816.72</v>
       </c>
       <c r="D7" s="17" t="str">
         <v>200–500 ms</v>
@@ -12619,7 +12619,7 @@
         <v>Average latency (ms)</v>
       </c>
       <c r="B8" s="5">
-        <v>166.5</v>
+        <v>159.9</v>
       </c>
       <c r="D8" s="13" t="str">
         <v>500–1000 ms</v>
@@ -12630,7 +12630,7 @@
         <v>p50 latency (ms)</v>
       </c>
       <c r="B9" s="5">
-        <v>43.8</v>
+        <v>39.3</v>
       </c>
       <c r="D9" s="17" t="str">
         <v>&gt; 1000 ms</v>
@@ -12641,7 +12641,7 @@
         <v>p95 latency (ms)</v>
       </c>
       <c r="B10" s="5">
-        <v>730.4</v>
+        <v>720.8</v>
       </c>
     </row>
     <row r="11">
@@ -12649,7 +12649,7 @@
         <v>p99 latency (ms)</v>
       </c>
       <c r="B11" s="5">
-        <v>793.9</v>
+        <v>775.2</v>
       </c>
     </row>
     <row r="12">
@@ -12657,7 +12657,7 @@
         <v>Max latency (ms)</v>
       </c>
       <c r="B12" s="5">
-        <v>984.9</v>
+        <v>845</v>
       </c>
     </row>
     <row r="13">
@@ -12745,7 +12745,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B8" s="13" t="str">
-        <v>40365246274</v>
+        <v>40366447214</v>
       </c>
     </row>
     <row r="9">
@@ -12769,7 +12769,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B11" s="17" t="str">
-        <v>8074ec1</v>
+        <v>a9ce338</v>
       </c>
     </row>
     <row r="12">
@@ -12777,7 +12777,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B12" s="13" t="str">
-        <v>2026-10-26T17:05:25.957Z</v>
+        <v>2026-10-26T17:13:56.779Z</v>
       </c>
     </row>
     <row r="13">
@@ -12785,7 +12785,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B13" s="17" t="str">
-        <v>2026-10-26T17:05:48.650Z</v>
+        <v>2026-10-26T17:14:19.441Z</v>
       </c>
     </row>
     <row r="14">
@@ -12817,7 +12817,7 @@
         <v>Sustained duration (s)</v>
       </c>
       <c r="B17" s="17">
-        <v>20.29</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="18">

--- a/reports/Load_Test_Analysis_Report.xlsx
+++ b/reports/Load_Test_Analysis_Report.xlsx
@@ -1295,7 +1295,7 @@
         <v>Test Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:13:56</v>
+        <v>26/10/2026, 17:34:51</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Status:</v>
@@ -1605,13 +1605,13 @@
         <v>Sustained phase duration (s)</v>
       </c>
       <c r="B23" s="5">
-        <v>20.32</v>
+        <v>20.28</v>
       </c>
       <c r="D23" s="13" t="str">
         <v>Throughput (req/s)</v>
       </c>
       <c r="E23" s="13" t="str">
-        <v>124.23 (≥ 5)</v>
+        <v>124.27 (≥ 5)</v>
       </c>
       <c r="F23" s="25" t="str">
         <v>PASS</v>
@@ -1622,13 +1622,13 @@
         <v>Total HTTP requests</v>
       </c>
       <c r="B24" s="5">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="D24" s="17" t="str">
         <v>p95 latency (ms)</v>
       </c>
       <c r="E24" s="17" t="str">
-        <v>720.8 (≤ 3000)</v>
+        <v>703.1 (≤ 3000)</v>
       </c>
       <c r="F24" s="25" t="str">
         <v>PASS</v>
@@ -1639,7 +1639,7 @@
         <v>Throughput (req/s)</v>
       </c>
       <c r="B25" s="5">
-        <v>124.23</v>
+        <v>124.27</v>
       </c>
       <c r="D25" s="13" t="str">
         <v>Error rate (%)</v>
@@ -1656,7 +1656,7 @@
         <v>Average latency (ms)</v>
       </c>
       <c r="B26" s="5">
-        <v>159.9</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27">
@@ -1664,7 +1664,7 @@
         <v>p95 latency (ms)</v>
       </c>
       <c r="B27" s="5">
-        <v>720.8</v>
+        <v>703.1</v>
       </c>
     </row>
     <row r="28">
@@ -1672,7 +1672,7 @@
         <v>p99 latency (ms)</v>
       </c>
       <c r="B28" s="5">
-        <v>775.2</v>
+        <v>772.3</v>
       </c>
     </row>
     <row r="29">
@@ -1688,7 +1688,7 @@
         <v>Data transferred (MB)</v>
       </c>
       <c r="B30" s="5">
-        <v>2075</v>
+        <v>2071.5</v>
       </c>
     </row>
   </sheetData>
@@ -1795,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="13">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H3" s="13">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I3" s="13">
         <v>1500</v>
@@ -1821,19 +1821,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D4" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E4" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F4" s="17">
         <v>1</v>
       </c>
       <c r="G4" s="17">
-        <v>549</v>
+        <v>632</v>
       </c>
       <c r="H4" s="17">
-        <v>549</v>
+        <v>632</v>
       </c>
       <c r="I4" s="17">
         <v>2500</v>
@@ -1856,19 +1856,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D5" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E5" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F5" s="13">
         <v>1</v>
       </c>
       <c r="G5" s="13">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="H5" s="13">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="I5" s="13">
         <v>2000</v>
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="17">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="H6" s="17">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="I6" s="17">
         <v>1200</v>
@@ -1935,10 +1935,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="13">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="H7" s="13">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="I7" s="13">
         <v>1500</v>
@@ -1970,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="17">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H8" s="17">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I8" s="17">
         <v>1500</v>
@@ -2005,10 +2005,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="13">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="H9" s="13">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="I9" s="13">
         <v>2000</v>
@@ -2040,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="17">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="H10" s="17">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="I10" s="17">
         <v>1500</v>
@@ -2066,19 +2066,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D11" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E11" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F11" s="13">
         <v>1</v>
       </c>
       <c r="G11" s="13">
-        <v>675</v>
+        <v>637</v>
       </c>
       <c r="H11" s="13">
-        <v>675</v>
+        <v>637</v>
       </c>
       <c r="I11" s="13">
         <v>2500</v>
@@ -2110,10 +2110,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="17">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="H12" s="17">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="I12" s="17">
         <v>1500</v>
@@ -2136,19 +2136,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D13" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E13" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F13" s="13">
         <v>1</v>
       </c>
       <c r="G13" s="13">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="H13" s="13">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="I13" s="13">
         <v>2000</v>
@@ -2180,10 +2180,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="17">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H14" s="17">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I14" s="17">
         <v>1200</v>
@@ -2215,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="13">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H15" s="13">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I15" s="13">
         <v>1500</v>
@@ -2250,10 +2250,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="17">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H16" s="17">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I16" s="17">
         <v>1500</v>
@@ -2285,10 +2285,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="13">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="H17" s="13">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="I17" s="13">
         <v>2000</v>
@@ -2320,10 +2320,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="17">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="H18" s="17">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="I18" s="17">
         <v>1500</v>
@@ -2346,19 +2346,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D19" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E19" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F19" s="13">
         <v>1</v>
       </c>
       <c r="G19" s="13">
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="H19" s="13">
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="I19" s="13">
         <v>2500</v>
@@ -2381,19 +2381,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D20" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E20" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F20" s="17">
         <v>1</v>
       </c>
       <c r="G20" s="17">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H20" s="17">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I20" s="17">
         <v>2000</v>
@@ -2425,10 +2425,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H21" s="13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I21" s="13">
         <v>1200</v>
@@ -2460,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="17">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H22" s="17">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I22" s="17">
         <v>1500</v>
@@ -2495,10 +2495,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="13">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H23" s="13">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I23" s="13">
         <v>1500</v>
@@ -2530,10 +2530,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H24" s="17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I24" s="17">
         <v>2000</v>
@@ -2565,10 +2565,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="13">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H25" s="13">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I25" s="13">
         <v>1500</v>
@@ -2591,19 +2591,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D26" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E26" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F26" s="17">
         <v>1</v>
       </c>
       <c r="G26" s="17">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="H26" s="17">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="I26" s="17">
         <v>2500</v>
@@ -2626,19 +2626,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D27" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E27" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F27" s="13">
         <v>1</v>
       </c>
       <c r="G27" s="13">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H27" s="13">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="I27" s="13">
         <v>2000</v>
@@ -2670,10 +2670,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H28" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I28" s="17">
         <v>1200</v>
@@ -2705,10 +2705,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="13">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H29" s="13">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I29" s="13">
         <v>1500</v>
@@ -2740,10 +2740,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="17">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H30" s="17">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I30" s="17">
         <v>1500</v>
@@ -2775,10 +2775,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="13">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H31" s="13">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I31" s="13">
         <v>2000</v>
@@ -2810,10 +2810,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="17">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H32" s="17">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I32" s="17">
         <v>1500</v>
@@ -2836,19 +2836,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D33" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E33" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F33" s="13">
         <v>1</v>
       </c>
       <c r="G33" s="13">
-        <v>473</v>
+        <v>535</v>
       </c>
       <c r="H33" s="13">
-        <v>473</v>
+        <v>535</v>
       </c>
       <c r="I33" s="13">
         <v>2500</v>
@@ -2880,10 +2880,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="17">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H34" s="17">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I34" s="17">
         <v>1500</v>
@@ -2906,19 +2906,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D35" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E35" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F35" s="13">
         <v>1</v>
       </c>
       <c r="G35" s="13">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H35" s="13">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I35" s="13">
         <v>2000</v>
@@ -2950,10 +2950,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H36" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I36" s="17">
         <v>1200</v>
@@ -2985,10 +2985,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H37" s="13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I37" s="13">
         <v>1500</v>
@@ -3020,10 +3020,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H38" s="17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I38" s="17">
         <v>1500</v>
@@ -3055,10 +3055,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="13">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H39" s="13">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I39" s="13">
         <v>2000</v>
@@ -3090,10 +3090,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="17">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H40" s="17">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I40" s="17">
         <v>1500</v>
@@ -3116,19 +3116,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D41" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E41" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F41" s="13">
         <v>1</v>
       </c>
       <c r="G41" s="13">
-        <v>660</v>
+        <v>493</v>
       </c>
       <c r="H41" s="13">
-        <v>660</v>
+        <v>493</v>
       </c>
       <c r="I41" s="13">
         <v>2500</v>
@@ -3151,19 +3151,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D42" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E42" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F42" s="17">
         <v>1</v>
       </c>
       <c r="G42" s="17">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H42" s="17">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="I42" s="17">
         <v>2000</v>
@@ -3195,10 +3195,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H43" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I43" s="13">
         <v>1200</v>
@@ -3230,10 +3230,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H44" s="17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I44" s="17">
         <v>1500</v>
@@ -3265,10 +3265,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H45" s="13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I45" s="13">
         <v>1500</v>
@@ -3300,10 +3300,10 @@
         <v>1</v>
       </c>
       <c r="G46" s="17">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H46" s="17">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I46" s="17">
         <v>2000</v>
@@ -3335,10 +3335,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="13">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H47" s="13">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I47" s="13">
         <v>1500</v>
@@ -3361,19 +3361,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D48" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E48" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F48" s="17">
         <v>1</v>
       </c>
       <c r="G48" s="17">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="H48" s="17">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="I48" s="17">
         <v>2500</v>
@@ -3396,19 +3396,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D49" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E49" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F49" s="13">
         <v>1</v>
       </c>
       <c r="G49" s="13">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="H49" s="13">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="I49" s="13">
         <v>2000</v>
@@ -3440,10 +3440,10 @@
         <v>1</v>
       </c>
       <c r="G50" s="17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H50" s="17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I50" s="17">
         <v>1200</v>
@@ -3475,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="13">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H51" s="13">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I51" s="13">
         <v>1500</v>
@@ -3545,10 +3545,10 @@
         <v>1</v>
       </c>
       <c r="G53" s="13">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H53" s="13">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I53" s="13">
         <v>2000</v>
@@ -3580,10 +3580,10 @@
         <v>1</v>
       </c>
       <c r="G54" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H54" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I54" s="17">
         <v>1500</v>
@@ -3606,19 +3606,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D55" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E55" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F55" s="13">
         <v>1</v>
       </c>
       <c r="G55" s="13">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="H55" s="13">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="I55" s="13">
         <v>2500</v>
@@ -3650,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="G56" s="17">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H56" s="17">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I56" s="17">
         <v>1500</v>
@@ -3676,19 +3676,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D57" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E57" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F57" s="13">
         <v>1</v>
       </c>
       <c r="G57" s="13">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H57" s="13">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I57" s="13">
         <v>2000</v>
@@ -3720,10 +3720,10 @@
         <v>1</v>
       </c>
       <c r="G58" s="17">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H58" s="17">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I58" s="17">
         <v>1200</v>
@@ -3755,10 +3755,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="13">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H59" s="13">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I59" s="13">
         <v>1500</v>
@@ -3790,10 +3790,10 @@
         <v>1</v>
       </c>
       <c r="G60" s="17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H60" s="17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I60" s="17">
         <v>1500</v>
@@ -3825,10 +3825,10 @@
         <v>1</v>
       </c>
       <c r="G61" s="13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H61" s="13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I61" s="13">
         <v>2000</v>
@@ -3860,10 +3860,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="17">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H62" s="17">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I62" s="17">
         <v>1500</v>
@@ -3886,19 +3886,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D63" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E63" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F63" s="13">
         <v>1</v>
       </c>
       <c r="G63" s="13">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="H63" s="13">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="I63" s="13">
         <v>2500</v>
@@ -3921,19 +3921,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D64" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E64" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F64" s="17">
         <v>1</v>
       </c>
       <c r="G64" s="17">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H64" s="17">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I64" s="17">
         <v>2000</v>
@@ -3965,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H65" s="13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I65" s="13">
         <v>1200</v>
@@ -4000,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H66" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I66" s="17">
         <v>1500</v>
@@ -4035,10 +4035,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H67" s="13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I67" s="13">
         <v>1500</v>
@@ -4070,10 +4070,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H68" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I68" s="17">
         <v>2000</v>
@@ -4105,10 +4105,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H69" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I69" s="13">
         <v>1500</v>
@@ -4131,19 +4131,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D70" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E70" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F70" s="17">
         <v>1</v>
       </c>
       <c r="G70" s="17">
-        <v>431</v>
+        <v>387</v>
       </c>
       <c r="H70" s="17">
-        <v>431</v>
+        <v>387</v>
       </c>
       <c r="I70" s="17">
         <v>2500</v>
@@ -4166,19 +4166,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D71" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E71" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F71" s="13">
         <v>1</v>
       </c>
       <c r="G71" s="13">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H71" s="13">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I71" s="13">
         <v>2000</v>
@@ -4210,10 +4210,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H72" s="17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I72" s="17">
         <v>1200</v>
@@ -4245,10 +4245,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="13">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H73" s="13">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I73" s="13">
         <v>1500</v>
@@ -4280,10 +4280,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H74" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I74" s="17">
         <v>1500</v>
@@ -4315,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="G75" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I75" s="13">
         <v>2000</v>
@@ -4350,10 +4350,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H76" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I76" s="17">
         <v>1500</v>
@@ -4376,19 +4376,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D77" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E77" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F77" s="13">
         <v>1</v>
       </c>
       <c r="G77" s="13">
-        <v>479</v>
+        <v>423</v>
       </c>
       <c r="H77" s="13">
-        <v>479</v>
+        <v>423</v>
       </c>
       <c r="I77" s="13">
         <v>2500</v>
@@ -4420,10 +4420,10 @@
         <v>1</v>
       </c>
       <c r="G78" s="17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H78" s="17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I78" s="17">
         <v>1500</v>
@@ -4446,19 +4446,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D79" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E79" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F79" s="13">
         <v>1</v>
       </c>
       <c r="G79" s="13">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H79" s="13">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I79" s="13">
         <v>2000</v>
@@ -4490,10 +4490,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H80" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I80" s="17">
         <v>1200</v>
@@ -4525,10 +4525,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H81" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I81" s="13">
         <v>1500</v>
@@ -4560,10 +4560,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="17">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H82" s="17">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I82" s="17">
         <v>1500</v>
@@ -4595,10 +4595,10 @@
         <v>1</v>
       </c>
       <c r="G83" s="13">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H83" s="13">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I83" s="13">
         <v>2000</v>
@@ -4630,10 +4630,10 @@
         <v>1</v>
       </c>
       <c r="G84" s="17">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H84" s="17">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I84" s="17">
         <v>1500</v>
@@ -4656,19 +4656,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D85" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E85" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F85" s="13">
         <v>1</v>
       </c>
       <c r="G85" s="13">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="H85" s="13">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="I85" s="13">
         <v>2500</v>
@@ -4691,19 +4691,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D86" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E86" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F86" s="17">
         <v>1</v>
       </c>
       <c r="G86" s="17">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H86" s="17">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I86" s="17">
         <v>2000</v>
@@ -4735,10 +4735,10 @@
         <v>1</v>
       </c>
       <c r="G87" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H87" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I87" s="13">
         <v>1200</v>
@@ -4770,10 +4770,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="17">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H88" s="17">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I88" s="17">
         <v>1500</v>
@@ -4805,10 +4805,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H89" s="13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I89" s="13">
         <v>1500</v>
@@ -4840,10 +4840,10 @@
         <v>1</v>
       </c>
       <c r="G90" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H90" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I90" s="17">
         <v>2000</v>
@@ -4875,10 +4875,10 @@
         <v>1</v>
       </c>
       <c r="G91" s="13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H91" s="13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I91" s="13">
         <v>1500</v>
@@ -4901,19 +4901,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D92" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E92" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F92" s="17">
         <v>1</v>
       </c>
       <c r="G92" s="17">
-        <v>495</v>
+        <v>449</v>
       </c>
       <c r="H92" s="17">
-        <v>495</v>
+        <v>449</v>
       </c>
       <c r="I92" s="17">
         <v>2500</v>
@@ -4936,19 +4936,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D93" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E93" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F93" s="13">
         <v>1</v>
       </c>
       <c r="G93" s="13">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H93" s="13">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I93" s="13">
         <v>2000</v>
@@ -4980,10 +4980,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H94" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I94" s="17">
         <v>1200</v>
@@ -5015,10 +5015,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H95" s="13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I95" s="13">
         <v>1500</v>
@@ -5050,10 +5050,10 @@
         <v>1</v>
       </c>
       <c r="G96" s="17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H96" s="17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I96" s="17">
         <v>1500</v>
@@ -5085,10 +5085,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="13">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I97" s="13">
         <v>2000</v>
@@ -5120,10 +5120,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="17">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H98" s="17">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I98" s="17">
         <v>1500</v>
@@ -5146,19 +5146,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D99" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E99" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F99" s="13">
         <v>1</v>
       </c>
       <c r="G99" s="13">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="H99" s="13">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="I99" s="13">
         <v>2500</v>
@@ -5190,10 +5190,10 @@
         <v>1</v>
       </c>
       <c r="G100" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H100" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I100" s="17">
         <v>1500</v>
@@ -5216,19 +5216,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D101" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E101" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F101" s="13">
         <v>1</v>
       </c>
       <c r="G101" s="13">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H101" s="13">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I101" s="13">
         <v>2000</v>
@@ -5260,10 +5260,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H102" s="17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I102" s="17">
         <v>1200</v>
@@ -5295,10 +5295,10 @@
         <v>1</v>
       </c>
       <c r="G103" s="13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H103" s="13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I103" s="13">
         <v>1500</v>
@@ -5330,10 +5330,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H104" s="17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I104" s="17">
         <v>1500</v>
@@ -5365,10 +5365,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="13">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H105" s="13">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I105" s="13">
         <v>2000</v>
@@ -5400,10 +5400,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H106" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I106" s="17">
         <v>1500</v>
@@ -5426,19 +5426,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D107" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E107" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F107" s="13">
         <v>1</v>
       </c>
       <c r="G107" s="13">
-        <v>458</v>
+        <v>430</v>
       </c>
       <c r="H107" s="13">
-        <v>458</v>
+        <v>430</v>
       </c>
       <c r="I107" s="13">
         <v>2500</v>
@@ -5461,19 +5461,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D108" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E108" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F108" s="17">
         <v>1</v>
       </c>
       <c r="G108" s="17">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H108" s="17">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I108" s="17">
         <v>2000</v>
@@ -5540,10 +5540,10 @@
         <v>1</v>
       </c>
       <c r="G110" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H110" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I110" s="17">
         <v>1500</v>
@@ -5610,10 +5610,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H112" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I112" s="17">
         <v>2000</v>
@@ -5645,10 +5645,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="13">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H113" s="13">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I113" s="13">
         <v>1500</v>
@@ -5671,19 +5671,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D114" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E114" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F114" s="17">
         <v>1</v>
       </c>
       <c r="G114" s="17">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="H114" s="17">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="I114" s="17">
         <v>2500</v>
@@ -5706,19 +5706,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D115" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E115" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F115" s="13">
         <v>1</v>
       </c>
       <c r="G115" s="13">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H115" s="13">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I115" s="13">
         <v>2000</v>
@@ -5750,10 +5750,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H116" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I116" s="17">
         <v>1200</v>
@@ -5785,10 +5785,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H117" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I117" s="13">
         <v>1500</v>
@@ -5820,10 +5820,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H118" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I118" s="17">
         <v>1500</v>
@@ -5855,10 +5855,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="13">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I119" s="13">
         <v>2000</v>
@@ -5890,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H120" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I120" s="17">
         <v>1500</v>
@@ -5916,19 +5916,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D121" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E121" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F121" s="13">
         <v>1</v>
       </c>
       <c r="G121" s="13">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="H121" s="13">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="I121" s="13">
         <v>2500</v>
@@ -5986,19 +5986,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D123" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E123" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F123" s="13">
         <v>1</v>
       </c>
       <c r="G123" s="13">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H123" s="13">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="I123" s="13">
         <v>2000</v>
@@ -6030,10 +6030,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H124" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I124" s="17">
         <v>1200</v>
@@ -6065,10 +6065,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="13">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="H125" s="13">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="I125" s="13">
         <v>1500</v>
@@ -6100,10 +6100,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="17">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H126" s="17">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I126" s="17">
         <v>1500</v>
@@ -6135,10 +6135,10 @@
         <v>1</v>
       </c>
       <c r="G127" s="13">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H127" s="13">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I127" s="13">
         <v>2000</v>
@@ -6170,10 +6170,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H128" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I128" s="17">
         <v>1500</v>
@@ -6196,19 +6196,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D129" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E129" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F129" s="13">
         <v>1</v>
       </c>
       <c r="G129" s="13">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="H129" s="13">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="I129" s="13">
         <v>2500</v>
@@ -6231,19 +6231,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D130" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E130" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F130" s="17">
         <v>1</v>
       </c>
       <c r="G130" s="17">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H130" s="17">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I130" s="17">
         <v>2000</v>
@@ -6275,10 +6275,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H131" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I131" s="13">
         <v>1200</v>
@@ -6345,10 +6345,10 @@
         <v>1</v>
       </c>
       <c r="G133" s="13">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H133" s="13">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I133" s="13">
         <v>1500</v>
@@ -6380,10 +6380,10 @@
         <v>1</v>
       </c>
       <c r="G134" s="17">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H134" s="17">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I134" s="17">
         <v>2000</v>
@@ -6415,10 +6415,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="13">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H135" s="13">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I135" s="13">
         <v>1500</v>
@@ -6441,19 +6441,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D136" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E136" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F136" s="17">
         <v>1</v>
       </c>
       <c r="G136" s="17">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="H136" s="17">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="I136" s="17">
         <v>2500</v>
@@ -6476,19 +6476,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D137" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E137" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F137" s="13">
         <v>1</v>
       </c>
       <c r="G137" s="13">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="H137" s="13">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="I137" s="13">
         <v>2000</v>
@@ -6520,10 +6520,10 @@
         <v>1</v>
       </c>
       <c r="G138" s="17">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H138" s="17">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I138" s="17">
         <v>1200</v>
@@ -6555,10 +6555,10 @@
         <v>1</v>
       </c>
       <c r="G139" s="13">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H139" s="13">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I139" s="13">
         <v>1500</v>
@@ -6590,10 +6590,10 @@
         <v>1</v>
       </c>
       <c r="G140" s="17">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H140" s="17">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I140" s="17">
         <v>1500</v>
@@ -6625,10 +6625,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="13">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H141" s="13">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I141" s="13">
         <v>2000</v>
@@ -6660,10 +6660,10 @@
         <v>1</v>
       </c>
       <c r="G142" s="17">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H142" s="17">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I142" s="17">
         <v>1500</v>
@@ -6686,19 +6686,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D143" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E143" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F143" s="13">
         <v>1</v>
       </c>
       <c r="G143" s="13">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="H143" s="13">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="I143" s="13">
         <v>2500</v>
@@ -6730,10 +6730,10 @@
         <v>1</v>
       </c>
       <c r="G144" s="17">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H144" s="17">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I144" s="17">
         <v>1500</v>
@@ -6756,19 +6756,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D145" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E145" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F145" s="13">
         <v>1</v>
       </c>
       <c r="G145" s="13">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H145" s="13">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I145" s="13">
         <v>2000</v>
@@ -6800,10 +6800,10 @@
         <v>1</v>
       </c>
       <c r="G146" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H146" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I146" s="17">
         <v>1200</v>
@@ -6835,10 +6835,10 @@
         <v>1</v>
       </c>
       <c r="G147" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H147" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I147" s="13">
         <v>1500</v>
@@ -6870,10 +6870,10 @@
         <v>1</v>
       </c>
       <c r="G148" s="17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H148" s="17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I148" s="17">
         <v>1500</v>
@@ -6905,10 +6905,10 @@
         <v>1</v>
       </c>
       <c r="G149" s="13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H149" s="13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I149" s="13">
         <v>2000</v>
@@ -6940,10 +6940,10 @@
         <v>1</v>
       </c>
       <c r="G150" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H150" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I150" s="17">
         <v>1500</v>
@@ -6966,19 +6966,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D151" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E151" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F151" s="13">
         <v>1</v>
       </c>
       <c r="G151" s="13">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="H151" s="13">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="I151" s="13">
         <v>2500</v>
@@ -7001,10 +7001,10 @@
         <v>CAT-03</v>
       </c>
       <c r="D152" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E152" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F152" s="17">
         <v>1</v>
@@ -7045,10 +7045,10 @@
         <v>1</v>
       </c>
       <c r="G153" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H153" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I153" s="13">
         <v>1200</v>
@@ -7080,10 +7080,10 @@
         <v>1</v>
       </c>
       <c r="G154" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H154" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I154" s="17">
         <v>1500</v>
@@ -7115,10 +7115,10 @@
         <v>1</v>
       </c>
       <c r="G155" s="13">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H155" s="13">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I155" s="13">
         <v>1500</v>
@@ -7150,10 +7150,10 @@
         <v>1</v>
       </c>
       <c r="G156" s="17">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H156" s="17">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I156" s="17">
         <v>2000</v>
@@ -7185,10 +7185,10 @@
         <v>1</v>
       </c>
       <c r="G157" s="13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H157" s="13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I157" s="13">
         <v>1500</v>
@@ -7211,19 +7211,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D158" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E158" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F158" s="17">
         <v>1</v>
       </c>
       <c r="G158" s="17">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H158" s="17">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I158" s="17">
         <v>2500</v>
@@ -7246,19 +7246,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D159" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E159" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F159" s="13">
         <v>1</v>
       </c>
       <c r="G159" s="13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H159" s="13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I159" s="13">
         <v>2000</v>
@@ -7290,10 +7290,10 @@
         <v>1</v>
       </c>
       <c r="G160" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H160" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I160" s="17">
         <v>1200</v>
@@ -7325,10 +7325,10 @@
         <v>1</v>
       </c>
       <c r="G161" s="13">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H161" s="13">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I161" s="13">
         <v>1500</v>
@@ -7360,10 +7360,10 @@
         <v>1</v>
       </c>
       <c r="G162" s="17">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H162" s="17">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I162" s="17">
         <v>1500</v>
@@ -7395,10 +7395,10 @@
         <v>1</v>
       </c>
       <c r="G163" s="13">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H163" s="13">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I163" s="13">
         <v>2000</v>
@@ -7430,10 +7430,10 @@
         <v>1</v>
       </c>
       <c r="G164" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H164" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I164" s="17">
         <v>1500</v>
@@ -7456,19 +7456,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D165" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E165" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F165" s="13">
         <v>1</v>
       </c>
       <c r="G165" s="13">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="H165" s="13">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="I165" s="13">
         <v>2500</v>
@@ -7500,10 +7500,10 @@
         <v>1</v>
       </c>
       <c r="G166" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H166" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I166" s="17">
         <v>1500</v>
@@ -7526,19 +7526,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D167" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E167" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F167" s="13">
         <v>1</v>
       </c>
       <c r="G167" s="13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H167" s="13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I167" s="13">
         <v>2000</v>
@@ -7570,10 +7570,10 @@
         <v>1</v>
       </c>
       <c r="G168" s="17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H168" s="17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I168" s="17">
         <v>1200</v>
@@ -7605,10 +7605,10 @@
         <v>1</v>
       </c>
       <c r="G169" s="13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H169" s="13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I169" s="13">
         <v>1500</v>
@@ -7640,10 +7640,10 @@
         <v>1</v>
       </c>
       <c r="G170" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H170" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I170" s="17">
         <v>1500</v>
@@ -7675,10 +7675,10 @@
         <v>1</v>
       </c>
       <c r="G171" s="13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H171" s="13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I171" s="13">
         <v>2000</v>
@@ -7710,10 +7710,10 @@
         <v>1</v>
       </c>
       <c r="G172" s="17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H172" s="17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I172" s="17">
         <v>1500</v>
@@ -7736,19 +7736,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D173" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E173" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F173" s="13">
         <v>1</v>
       </c>
       <c r="G173" s="13">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="H173" s="13">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="I173" s="13">
         <v>2500</v>
@@ -7771,19 +7771,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D174" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E174" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F174" s="17">
         <v>1</v>
       </c>
       <c r="G174" s="17">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H174" s="17">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I174" s="17">
         <v>2000</v>
@@ -7850,10 +7850,10 @@
         <v>1</v>
       </c>
       <c r="G176" s="17">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H176" s="17">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I176" s="17">
         <v>1500</v>
@@ -7885,10 +7885,10 @@
         <v>1</v>
       </c>
       <c r="G177" s="13">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H177" s="13">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I177" s="13">
         <v>1500</v>
@@ -7920,10 +7920,10 @@
         <v>1</v>
       </c>
       <c r="G178" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H178" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I178" s="17">
         <v>2000</v>
@@ -7955,10 +7955,10 @@
         <v>1</v>
       </c>
       <c r="G179" s="13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H179" s="13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I179" s="13">
         <v>1500</v>
@@ -7981,19 +7981,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D180" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E180" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F180" s="17">
         <v>1</v>
       </c>
       <c r="G180" s="17">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="H180" s="17">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="I180" s="17">
         <v>2500</v>
@@ -8016,19 +8016,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D181" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E181" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F181" s="13">
         <v>1</v>
       </c>
       <c r="G181" s="13">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H181" s="13">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I181" s="13">
         <v>2000</v>
@@ -8060,10 +8060,10 @@
         <v>1</v>
       </c>
       <c r="G182" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H182" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I182" s="17">
         <v>1200</v>
@@ -8095,10 +8095,10 @@
         <v>1</v>
       </c>
       <c r="G183" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H183" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I183" s="13">
         <v>1500</v>
@@ -8130,10 +8130,10 @@
         <v>1</v>
       </c>
       <c r="G184" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H184" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I184" s="17">
         <v>1500</v>
@@ -8165,10 +8165,10 @@
         <v>1</v>
       </c>
       <c r="G185" s="13">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H185" s="13">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I185" s="13">
         <v>2000</v>
@@ -8200,10 +8200,10 @@
         <v>1</v>
       </c>
       <c r="G186" s="17">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H186" s="17">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I186" s="17">
         <v>1500</v>
@@ -8226,19 +8226,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D187" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E187" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F187" s="13">
         <v>1</v>
       </c>
       <c r="G187" s="13">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="H187" s="13">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="I187" s="13">
         <v>2500</v>
@@ -8270,10 +8270,10 @@
         <v>1</v>
       </c>
       <c r="G188" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H188" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I188" s="17">
         <v>1500</v>
@@ -8296,19 +8296,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D189" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E189" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F189" s="13">
         <v>1</v>
       </c>
       <c r="G189" s="13">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H189" s="13">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I189" s="13">
         <v>2000</v>
@@ -8340,10 +8340,10 @@
         <v>1</v>
       </c>
       <c r="G190" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H190" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I190" s="17">
         <v>1200</v>
@@ -8375,10 +8375,10 @@
         <v>1</v>
       </c>
       <c r="G191" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H191" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I191" s="13">
         <v>1500</v>
@@ -8410,10 +8410,10 @@
         <v>1</v>
       </c>
       <c r="G192" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H192" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I192" s="17">
         <v>1500</v>
@@ -8445,10 +8445,10 @@
         <v>1</v>
       </c>
       <c r="G193" s="13">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H193" s="13">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I193" s="13">
         <v>2000</v>
@@ -8480,10 +8480,10 @@
         <v>1</v>
       </c>
       <c r="G194" s="17">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H194" s="17">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I194" s="17">
         <v>1500</v>
@@ -8506,19 +8506,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D195" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E195" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F195" s="13">
         <v>1</v>
       </c>
       <c r="G195" s="13">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="H195" s="13">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="I195" s="13">
         <v>2500</v>
@@ -8541,19 +8541,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D196" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E196" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F196" s="17">
         <v>1</v>
       </c>
       <c r="G196" s="17">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H196" s="17">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I196" s="17">
         <v>2000</v>
@@ -8585,10 +8585,10 @@
         <v>1</v>
       </c>
       <c r="G197" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H197" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I197" s="13">
         <v>1200</v>
@@ -8620,10 +8620,10 @@
         <v>1</v>
       </c>
       <c r="G198" s="17">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H198" s="17">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I198" s="17">
         <v>1500</v>
@@ -8655,10 +8655,10 @@
         <v>1</v>
       </c>
       <c r="G199" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H199" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I199" s="13">
         <v>1500</v>
@@ -8725,10 +8725,10 @@
         <v>1</v>
       </c>
       <c r="G201" s="13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H201" s="13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I201" s="13">
         <v>1500</v>
@@ -8751,19 +8751,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D202" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E202" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F202" s="17">
         <v>1</v>
       </c>
       <c r="G202" s="17">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="H202" s="17">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="I202" s="17">
         <v>2500</v>
@@ -8786,19 +8786,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D203" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E203" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F203" s="13">
         <v>1</v>
       </c>
       <c r="G203" s="13">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H203" s="13">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="I203" s="13">
         <v>2000</v>
@@ -8830,10 +8830,10 @@
         <v>1</v>
       </c>
       <c r="G204" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H204" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I204" s="17">
         <v>1200</v>
@@ -8865,10 +8865,10 @@
         <v>1</v>
       </c>
       <c r="G205" s="13">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H205" s="13">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I205" s="13">
         <v>1500</v>
@@ -8900,10 +8900,10 @@
         <v>1</v>
       </c>
       <c r="G206" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H206" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I206" s="17">
         <v>1500</v>
@@ -8996,19 +8996,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D209" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E209" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F209" s="13">
         <v>1</v>
       </c>
       <c r="G209" s="13">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="H209" s="13">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="I209" s="13">
         <v>2500</v>
@@ -9040,10 +9040,10 @@
         <v>1</v>
       </c>
       <c r="G210" s="17">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H210" s="17">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I210" s="17">
         <v>1500</v>
@@ -9066,19 +9066,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D211" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E211" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F211" s="13">
         <v>1</v>
       </c>
       <c r="G211" s="13">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H211" s="13">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I211" s="13">
         <v>2000</v>
@@ -9110,10 +9110,10 @@
         <v>1</v>
       </c>
       <c r="G212" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H212" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I212" s="17">
         <v>1200</v>
@@ -9145,10 +9145,10 @@
         <v>1</v>
       </c>
       <c r="G213" s="13">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H213" s="13">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I213" s="13">
         <v>1500</v>
@@ -9180,10 +9180,10 @@
         <v>1</v>
       </c>
       <c r="G214" s="17">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H214" s="17">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I214" s="17">
         <v>1500</v>
@@ -9215,10 +9215,10 @@
         <v>1</v>
       </c>
       <c r="G215" s="13">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H215" s="13">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I215" s="13">
         <v>2000</v>
@@ -9250,10 +9250,10 @@
         <v>1</v>
       </c>
       <c r="G216" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H216" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I216" s="17">
         <v>1500</v>
@@ -9276,19 +9276,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D217" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E217" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F217" s="13">
         <v>1</v>
       </c>
       <c r="G217" s="13">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="H217" s="13">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="I217" s="13">
         <v>2500</v>
@@ -9311,19 +9311,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D218" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E218" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F218" s="17">
         <v>1</v>
       </c>
       <c r="G218" s="17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H218" s="17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I218" s="17">
         <v>2000</v>
@@ -9355,10 +9355,10 @@
         <v>1</v>
       </c>
       <c r="G219" s="13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H219" s="13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I219" s="13">
         <v>1200</v>
@@ -9390,10 +9390,10 @@
         <v>1</v>
       </c>
       <c r="G220" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H220" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I220" s="17">
         <v>1500</v>
@@ -9425,10 +9425,10 @@
         <v>1</v>
       </c>
       <c r="G221" s="13">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H221" s="13">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I221" s="13">
         <v>1500</v>
@@ -9460,10 +9460,10 @@
         <v>1</v>
       </c>
       <c r="G222" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H222" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I222" s="17">
         <v>2000</v>
@@ -9495,10 +9495,10 @@
         <v>1</v>
       </c>
       <c r="G223" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H223" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I223" s="13">
         <v>1500</v>
@@ -9521,19 +9521,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D224" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E224" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F224" s="17">
         <v>1</v>
       </c>
       <c r="G224" s="17">
-        <v>401</v>
+        <v>530</v>
       </c>
       <c r="H224" s="17">
-        <v>401</v>
+        <v>530</v>
       </c>
       <c r="I224" s="17">
         <v>2500</v>
@@ -9556,19 +9556,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D225" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E225" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F225" s="13">
         <v>1</v>
       </c>
       <c r="G225" s="13">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H225" s="13">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I225" s="13">
         <v>2000</v>
@@ -9600,10 +9600,10 @@
         <v>1</v>
       </c>
       <c r="G226" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H226" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I226" s="17">
         <v>1200</v>
@@ -9635,10 +9635,10 @@
         <v>1</v>
       </c>
       <c r="G227" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H227" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I227" s="13">
         <v>1500</v>
@@ -9670,10 +9670,10 @@
         <v>1</v>
       </c>
       <c r="G228" s="17">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H228" s="17">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I228" s="17">
         <v>1500</v>
@@ -9705,10 +9705,10 @@
         <v>1</v>
       </c>
       <c r="G229" s="13">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H229" s="13">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I229" s="13">
         <v>2000</v>
@@ -9740,10 +9740,10 @@
         <v>1</v>
       </c>
       <c r="G230" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H230" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I230" s="17">
         <v>1500</v>
@@ -9766,19 +9766,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D231" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E231" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F231" s="13">
         <v>1</v>
       </c>
       <c r="G231" s="13">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="H231" s="13">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="I231" s="13">
         <v>2500</v>
@@ -9810,10 +9810,10 @@
         <v>1</v>
       </c>
       <c r="G232" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H232" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I232" s="17">
         <v>1500</v>
@@ -9836,19 +9836,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D233" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E233" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F233" s="13">
         <v>1</v>
       </c>
       <c r="G233" s="13">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H233" s="13">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I233" s="13">
         <v>2000</v>
@@ -9880,10 +9880,10 @@
         <v>1</v>
       </c>
       <c r="G234" s="17">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H234" s="17">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I234" s="17">
         <v>1200</v>
@@ -9915,10 +9915,10 @@
         <v>1</v>
       </c>
       <c r="G235" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H235" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I235" s="13">
         <v>1500</v>
@@ -9950,10 +9950,10 @@
         <v>1</v>
       </c>
       <c r="G236" s="17">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H236" s="17">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I236" s="17">
         <v>1500</v>
@@ -9985,10 +9985,10 @@
         <v>1</v>
       </c>
       <c r="G237" s="13">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H237" s="13">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I237" s="13">
         <v>2000</v>
@@ -10020,10 +10020,10 @@
         <v>1</v>
       </c>
       <c r="G238" s="17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H238" s="17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I238" s="17">
         <v>1500</v>
@@ -10046,19 +10046,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D239" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E239" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F239" s="13">
         <v>1</v>
       </c>
       <c r="G239" s="13">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="H239" s="13">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="I239" s="13">
         <v>2500</v>
@@ -10081,19 +10081,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D240" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E240" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F240" s="17">
         <v>1</v>
       </c>
       <c r="G240" s="17">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H240" s="17">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I240" s="17">
         <v>2000</v>
@@ -10125,10 +10125,10 @@
         <v>1</v>
       </c>
       <c r="G241" s="13">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H241" s="13">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I241" s="13">
         <v>1200</v>
@@ -10160,10 +10160,10 @@
         <v>1</v>
       </c>
       <c r="G242" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H242" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I242" s="17">
         <v>1500</v>
@@ -10195,10 +10195,10 @@
         <v>1</v>
       </c>
       <c r="G243" s="13">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H243" s="13">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I243" s="13">
         <v>1500</v>
@@ -10230,10 +10230,10 @@
         <v>1</v>
       </c>
       <c r="G244" s="17">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H244" s="17">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I244" s="17">
         <v>2000</v>
@@ -10265,10 +10265,10 @@
         <v>1</v>
       </c>
       <c r="G245" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H245" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I245" s="13">
         <v>1500</v>
@@ -10291,19 +10291,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D246" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E246" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F246" s="17">
         <v>1</v>
       </c>
       <c r="G246" s="17">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="H246" s="17">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="I246" s="17">
         <v>2500</v>
@@ -10326,19 +10326,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D247" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E247" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F247" s="13">
         <v>1</v>
       </c>
       <c r="G247" s="13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H247" s="13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I247" s="13">
         <v>2000</v>
@@ -10370,10 +10370,10 @@
         <v>1</v>
       </c>
       <c r="G248" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H248" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I248" s="17">
         <v>1200</v>
@@ -10405,10 +10405,10 @@
         <v>1</v>
       </c>
       <c r="G249" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H249" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I249" s="13">
         <v>1500</v>
@@ -10440,10 +10440,10 @@
         <v>1</v>
       </c>
       <c r="G250" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H250" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I250" s="17">
         <v>1500</v>
@@ -10475,10 +10475,10 @@
         <v>1</v>
       </c>
       <c r="G251" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H251" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I251" s="13">
         <v>2000</v>
@@ -10510,10 +10510,10 @@
         <v>1</v>
       </c>
       <c r="G252" s="17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H252" s="17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I252" s="17">
         <v>1500</v>
@@ -10536,19 +10536,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D253" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E253" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F253" s="13">
         <v>1</v>
       </c>
       <c r="G253" s="13">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="H253" s="13">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="I253" s="13">
         <v>2500</v>
@@ -10580,10 +10580,10 @@
         <v>1</v>
       </c>
       <c r="G254" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H254" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I254" s="17">
         <v>1500</v>
@@ -10606,19 +10606,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D255" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E255" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F255" s="13">
         <v>1</v>
       </c>
       <c r="G255" s="13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H255" s="13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I255" s="13">
         <v>2000</v>
@@ -10650,10 +10650,10 @@
         <v>1</v>
       </c>
       <c r="G256" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H256" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I256" s="17">
         <v>1200</v>
@@ -10685,10 +10685,10 @@
         <v>1</v>
       </c>
       <c r="G257" s="13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H257" s="13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I257" s="13">
         <v>1500</v>
@@ -10720,10 +10720,10 @@
         <v>1</v>
       </c>
       <c r="G258" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H258" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I258" s="17">
         <v>1500</v>
@@ -10755,10 +10755,10 @@
         <v>1</v>
       </c>
       <c r="G259" s="13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H259" s="13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I259" s="13">
         <v>2000</v>
@@ -10790,10 +10790,10 @@
         <v>1</v>
       </c>
       <c r="G260" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H260" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I260" s="17">
         <v>1500</v>
@@ -10816,19 +10816,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D261" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E261" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F261" s="13">
         <v>1</v>
       </c>
       <c r="G261" s="13">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="H261" s="13">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="I261" s="13">
         <v>2500</v>
@@ -10851,19 +10851,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D262" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E262" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F262" s="17">
         <v>1</v>
       </c>
       <c r="G262" s="17">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H262" s="17">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I262" s="17">
         <v>2000</v>
@@ -10895,10 +10895,10 @@
         <v>1</v>
       </c>
       <c r="G263" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H263" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I263" s="13">
         <v>1200</v>
@@ -10930,10 +10930,10 @@
         <v>1</v>
       </c>
       <c r="G264" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H264" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I264" s="17">
         <v>1500</v>
@@ -10965,10 +10965,10 @@
         <v>1</v>
       </c>
       <c r="G265" s="13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H265" s="13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I265" s="13">
         <v>1500</v>
@@ -11000,10 +11000,10 @@
         <v>1</v>
       </c>
       <c r="G266" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H266" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I266" s="17">
         <v>2000</v>
@@ -11035,10 +11035,10 @@
         <v>1</v>
       </c>
       <c r="G267" s="13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I267" s="13">
         <v>1500</v>
@@ -11061,19 +11061,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D268" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E268" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F268" s="17">
         <v>1</v>
       </c>
       <c r="G268" s="17">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H268" s="17">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I268" s="17">
         <v>2500</v>
@@ -11096,19 +11096,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D269" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E269" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F269" s="13">
         <v>1</v>
       </c>
       <c r="G269" s="13">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H269" s="13">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I269" s="13">
         <v>2000</v>
@@ -11140,10 +11140,10 @@
         <v>1</v>
       </c>
       <c r="G270" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H270" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I270" s="17">
         <v>1200</v>
@@ -11175,10 +11175,10 @@
         <v>1</v>
       </c>
       <c r="G271" s="13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H271" s="13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I271" s="13">
         <v>1500</v>
@@ -11210,10 +11210,10 @@
         <v>1</v>
       </c>
       <c r="G272" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H272" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I272" s="17">
         <v>1500</v>
@@ -11245,10 +11245,10 @@
         <v>1</v>
       </c>
       <c r="G273" s="13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H273" s="13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I273" s="13">
         <v>2000</v>
@@ -11280,10 +11280,10 @@
         <v>1</v>
       </c>
       <c r="G274" s="17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H274" s="17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I274" s="17">
         <v>1500</v>
@@ -11306,19 +11306,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D275" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E275" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F275" s="13">
         <v>1</v>
       </c>
       <c r="G275" s="13">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="H275" s="13">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="I275" s="13">
         <v>2500</v>
@@ -11350,10 +11350,10 @@
         <v>1</v>
       </c>
       <c r="G276" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H276" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I276" s="17">
         <v>1500</v>
@@ -11376,19 +11376,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D277" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E277" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F277" s="13">
         <v>1</v>
       </c>
       <c r="G277" s="13">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H277" s="13">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I277" s="13">
         <v>2000</v>
@@ -11420,10 +11420,10 @@
         <v>1</v>
       </c>
       <c r="G278" s="17">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H278" s="17">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I278" s="17">
         <v>1200</v>
@@ -11455,10 +11455,10 @@
         <v>1</v>
       </c>
       <c r="G279" s="13">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H279" s="13">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I279" s="13">
         <v>1500</v>
@@ -11490,10 +11490,10 @@
         <v>1</v>
       </c>
       <c r="G280" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H280" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I280" s="17">
         <v>1500</v>
@@ -11525,10 +11525,10 @@
         <v>1</v>
       </c>
       <c r="G281" s="13">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H281" s="13">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I281" s="13">
         <v>2000</v>
@@ -11560,10 +11560,10 @@
         <v>1</v>
       </c>
       <c r="G282" s="17">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H282" s="17">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I282" s="17">
         <v>1500</v>
@@ -11586,19 +11586,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D283" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E283" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F283" s="13">
         <v>1</v>
       </c>
       <c r="G283" s="13">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="H283" s="13">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="I283" s="13">
         <v>2500</v>
@@ -11621,19 +11621,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D284" s="17" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E284" s="17" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F284" s="17">
         <v>1</v>
       </c>
       <c r="G284" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H284" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I284" s="17">
         <v>2000</v>
@@ -11665,10 +11665,10 @@
         <v>1</v>
       </c>
       <c r="G285" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H285" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I285" s="13">
         <v>1200</v>
@@ -11700,10 +11700,10 @@
         <v>1</v>
       </c>
       <c r="G286" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H286" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I286" s="17">
         <v>1500</v>
@@ -11805,10 +11805,10 @@
         <v>1</v>
       </c>
       <c r="G289" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H289" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I289" s="13">
         <v>1500</v>
@@ -11831,19 +11831,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D290" s="17" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E290" s="17" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F290" s="17">
         <v>1</v>
       </c>
       <c r="G290" s="17">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="H290" s="17">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="I290" s="17">
         <v>2500</v>
@@ -11866,19 +11866,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D291" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E291" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F291" s="13">
         <v>1</v>
       </c>
       <c r="G291" s="13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H291" s="13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I291" s="13">
         <v>2000</v>
@@ -11910,10 +11910,10 @@
         <v>1</v>
       </c>
       <c r="G292" s="17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H292" s="17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I292" s="17">
         <v>1200</v>
@@ -11945,10 +11945,10 @@
         <v>1</v>
       </c>
       <c r="G293" s="13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H293" s="13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I293" s="13">
         <v>1500</v>
@@ -11980,10 +11980,10 @@
         <v>1</v>
       </c>
       <c r="G294" s="17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H294" s="17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I294" s="17">
         <v>1500</v>
@@ -12015,10 +12015,10 @@
         <v>1</v>
       </c>
       <c r="G295" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H295" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I295" s="13">
         <v>2000</v>
@@ -12050,10 +12050,10 @@
         <v>1</v>
       </c>
       <c r="G296" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H296" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I296" s="17">
         <v>1500</v>
@@ -12076,19 +12076,19 @@
         <v>CAT-02</v>
       </c>
       <c r="D297" s="13" t="str">
-        <v>JavaScript bundle download · index-6NSHBj9Z.js</v>
+        <v>JavaScript bundle download · index-WyB0cNfi.js</v>
       </c>
       <c r="E297" s="13" t="str">
-        <v>GET /assets/index-6NSHBj9Z.js</v>
+        <v>GET /assets/index-WyB0cNfi.js</v>
       </c>
       <c r="F297" s="13">
         <v>1</v>
       </c>
       <c r="G297" s="13">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H297" s="13">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="I297" s="13">
         <v>2500</v>
@@ -12120,10 +12120,10 @@
         <v>1</v>
       </c>
       <c r="G298" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H298" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I298" s="17">
         <v>1500</v>
@@ -12146,19 +12146,19 @@
         <v>CAT-03</v>
       </c>
       <c r="D299" s="13" t="str">
-        <v>Stylesheet download · index-C8JlRIH3.css</v>
+        <v>Stylesheet download · index-Du5f6LYc.css</v>
       </c>
       <c r="E299" s="13" t="str">
-        <v>GET /assets/index-C8JlRIH3.css</v>
+        <v>GET /assets/index-Du5f6LYc.css</v>
       </c>
       <c r="F299" s="13">
         <v>1</v>
       </c>
       <c r="G299" s="13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H299" s="13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I299" s="13">
         <v>2000</v>
@@ -12190,10 +12190,10 @@
         <v>1</v>
       </c>
       <c r="G300" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H300" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I300" s="17">
         <v>1200</v>
@@ -12225,10 +12225,10 @@
         <v>1</v>
       </c>
       <c r="G301" s="13">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H301" s="13">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I301" s="13">
         <v>1500</v>
@@ -12260,10 +12260,10 @@
         <v>1</v>
       </c>
       <c r="G302" s="17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H302" s="17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I302" s="17">
         <v>2000</v>
@@ -12292,10 +12292,10 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F303" s="13">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="G303" s="13">
-        <v>159.9</v>
+        <v>160</v>
       </c>
       <c r="H303" s="13">
         <v>160</v>
@@ -12327,13 +12327,13 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F304" s="17">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="G304" s="17">
-        <v>720.8</v>
+        <v>703.1</v>
       </c>
       <c r="H304" s="17">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="I304" s="17">
         <v>3000</v>
@@ -12362,7 +12362,7 @@
         <v>LOAD sustained phase</v>
       </c>
       <c r="F305" s="13">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="G305" s="13">
         <v>0</v>
@@ -12575,7 +12575,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B4" s="5">
-        <v>20.32</v>
+        <v>20.28</v>
       </c>
       <c r="D4" s="13" t="str">
         <v>&lt; 50 ms</v>
@@ -12586,7 +12586,7 @@
         <v>Requests</v>
       </c>
       <c r="B5" s="5">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="D5" s="17" t="str">
         <v>50–100 ms</v>
@@ -12597,7 +12597,7 @@
         <v>Throughput (req/s)</v>
       </c>
       <c r="B6" s="5">
-        <v>124.23</v>
+        <v>124.27</v>
       </c>
       <c r="D6" s="13" t="str">
         <v>100–200 ms</v>
@@ -12608,7 +12608,7 @@
         <v>Data transfer (Mbps)</v>
       </c>
       <c r="B7" s="5">
-        <v>816.72</v>
+        <v>817.21</v>
       </c>
       <c r="D7" s="17" t="str">
         <v>200–500 ms</v>
@@ -12619,7 +12619,7 @@
         <v>Average latency (ms)</v>
       </c>
       <c r="B8" s="5">
-        <v>159.9</v>
+        <v>160</v>
       </c>
       <c r="D8" s="13" t="str">
         <v>500–1000 ms</v>
@@ -12630,7 +12630,7 @@
         <v>p50 latency (ms)</v>
       </c>
       <c r="B9" s="5">
-        <v>39.3</v>
+        <v>40.8</v>
       </c>
       <c r="D9" s="17" t="str">
         <v>&gt; 1000 ms</v>
@@ -12641,7 +12641,7 @@
         <v>p95 latency (ms)</v>
       </c>
       <c r="B10" s="5">
-        <v>720.8</v>
+        <v>703.1</v>
       </c>
     </row>
     <row r="11">
@@ -12649,7 +12649,7 @@
         <v>p99 latency (ms)</v>
       </c>
       <c r="B11" s="5">
-        <v>775.2</v>
+        <v>772.3</v>
       </c>
     </row>
     <row r="12">
@@ -12657,7 +12657,7 @@
         <v>Max latency (ms)</v>
       </c>
       <c r="B12" s="5">
-        <v>845</v>
+        <v>926.2</v>
       </c>
     </row>
     <row r="13">
@@ -12745,7 +12745,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B8" s="13" t="str">
-        <v>40366447214</v>
+        <v>40369854574</v>
       </c>
     </row>
     <row r="9">
@@ -12769,7 +12769,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B11" s="17" t="str">
-        <v>a9ce338</v>
+        <v>0cee3c6</v>
       </c>
     </row>
     <row r="12">
@@ -12777,7 +12777,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B12" s="13" t="str">
-        <v>2026-10-26T17:13:56.779Z</v>
+        <v>2026-10-26T17:34:51.500Z</v>
       </c>
     </row>
     <row r="13">
@@ -12785,7 +12785,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B13" s="17" t="str">
-        <v>2026-10-26T17:14:19.441Z</v>
+        <v>2026-10-26T17:35:14.184Z</v>
       </c>
     </row>
     <row r="14">
@@ -12817,7 +12817,7 @@
         <v>Sustained duration (s)</v>
       </c>
       <c r="B17" s="17">
-        <v>20.32</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="18">
